--- a/research/traditional_assets/database/data/luxembourg/luxembourg_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_hospitals_healthcare_facilities.xlsx
@@ -638,10 +638,10 @@
         <v>-0.0776084407971864</v>
       </c>
       <c r="X2">
-        <v>0.1067191374931998</v>
+        <v>0.1066799719041445</v>
       </c>
       <c r="Y2">
-        <v>-0.1843275782903862</v>
+        <v>-0.1842884127013309</v>
       </c>
       <c r="Z2">
         <v>0.8636699689486913</v>
@@ -650,10 +650,10 @@
         <v>0.1475676474937158</v>
       </c>
       <c r="AB2">
-        <v>0.07164709765567484</v>
+        <v>0.07163397170880423</v>
       </c>
       <c r="AC2">
-        <v>0.07592054983804095</v>
+        <v>0.07593367578491156</v>
       </c>
       <c r="AD2">
         <v>1006</v>
@@ -763,10 +763,10 @@
         <v>-0.0776084407971864</v>
       </c>
       <c r="X3">
-        <v>0.1067191374931998</v>
+        <v>0.1066799719041445</v>
       </c>
       <c r="Y3">
-        <v>-0.1843275782903862</v>
+        <v>-0.1842884127013309</v>
       </c>
       <c r="Z3">
         <v>0.8636699689486913</v>
@@ -775,10 +775,10 @@
         <v>0.1475676474937158</v>
       </c>
       <c r="AB3">
-        <v>0.07164709765567484</v>
+        <v>0.07163397170880423</v>
       </c>
       <c r="AC3">
-        <v>0.07592054983804095</v>
+        <v>0.07593367578491156</v>
       </c>
       <c r="AD3">
         <v>1006</v>
@@ -1115,49 +1115,49 @@
         <v>1.33601070950469</v>
       </c>
       <c r="F2">
-        <v>4.53268226943944</v>
+        <v>4.50116364587722</v>
       </c>
       <c r="G2">
         <v>4.04666130329847</v>
       </c>
       <c r="H2">
-        <v>5.59956556717619</v>
+        <v>5.90388978278359</v>
       </c>
       <c r="I2">
         <v>0.664860220738881</v>
       </c>
       <c r="J2">
-        <v>0.92</v>
+        <v>0.97</v>
       </c>
       <c r="K2">
         <v>507.1</v>
       </c>
       <c r="L2">
-        <v>320.296335602291</v>
+        <v>304.023721319083</v>
       </c>
       <c r="M2">
         <v>1459.2</v>
       </c>
       <c r="N2">
-        <v>1658.44833560229</v>
+        <v>1717.83072131908</v>
       </c>
       <c r="O2">
         <v>1006</v>
       </c>
       <c r="P2">
-        <v>1392.052</v>
+        <v>1467.707</v>
       </c>
       <c r="Q2">
-        <v>0.0716470976556748</v>
+        <v>0.0716339717088042</v>
       </c>
       <c r="R2">
-        <v>0.06250601435981321</v>
+        <v>0.060178859775647</v>
       </c>
       <c r="S2">
         <v>0.05396814</v>
       </c>
       <c r="T2">
-        <v>0.04345974</v>
+        <v>0.04150818</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1170,16 +1170,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.1067191374932</v>
+        <v>0.106679971904145</v>
       </c>
       <c r="X2">
-        <v>0.281538169497665</v>
+        <v>0.663864172521565</v>
       </c>
       <c r="Y2">
         <v>1.40600397007262</v>
       </c>
       <c r="Z2">
-        <v>5.44079932596499</v>
+        <v>14.2739993653941</v>
       </c>
       <c r="AA2">
         <v>1006</v>
@@ -1212,7 +1212,7 @@
         <v>507.1</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.0433</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.07027473182836876</v>
+        <v>0.07025899675186452</v>
       </c>
       <c r="C2">
-        <v>1539.903079457958</v>
+        <v>1539.955310042646</v>
       </c>
       <c r="D2">
-        <v>1486.003079457958</v>
+        <v>1486.055310042646</v>
       </c>
       <c r="E2">
         <v>-1006</v>
@@ -1451,19 +1451,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.07027473182836876</v>
+        <v>0.07025899675186452</v>
       </c>
       <c r="T2">
         <v>0.5648729042001043</v>
       </c>
       <c r="U2">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.2494</v>
       </c>
       <c r="W2">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1482,13 +1482,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.0701437520471888</v>
+        <v>0.07011754781396537</v>
       </c>
       <c r="C3">
-        <v>1527.381751740811</v>
+        <v>1527.643200872283</v>
       </c>
       <c r="D3">
-        <v>1488.612751740811</v>
+        <v>1488.874200872283</v>
       </c>
       <c r="E3">
         <v>-990.869</v>
@@ -1515,37 +1515,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M3">
-        <v>0.7822727000000002</v>
+        <v>0.7610893000000001</v>
       </c>
       <c r="N3">
-        <v>364.5510606333333</v>
+        <v>364.5722440333333</v>
       </c>
       <c r="O3">
-        <v>90.91903452195332</v>
+        <v>90.92431766191334</v>
       </c>
       <c r="P3">
-        <v>273.63202611138</v>
+        <v>273.64792637142</v>
       </c>
       <c r="Q3">
-        <v>322.63202611138</v>
+        <v>322.64792637142</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.0704602947951402</v>
+        <v>0.07044444041814683</v>
       </c>
       <c r="T3">
         <v>0.569155667855585</v>
       </c>
       <c r="U3">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.2494</v>
       </c>
       <c r="W3">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>467.0153174632493</v>
+        <v>480.013755722664</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1564,13 +1564,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.07001277226600884</v>
+        <v>0.06997609887606622</v>
       </c>
       <c r="C4">
-        <v>1514.869606199331</v>
+        <v>1515.341806306019</v>
       </c>
       <c r="D4">
-        <v>1491.23160619933</v>
+        <v>1491.703806306019</v>
       </c>
       <c r="E4">
         <v>-975.7380000000001</v>
@@ -1597,37 +1597,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M4">
-        <v>1.5645454</v>
+        <v>1.5221786</v>
       </c>
       <c r="N4">
-        <v>363.7687879333333</v>
+        <v>363.8111547333333</v>
       </c>
       <c r="O4">
-        <v>90.72393571057333</v>
+        <v>90.73450199049333</v>
       </c>
       <c r="P4">
-        <v>273.04485222276</v>
+        <v>273.07665274284</v>
       </c>
       <c r="Q4">
-        <v>322.04485222276</v>
+        <v>322.07665274284</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.07064964476123352</v>
+        <v>0.07063366864904716</v>
       </c>
       <c r="T4">
         <v>0.5735258348509736</v>
       </c>
       <c r="U4">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.2494</v>
       </c>
       <c r="W4">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>233.5076587316247</v>
+        <v>240.006877861332</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1646,13 +1646,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.06988179248482888</v>
+        <v>0.06983464993816706</v>
       </c>
       <c r="C5">
-        <v>1502.366691380382</v>
+        <v>1503.051187549493</v>
       </c>
       <c r="D5">
-        <v>1493.859691380382</v>
+        <v>1494.544187549493</v>
       </c>
       <c r="E5">
         <v>-960.607</v>
@@ -1679,37 +1679,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M5">
-        <v>2.3468181</v>
+        <v>2.2832679</v>
       </c>
       <c r="N5">
-        <v>362.9865152333333</v>
+        <v>363.0500654333333</v>
       </c>
       <c r="O5">
-        <v>90.52883689919334</v>
+        <v>90.54468631907334</v>
       </c>
       <c r="P5">
-        <v>272.45767833414</v>
+        <v>272.50537911426</v>
       </c>
       <c r="Q5">
-        <v>321.45767833414</v>
+        <v>321.50537911426</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.07084289885033906</v>
+        <v>0.07082679849295573</v>
       </c>
       <c r="T5">
         <v>0.5779861083823495</v>
       </c>
       <c r="U5">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.2494</v>
       </c>
       <c r="W5">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>155.6717724877498</v>
+        <v>160.004585240888</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1728,13 +1728,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.06975081270364894</v>
+        <v>0.06969320100026791</v>
       </c>
       <c r="C6">
-        <v>1489.873056173662</v>
+        <v>1490.771406275401</v>
       </c>
       <c r="D6">
-        <v>1496.497056173662</v>
+        <v>1497.395406275401</v>
       </c>
       <c r="E6">
         <v>-945.476</v>
@@ -1761,37 +1761,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M6">
-        <v>3.129090800000001</v>
+        <v>3.0443572</v>
       </c>
       <c r="N6">
-        <v>362.2042425333333</v>
+        <v>362.2889761333333</v>
       </c>
       <c r="O6">
-        <v>90.33373808781333</v>
+        <v>90.35487064765334</v>
       </c>
       <c r="P6">
-        <v>271.8705044455199</v>
+        <v>271.93410548568</v>
       </c>
       <c r="Q6">
-        <v>320.8705044455199</v>
+        <v>320.93410548568</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.07104017906630097</v>
+        <v>0.07102395187527907</v>
       </c>
       <c r="T6">
         <v>0.5825393042789625</v>
       </c>
       <c r="U6">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.2494</v>
       </c>
       <c r="W6">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>116.7538293658123</v>
+        <v>120.003438930666</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1810,13 +1810,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.069619832922469</v>
+        <v>0.06955175206236876</v>
       </c>
       <c r="C7">
-        <v>1477.388749814732</v>
+        <v>1478.502524627966</v>
       </c>
       <c r="D7">
-        <v>1499.143749814732</v>
+        <v>1500.257524627965</v>
       </c>
       <c r="E7">
         <v>-930.345</v>
@@ -1843,37 +1843,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M7">
-        <v>3.911363500000001</v>
+        <v>3.8054465</v>
       </c>
       <c r="N7">
-        <v>361.4219698333333</v>
+        <v>361.5278868333333</v>
       </c>
       <c r="O7">
-        <v>90.13863927643334</v>
+        <v>90.16505497623332</v>
       </c>
       <c r="P7">
-        <v>271.2833305569</v>
+        <v>271.3628318571</v>
       </c>
       <c r="Q7">
-        <v>320.2833305569</v>
+        <v>320.3628318571</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.07124161254996736</v>
+        <v>0.07122525585512501</v>
       </c>
       <c r="T7">
         <v>0.5871883569312937</v>
       </c>
       <c r="U7">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.2494</v>
       </c>
       <c r="W7">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>93.40306349264988</v>
+        <v>96.00275114453278</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1892,13 +1892,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.06948885314128904</v>
+        <v>0.06941030312446961</v>
       </c>
       <c r="C8">
-        <v>1464.913821888081</v>
+        <v>1466.244605227447</v>
       </c>
       <c r="D8">
-        <v>1501.799821888081</v>
+        <v>1503.130605227447</v>
       </c>
       <c r="E8">
         <v>-915.2140000000001</v>
@@ -1925,37 +1925,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M8">
-        <v>4.6936362</v>
+        <v>4.5665358</v>
       </c>
       <c r="N8">
-        <v>360.6396971333333</v>
+        <v>360.7667975333333</v>
       </c>
       <c r="O8">
-        <v>89.94354046505333</v>
+        <v>89.97523930481333</v>
       </c>
       <c r="P8">
-        <v>270.69615666828</v>
+        <v>270.79155822852</v>
       </c>
       <c r="Q8">
-        <v>319.69615666828</v>
+        <v>319.79155822852</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.07144733185243515</v>
+        <v>0.07143084289837193</v>
       </c>
       <c r="T8">
         <v>0.5919363255975041</v>
       </c>
       <c r="U8">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.2494</v>
       </c>
       <c r="W8">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>77.83588624387491</v>
+        <v>80.00229262044401</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1974,13 +1974,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.06935787336010908</v>
+        <v>0.06926885418657046</v>
       </c>
       <c r="C9">
-        <v>1452.448322330222</v>
+        <v>1453.997711174713</v>
       </c>
       <c r="D9">
-        <v>1504.465322330221</v>
+        <v>1506.014711174713</v>
       </c>
       <c r="E9">
         <v>-900.083</v>
@@ -2007,37 +2007,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M9">
-        <v>5.475908900000001</v>
+        <v>5.327625100000001</v>
       </c>
       <c r="N9">
-        <v>359.8574244333333</v>
+        <v>360.0057082333333</v>
       </c>
       <c r="O9">
-        <v>89.74844165367334</v>
+        <v>89.78542363339334</v>
       </c>
       <c r="P9">
-        <v>270.10898277966</v>
+        <v>270.22028459994</v>
       </c>
       <c r="Q9">
-        <v>319.10898277966</v>
+        <v>319.22028459994</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.07165747522592375</v>
+        <v>0.07164085116835534</v>
       </c>
       <c r="T9">
         <v>0.5967864011167515</v>
       </c>
       <c r="U9">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.2494</v>
       </c>
       <c r="W9">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>66.71647392332135</v>
+        <v>68.57339367466628</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2056,13 +2056,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.06922689357892914</v>
+        <v>0.06912740524867132</v>
       </c>
       <c r="C10">
-        <v>1439.99230143282</v>
+        <v>1441.761906055856</v>
       </c>
       <c r="D10">
-        <v>1507.14030143282</v>
+        <v>1508.909906055856</v>
       </c>
       <c r="E10">
         <v>-884.952</v>
@@ -2089,37 +2089,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M10">
-        <v>6.258181600000001</v>
+        <v>6.088714400000001</v>
       </c>
       <c r="N10">
-        <v>359.0751517333333</v>
+        <v>359.2446189333333</v>
       </c>
       <c r="O10">
-        <v>89.55334284229333</v>
+        <v>89.59560796197333</v>
       </c>
       <c r="P10">
-        <v>269.52180889104</v>
+        <v>269.64901097136</v>
       </c>
       <c r="Q10">
-        <v>318.52180889104</v>
+        <v>318.64901097136</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.07187218693361863</v>
+        <v>0.0718554248355123</v>
       </c>
       <c r="T10">
         <v>0.6017419130603302</v>
       </c>
       <c r="U10">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.2494</v>
       </c>
       <c r="W10">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>58.37691468290618</v>
+        <v>60.00171946533299</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2138,13 +2138,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.06909591379774918</v>
+        <v>0.06898595631077217</v>
       </c>
       <c r="C11">
-        <v>1427.54580984586</v>
+        <v>1429.537253946868</v>
       </c>
       <c r="D11">
-        <v>1509.82480984586</v>
+        <v>1511.816253946868</v>
       </c>
       <c r="E11">
         <v>-869.821</v>
@@ -2171,37 +2171,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M11">
-        <v>7.0404543</v>
+        <v>6.849803699999999</v>
       </c>
       <c r="N11">
-        <v>358.2928790333333</v>
+        <v>358.4835296333333</v>
       </c>
       <c r="O11">
-        <v>89.35824403091333</v>
+        <v>89.40579229055334</v>
       </c>
       <c r="P11">
-        <v>268.93463500242</v>
+        <v>269.07773734278</v>
       </c>
       <c r="Q11">
-        <v>317.93463500242</v>
+        <v>318.07773734278</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.07209161757994416</v>
+        <v>0.07207471440744194</v>
       </c>
       <c r="T11">
         <v>0.6068063373543173</v>
       </c>
       <c r="U11">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.2494</v>
       </c>
       <c r="W11">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>51.89059082924994</v>
+        <v>53.33486174696267</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2220,13 +2220,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.06896493401656924</v>
+        <v>0.06884450737287302</v>
       </c>
       <c r="C12">
-        <v>1415.108898580838</v>
+        <v>1417.323819418367</v>
       </c>
       <c r="D12">
-        <v>1512.518898580838</v>
+        <v>1514.733819418367</v>
       </c>
       <c r="E12">
         <v>-854.6900000000001</v>
@@ -2253,37 +2253,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M12">
-        <v>7.822727000000001</v>
+        <v>7.610893000000001</v>
       </c>
       <c r="N12">
-        <v>357.5106063333333</v>
+        <v>357.7224403333333</v>
       </c>
       <c r="O12">
-        <v>89.16314521953333</v>
+        <v>89.21597661913334</v>
       </c>
       <c r="P12">
-        <v>268.3474611138</v>
+        <v>268.5064637142</v>
       </c>
       <c r="Q12">
-        <v>317.3474611138</v>
+        <v>317.5064637142</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.0723159244628547</v>
+        <v>0.07229887708097002</v>
       </c>
       <c r="T12">
         <v>0.6119833044103929</v>
       </c>
       <c r="U12">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.2494</v>
       </c>
       <c r="W12">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>46.70153174632494</v>
+        <v>48.0013755722664</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2302,13 +2302,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.06883395423538927</v>
+        <v>0.06870305843497387</v>
       </c>
       <c r="C13">
-        <v>1402.681619013997</v>
+        <v>1405.121667540379</v>
       </c>
       <c r="D13">
-        <v>1515.222619013997</v>
+        <v>1517.662667540379</v>
       </c>
       <c r="E13">
         <v>-839.559</v>
@@ -2335,37 +2335,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M13">
-        <v>8.604999700000002</v>
+        <v>8.371982300000001</v>
       </c>
       <c r="N13">
-        <v>356.7283336333333</v>
+        <v>356.9613510333333</v>
       </c>
       <c r="O13">
-        <v>88.96804640815333</v>
+        <v>89.02616094771332</v>
       </c>
       <c r="P13">
-        <v>267.76028722518</v>
+        <v>267.93519008562</v>
       </c>
       <c r="Q13">
-        <v>316.76028722518</v>
+        <v>316.93519008562</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.07254527194987559</v>
+        <v>0.07252807711794816</v>
       </c>
       <c r="T13">
         <v>0.6172766078048074</v>
       </c>
       <c r="U13">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.2494</v>
       </c>
       <c r="W13">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>42.45593795120448</v>
+        <v>43.63761415660581</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2384,13 +2384,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.06870297445420934</v>
+        <v>0.06856160949707471</v>
       </c>
       <c r="C14">
-        <v>1390.264022889588</v>
+        <v>1392.930863887175</v>
       </c>
       <c r="D14">
-        <v>1517.936022889588</v>
+        <v>1520.602863887175</v>
       </c>
       <c r="E14">
         <v>-824.428</v>
@@ -2417,37 +2417,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M14">
-        <v>9.387272400000001</v>
+        <v>9.133071599999999</v>
       </c>
       <c r="N14">
-        <v>355.9460609333333</v>
+        <v>356.2002617333333</v>
       </c>
       <c r="O14">
-        <v>88.77294759677334</v>
+        <v>88.83634527629333</v>
       </c>
       <c r="P14">
-        <v>267.17311333656</v>
+        <v>267.36391645704</v>
       </c>
       <c r="Q14">
-        <v>316.17311333656</v>
+        <v>316.36391645704</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.07277983187978333</v>
+        <v>0.07276248624667581</v>
       </c>
       <c r="T14">
         <v>0.6226902135490949</v>
       </c>
       <c r="U14">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.2494</v>
       </c>
       <c r="W14">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>38.91794312193745</v>
+        <v>40.001146310222</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2466,13 +2466,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.06857199467302938</v>
+        <v>0.06842016055917557</v>
       </c>
       <c r="C15">
-        <v>1377.856162323175</v>
+        <v>1380.751474542164</v>
       </c>
       <c r="D15">
-        <v>1520.659162323175</v>
+        <v>1523.554474542164</v>
       </c>
       <c r="E15">
         <v>-809.297</v>
@@ -2499,37 +2499,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M15">
-        <v>10.1695451</v>
+        <v>9.894160900000001</v>
       </c>
       <c r="N15">
-        <v>355.1637882333333</v>
+        <v>355.4391724333333</v>
       </c>
       <c r="O15">
-        <v>88.57784878539333</v>
+        <v>88.64652960487334</v>
       </c>
       <c r="P15">
-        <v>266.58593944794</v>
+        <v>266.79264282846</v>
       </c>
       <c r="Q15">
-        <v>315.58593944794</v>
+        <v>315.79264282846</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.07301978399198779</v>
+        <v>0.0730022840910064</v>
       </c>
       <c r="T15">
         <v>0.6282282700001477</v>
       </c>
       <c r="U15">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.2494</v>
       </c>
       <c r="W15">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>35.92425518948072</v>
+        <v>36.92413505558954</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2548,13 +2548,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.06844101489184944</v>
+        <v>0.06827871162127641</v>
       </c>
       <c r="C16">
-        <v>1365.458089804972</v>
+        <v>1368.58356610285</v>
       </c>
       <c r="D16">
-        <v>1523.392089804972</v>
+        <v>1526.51756610285</v>
       </c>
       <c r="E16">
         <v>-794.1659999999999</v>
@@ -2581,37 +2581,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M16">
-        <v>10.9518178</v>
+        <v>10.6552502</v>
       </c>
       <c r="N16">
-        <v>354.3815155333333</v>
+        <v>354.6780831333333</v>
       </c>
       <c r="O16">
-        <v>88.38274997401332</v>
+        <v>88.45671393345333</v>
       </c>
       <c r="P16">
-        <v>265.99876555932</v>
+        <v>266.22136919988</v>
       </c>
       <c r="Q16">
-        <v>314.99876555932</v>
+        <v>315.22136919988</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.07326531638587143</v>
+        <v>0.07324765862939119</v>
       </c>
       <c r="T16">
         <v>0.6338951184616901</v>
       </c>
       <c r="U16">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.2494</v>
       </c>
       <c r="W16">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>33.35823696166067</v>
+        <v>34.28669683733314</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2630,13 +2630,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.06831003511066946</v>
+        <v>0.06813726268337726</v>
       </c>
       <c r="C17">
-        <v>1353.06985820321</v>
+        <v>1356.427205685832</v>
       </c>
       <c r="D17">
-        <v>1526.134858203209</v>
+        <v>1529.492205685832</v>
       </c>
       <c r="E17">
         <v>-779.0350000000001</v>
@@ -2663,37 +2663,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M17">
-        <v>11.7340905</v>
+        <v>11.4163395</v>
       </c>
       <c r="N17">
-        <v>353.5992428333333</v>
+        <v>353.9169938333333</v>
       </c>
       <c r="O17">
-        <v>88.18765116263334</v>
+        <v>88.26689826203334</v>
       </c>
       <c r="P17">
-        <v>265.4115916707</v>
+        <v>265.6500955713</v>
       </c>
       <c r="Q17">
-        <v>314.4115916707</v>
+        <v>314.6500955713</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.07351662601255232</v>
+        <v>0.07349880668632619</v>
       </c>
       <c r="T17">
         <v>0.6396953045340922</v>
       </c>
       <c r="U17">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.2494</v>
       </c>
       <c r="W17">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>31.13435449754996</v>
+        <v>32.0009170481776</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2712,13 +2712,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.06817905532948952</v>
+        <v>0.06799581374547811</v>
       </c>
       <c r="C18">
-        <v>1340.691520767552</v>
+        <v>1344.282460931877</v>
       </c>
       <c r="D18">
-        <v>1528.887520767552</v>
+        <v>1532.478460931877</v>
       </c>
       <c r="E18">
         <v>-763.904</v>
@@ -2745,37 +2745,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M18">
-        <v>12.5163632</v>
+        <v>12.1774288</v>
       </c>
       <c r="N18">
-        <v>352.8169701333333</v>
+        <v>353.1559045333333</v>
       </c>
       <c r="O18">
-        <v>87.99255235125334</v>
+        <v>88.07708259061334</v>
       </c>
       <c r="P18">
-        <v>264.82441778208</v>
+        <v>265.07882194272</v>
       </c>
       <c r="Q18">
-        <v>313.82441778208</v>
+        <v>314.07882194272</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.07377391920177324</v>
+        <v>0.07375593445890252</v>
       </c>
       <c r="T18">
         <v>0.6456335902748849</v>
       </c>
       <c r="U18">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.2494</v>
       </c>
       <c r="W18">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>29.18845734145309</v>
+        <v>30.0008597326665</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2794,13 +2794,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.06804807554830958</v>
+        <v>0.06785436480757895</v>
       </c>
       <c r="C19">
-        <v>1328.323131132538</v>
+        <v>1332.149400011048</v>
       </c>
       <c r="D19">
-        <v>1531.650131132537</v>
+        <v>1535.476400011048</v>
       </c>
       <c r="E19">
         <v>-748.773</v>
@@ -2827,37 +2827,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M19">
-        <v>13.2986359</v>
+        <v>12.9385181</v>
       </c>
       <c r="N19">
-        <v>352.0346974333333</v>
+        <v>352.3948152333333</v>
       </c>
       <c r="O19">
-        <v>87.79745353987333</v>
+        <v>87.88726691919332</v>
       </c>
       <c r="P19">
-        <v>264.2372438934599</v>
+        <v>264.50754831414</v>
       </c>
       <c r="Q19">
-        <v>313.2372438934599</v>
+        <v>313.50754831414</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.07403741222687901</v>
+        <v>0.07401925808142043</v>
       </c>
       <c r="T19">
         <v>0.6517149672383473</v>
       </c>
       <c r="U19">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.2494</v>
       </c>
       <c r="W19">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>27.47148926254408</v>
+        <v>28.23610327780376</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2876,13 +2876,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.06791709576712963</v>
+        <v>0.06771291586967981</v>
       </c>
       <c r="C20">
-        <v>1315.964743321065</v>
+        <v>1320.028091627886</v>
       </c>
       <c r="D20">
-        <v>1534.422743321065</v>
+        <v>1538.486091627886</v>
       </c>
       <c r="E20">
         <v>-733.6420000000001</v>
@@ -2909,37 +2909,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M20">
-        <v>14.0809086</v>
+        <v>13.6996074</v>
       </c>
       <c r="N20">
-        <v>351.2524247333333</v>
+        <v>351.6337259333333</v>
       </c>
       <c r="O20">
-        <v>87.60235472849334</v>
+        <v>87.69745124777333</v>
       </c>
       <c r="P20">
-        <v>263.65007000484</v>
+        <v>263.93627468556</v>
       </c>
       <c r="Q20">
-        <v>312.65007000484</v>
+        <v>312.93627468556</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.07430733191113369</v>
+        <v>0.07428900423131685</v>
       </c>
       <c r="T20">
         <v>0.6579446704692112</v>
       </c>
       <c r="U20">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.2494</v>
       </c>
       <c r="W20">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>25.94529541462497</v>
+        <v>26.66743087348134</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2958,13 +2958,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.06778611598594968</v>
+        <v>0.06757146693178066</v>
       </c>
       <c r="C21">
-        <v>1303.616411747916</v>
+        <v>1307.918605026663</v>
       </c>
       <c r="D21">
-        <v>1537.205411747916</v>
+        <v>1541.507605026663</v>
       </c>
       <c r="E21">
         <v>-718.511</v>
@@ -2991,37 +2991,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M21">
-        <v>14.8631813</v>
+        <v>14.4606967</v>
       </c>
       <c r="N21">
-        <v>350.4701520333333</v>
+        <v>350.8726366333333</v>
       </c>
       <c r="O21">
-        <v>87.40725591711333</v>
+        <v>87.50763557635332</v>
       </c>
       <c r="P21">
-        <v>263.06289611622</v>
+        <v>263.36500105698</v>
       </c>
       <c r="Q21">
-        <v>312.06289611622</v>
+        <v>312.36500105698</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.07458391627895021</v>
+        <v>0.07456541077997612</v>
       </c>
       <c r="T21">
         <v>0.6643281935329359</v>
       </c>
       <c r="U21">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.2494</v>
       </c>
       <c r="W21">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>24.57975355069734</v>
+        <v>25.26388188014021</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3040,13 +3040,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.06765513620476972</v>
+        <v>0.06743001799388151</v>
       </c>
       <c r="C22">
-        <v>1291.278191223309</v>
+        <v>1295.821009996694</v>
       </c>
       <c r="D22">
-        <v>1539.99819122331</v>
+        <v>1544.541009996694</v>
       </c>
       <c r="E22">
         <v>-703.38</v>
@@ -3073,37 +3073,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M22">
-        <v>15.645454</v>
+        <v>15.221786</v>
       </c>
       <c r="N22">
-        <v>349.6878793333333</v>
+        <v>350.1115473333333</v>
       </c>
       <c r="O22">
-        <v>87.21215710573333</v>
+        <v>87.31781990493333</v>
       </c>
       <c r="P22">
-        <v>262.4757222275999</v>
+        <v>262.7937274284</v>
       </c>
       <c r="Q22">
-        <v>311.4757222275999</v>
+        <v>311.7937274284</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.07486741525596215</v>
+        <v>0.07484872749235189</v>
       </c>
       <c r="T22">
         <v>0.6708713046732538</v>
       </c>
       <c r="U22">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.2494</v>
       </c>
       <c r="W22">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>23.35076587316247</v>
+        <v>24.0006877861332</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3122,13 +3122,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.06752415642358978</v>
+        <v>0.06728856905598238</v>
       </c>
       <c r="C23">
-        <v>1278.950136956506</v>
+        <v>1283.735376877703</v>
       </c>
       <c r="D23">
-        <v>1542.801136956506</v>
+        <v>1547.586376877703</v>
       </c>
       <c r="E23">
         <v>-688.249</v>
@@ -3155,37 +3155,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M23">
-        <v>16.4277267</v>
+        <v>15.9828753</v>
       </c>
       <c r="N23">
-        <v>348.9056066333333</v>
+        <v>349.3504580333333</v>
       </c>
       <c r="O23">
-        <v>87.01705829435333</v>
+        <v>87.12800423351334</v>
       </c>
       <c r="P23">
-        <v>261.88854833898</v>
+        <v>262.22245379982</v>
       </c>
       <c r="Q23">
-        <v>310.88854833898</v>
+        <v>311.22245379982</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.07515809142226552</v>
+        <v>0.07513921677972452</v>
       </c>
       <c r="T23">
         <v>0.6775800641968709</v>
       </c>
       <c r="U23">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.2494</v>
       </c>
       <c r="W23">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.23882464110712</v>
+        <v>22.85779789155543</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3204,13 +3204,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.06739317664240982</v>
+        <v>0.06714712011808321</v>
       </c>
       <c r="C24">
-        <v>1266.632304559444</v>
+        <v>1271.661776565268</v>
       </c>
       <c r="D24">
-        <v>1545.614304559444</v>
+        <v>1550.643776565268</v>
       </c>
       <c r="E24">
         <v>-673.1179999999999</v>
@@ -3237,37 +3237,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M24">
-        <v>17.2099994</v>
+        <v>16.7439646</v>
       </c>
       <c r="N24">
-        <v>348.1233339333333</v>
+        <v>348.5893687333333</v>
       </c>
       <c r="O24">
-        <v>86.82195948297333</v>
+        <v>86.93818856209333</v>
       </c>
       <c r="P24">
-        <v>261.30137445036</v>
+        <v>261.65118017124</v>
       </c>
       <c r="Q24">
-        <v>310.30137445036</v>
+        <v>310.65118017124</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.07545622082360233</v>
+        <v>0.07543715451036309</v>
       </c>
       <c r="T24">
         <v>0.6844608431954525</v>
       </c>
       <c r="U24">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.22796897560224</v>
+        <v>21.8188070783029</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3286,13 +3286,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.06726219686122986</v>
+        <v>0.06700567118018406</v>
       </c>
       <c r="C25">
-        <v>1254.324750050418</v>
+        <v>1259.600280516318</v>
       </c>
       <c r="D25">
-        <v>1548.437750050418</v>
+        <v>1553.713280516318</v>
       </c>
       <c r="E25">
         <v>-657.9870000000001</v>
@@ -3319,37 +3319,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M25">
-        <v>17.9922721</v>
+        <v>17.5050539</v>
       </c>
       <c r="N25">
-        <v>347.3410612333333</v>
+        <v>347.8282794333333</v>
       </c>
       <c r="O25">
-        <v>86.62686067159333</v>
+        <v>86.74837289067334</v>
       </c>
       <c r="P25">
-        <v>260.71420056174</v>
+        <v>261.07990654266</v>
       </c>
       <c r="Q25">
-        <v>309.71420056174</v>
+        <v>310.07990654266</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.07576209384575307</v>
+        <v>0.07574283088335593</v>
       </c>
       <c r="T25">
         <v>0.6915203437264649</v>
       </c>
       <c r="U25">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V25">
         <v>0.2494</v>
       </c>
       <c r="W25">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.30501380274998</v>
+        <v>20.87016329228974</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3368,13 +3368,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.0671312170800499</v>
+        <v>0.06686422224228492</v>
       </c>
       <c r="C26">
-        <v>1242.027529857794</v>
+        <v>1247.550960754699</v>
       </c>
       <c r="D26">
-        <v>1551.271529857794</v>
+        <v>1556.794960754699</v>
       </c>
       <c r="E26">
         <v>-642.856</v>
@@ -3401,37 +3401,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M26">
-        <v>18.7745448</v>
+        <v>18.2661432</v>
       </c>
       <c r="N26">
-        <v>346.5587885333333</v>
+        <v>347.0671901333333</v>
       </c>
       <c r="O26">
-        <v>86.43176186021333</v>
+        <v>86.55855721925333</v>
       </c>
       <c r="P26">
-        <v>260.12702667312</v>
+        <v>260.50863291408</v>
       </c>
       <c r="Q26">
-        <v>309.12702667312</v>
+        <v>309.50863291408</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.0760760161579604</v>
+        <v>0.07605655137142751</v>
       </c>
       <c r="T26">
         <v>0.6987656205872406</v>
       </c>
       <c r="U26">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V26">
         <v>0.2494</v>
       </c>
       <c r="W26">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>19.45897156096873</v>
+        <v>20.000573155111</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3450,13 +3450,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.06700023729886996</v>
+        <v>0.06672277330438577</v>
       </c>
       <c r="C27">
-        <v>1229.740700823774</v>
+        <v>1235.513889876813</v>
       </c>
       <c r="D27">
-        <v>1554.115700823774</v>
+        <v>1559.888889876813</v>
       </c>
       <c r="E27">
         <v>-627.725</v>
@@ -3483,37 +3483,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M27">
-        <v>19.5568175</v>
+        <v>19.0272325</v>
       </c>
       <c r="N27">
-        <v>345.7765158333333</v>
+        <v>346.3061008333333</v>
       </c>
       <c r="O27">
-        <v>86.23666304883332</v>
+        <v>86.36874154783332</v>
       </c>
       <c r="P27">
-        <v>259.5398527845</v>
+        <v>259.9373592855</v>
       </c>
       <c r="Q27">
-        <v>308.5398527845</v>
+        <v>308.9373592855</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.07639830973182661</v>
+        <v>0.07637863773918102</v>
       </c>
       <c r="T27">
         <v>0.7062041048309704</v>
       </c>
       <c r="U27">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V27">
         <v>0.2494</v>
       </c>
       <c r="W27">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>18.68061269852998</v>
+        <v>19.20055022890656</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3532,13 +3532,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.06686925751769002</v>
+        <v>0.06658132436648662</v>
       </c>
       <c r="C28">
-        <v>1217.464320208192</v>
+        <v>1223.489141057312</v>
       </c>
       <c r="D28">
-        <v>1556.970320208192</v>
+        <v>1562.995141057311</v>
       </c>
       <c r="E28">
         <v>-612.5940000000001</v>
@@ -3565,37 +3565,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M28">
-        <v>20.3390902</v>
+        <v>19.7883218</v>
       </c>
       <c r="N28">
-        <v>344.9942431333333</v>
+        <v>345.5450115333333</v>
       </c>
       <c r="O28">
-        <v>86.04156423745333</v>
+        <v>86.17892587641333</v>
       </c>
       <c r="P28">
-        <v>258.95267889588</v>
+        <v>259.3660856569199</v>
       </c>
       <c r="Q28">
-        <v>307.95267889588</v>
+        <v>308.3660856569199</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.07672931394282434</v>
+        <v>0.07670942914390083</v>
       </c>
       <c r="T28">
         <v>0.7138436291893956</v>
       </c>
       <c r="U28">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V28">
         <v>0.2494</v>
       </c>
       <c r="W28">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>17.96212759474036</v>
+        <v>18.46206752779477</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3614,13 +3614,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.06673827773651005</v>
+        <v>0.06643987542858745</v>
       </c>
       <c r="C29">
-        <v>1205.198445692361</v>
+        <v>1211.476788054872</v>
       </c>
       <c r="D29">
-        <v>1559.835445692361</v>
+        <v>1566.113788054872</v>
       </c>
       <c r="E29">
         <v>-597.463</v>
@@ -3647,37 +3647,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M29">
-        <v>21.1213629</v>
+        <v>20.5494111</v>
       </c>
       <c r="N29">
-        <v>344.2119704333333</v>
+        <v>344.7839222333333</v>
       </c>
       <c r="O29">
-        <v>85.84646542607334</v>
+        <v>85.98911020499334</v>
       </c>
       <c r="P29">
-        <v>258.36550500726</v>
+        <v>258.79481202834</v>
       </c>
       <c r="Q29">
-        <v>307.36550500726</v>
+        <v>307.79481202834</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.07706938676234254</v>
+        <v>0.07704928332683214</v>
       </c>
       <c r="T29">
         <v>0.7216924555850378</v>
       </c>
       <c r="U29">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V29">
         <v>0.2494</v>
       </c>
       <c r="W29">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.29686360974998</v>
+        <v>17.77828724898756</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3696,13 +3696,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.0666072979553301</v>
+        <v>0.06629842649068832</v>
       </c>
       <c r="C30">
-        <v>1192.943135382952</v>
+        <v>1199.476905218028</v>
       </c>
       <c r="D30">
-        <v>1562.711135382952</v>
+        <v>1569.244905218027</v>
       </c>
       <c r="E30">
         <v>-582.332</v>
@@ -3729,37 +3729,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M30">
-        <v>21.9036356</v>
+        <v>21.3105004</v>
       </c>
       <c r="N30">
-        <v>343.4296977333333</v>
+        <v>344.0228329333333</v>
       </c>
       <c r="O30">
-        <v>85.65136661469333</v>
+        <v>85.79929453357333</v>
       </c>
       <c r="P30">
-        <v>257.7783311186399</v>
+        <v>258.2235383997599</v>
       </c>
       <c r="Q30">
-        <v>306.7783311186399</v>
+        <v>307.2235383997599</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.07741890604906959</v>
+        <v>0.07739857790373376</v>
       </c>
       <c r="T30">
         <v>0.7297593049361147</v>
       </c>
       <c r="U30">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>16.67911848083033</v>
+        <v>17.14334841866657</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3778,13 +3778,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.06647631817415016</v>
+        <v>0.06615697755278917</v>
       </c>
       <c r="C31">
-        <v>1180.698447815929</v>
+        <v>1187.489567491084</v>
       </c>
       <c r="D31">
-        <v>1565.597447815929</v>
+        <v>1572.388567491084</v>
       </c>
       <c r="E31">
         <v>-567.201</v>
@@ -3811,37 +3811,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M31">
-        <v>22.6859083</v>
+        <v>22.0715897</v>
       </c>
       <c r="N31">
-        <v>342.6474250333333</v>
+        <v>343.2617436333333</v>
       </c>
       <c r="O31">
-        <v>85.45626780331334</v>
+        <v>85.60947886215334</v>
       </c>
       <c r="P31">
-        <v>257.19115723002</v>
+        <v>257.6522647711799</v>
       </c>
       <c r="Q31">
-        <v>306.19115723002</v>
+        <v>306.6522647711799</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.07777827094950726</v>
+        <v>0.07775771176449178</v>
       </c>
       <c r="T31">
         <v>0.7380533894801796</v>
       </c>
       <c r="U31">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V31">
         <v>0.2494</v>
       </c>
       <c r="W31">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.10397646424998</v>
+        <v>16.55219847319531</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3860,13 +3860,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.0663453383929702</v>
+        <v>0.06601552861489002</v>
       </c>
       <c r="C32">
-        <v>1168.464441960517</v>
+        <v>1175.514850420093</v>
       </c>
       <c r="D32">
-        <v>1568.494441960516</v>
+        <v>1575.544850420093</v>
       </c>
       <c r="E32">
         <v>-552.0700000000001</v>
@@ -3893,37 +3893,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M32">
-        <v>23.468181</v>
+        <v>22.832679</v>
       </c>
       <c r="N32">
-        <v>341.8651523333333</v>
+        <v>342.5006543333333</v>
       </c>
       <c r="O32">
-        <v>85.26116899193333</v>
+        <v>85.41966319073333</v>
       </c>
       <c r="P32">
-        <v>256.6039833414</v>
+        <v>257.0809911426</v>
       </c>
       <c r="Q32">
-        <v>305.6039833414</v>
+        <v>306.0809911426</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.07814790341852887</v>
+        <v>0.07812710659270003</v>
       </c>
       <c r="T32">
         <v>0.7465844478683608</v>
       </c>
       <c r="U32">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V32">
         <v>0.2494</v>
       </c>
       <c r="W32">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>15.56717724877498</v>
+        <v>16.0004585240888</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3942,13 +3942,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.06621435861179024</v>
+        <v>0.06587407967699085</v>
       </c>
       <c r="C33">
-        <v>1156.241177223217</v>
+        <v>1163.552830158907</v>
       </c>
       <c r="D33">
-        <v>1571.402177223217</v>
+        <v>1578.713830158907</v>
       </c>
       <c r="E33">
         <v>-536.9390000000001</v>
@@ -3975,37 +3975,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M33">
-        <v>24.2504537</v>
+        <v>23.5937683</v>
       </c>
       <c r="N33">
-        <v>341.0828796333333</v>
+        <v>341.7395650333333</v>
       </c>
       <c r="O33">
-        <v>85.06607018055334</v>
+        <v>85.22984751931332</v>
       </c>
       <c r="P33">
-        <v>256.01680945278</v>
+        <v>256.5097175140199</v>
       </c>
       <c r="Q33">
-        <v>305.01680945278</v>
+        <v>305.5097175140199</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.07852824987215978</v>
+        <v>0.07850720851737805</v>
       </c>
       <c r="T33">
         <v>0.7553627833112716</v>
       </c>
       <c r="U33">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V33">
         <v>0.2494</v>
       </c>
       <c r="W33">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.06501024074998</v>
+        <v>15.48431470073109</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4024,13 +4024,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.0660833788306103</v>
+        <v>0.0657326307390917</v>
       </c>
       <c r="C34">
-        <v>1144.02871345187</v>
+        <v>1151.603583475301</v>
       </c>
       <c r="D34">
-        <v>1574.32071345187</v>
+        <v>1581.895583475301</v>
       </c>
       <c r="E34">
         <v>-521.808</v>
@@ -4057,37 +4057,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M34">
-        <v>25.0327264</v>
+        <v>24.3548576</v>
       </c>
       <c r="N34">
-        <v>340.3006069333333</v>
+        <v>340.9784757333333</v>
       </c>
       <c r="O34">
-        <v>84.87097136917333</v>
+        <v>85.04003184789333</v>
       </c>
       <c r="P34">
-        <v>255.42963556416</v>
+        <v>255.93844388544</v>
       </c>
       <c r="Q34">
-        <v>304.42963556416</v>
+        <v>304.93844388544</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.07891978298619162</v>
+        <v>0.07889848991042898</v>
       </c>
       <c r="T34">
         <v>0.7643993050907387</v>
       </c>
       <c r="U34">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V34">
         <v>0.2494</v>
       </c>
       <c r="W34">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>14.59422867072654</v>
+        <v>15.00042986633325</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4106,13 +4106,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.06595239904943034</v>
+        <v>0.06559118180119256</v>
       </c>
       <c r="C35">
-        <v>1131.827110939762</v>
+        <v>1139.667187757176</v>
       </c>
       <c r="D35">
-        <v>1577.250110939762</v>
+        <v>1585.090187757175</v>
       </c>
       <c r="E35">
         <v>-506.677</v>
@@ -4139,37 +4139,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M35">
-        <v>25.8149991</v>
+        <v>25.1159469</v>
       </c>
       <c r="N35">
-        <v>339.5183342333333</v>
+        <v>340.2173864333333</v>
       </c>
       <c r="O35">
-        <v>84.67587255779333</v>
+        <v>84.85021617647334</v>
       </c>
       <c r="P35">
-        <v>254.84246167554</v>
+        <v>255.36717025686</v>
       </c>
       <c r="Q35">
-        <v>303.84246167554</v>
+        <v>304.36717025686</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.0793230036558662</v>
+        <v>0.07930145134506353</v>
       </c>
       <c r="T35">
         <v>0.773705573788996</v>
       </c>
       <c r="U35">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V35">
         <v>0.2494</v>
       </c>
       <c r="W35">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.15197931706816</v>
+        <v>14.54587138553527</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4188,13 +4188,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.0658214192682504</v>
+        <v>0.06544973286329341</v>
       </c>
       <c r="C36">
-        <v>1119.636430429773</v>
+        <v>1127.743721018828</v>
       </c>
       <c r="D36">
-        <v>1580.190430429773</v>
+        <v>1588.297721018828</v>
       </c>
       <c r="E36">
         <v>-491.546</v>
@@ -4221,37 +4221,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M36">
-        <v>26.5972718</v>
+        <v>25.8770362</v>
       </c>
       <c r="N36">
-        <v>338.7360615333333</v>
+        <v>339.4562971333333</v>
       </c>
       <c r="O36">
-        <v>84.48077374641333</v>
+        <v>84.66040050505333</v>
       </c>
       <c r="P36">
-        <v>254.25528778692</v>
+        <v>254.79589662828</v>
       </c>
       <c r="Q36">
-        <v>303.25528778692</v>
+        <v>303.7958966282799</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.07973844313371273</v>
+        <v>0.07971662373226274</v>
       </c>
       <c r="T36">
         <v>0.7832938506296246</v>
       </c>
       <c r="U36">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V36">
         <v>0.2494</v>
       </c>
       <c r="W36">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>13.73574463127204</v>
+        <v>14.11805163890188</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4270,13 +4270,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.06569043948707043</v>
+        <v>0.06530828392539426</v>
       </c>
       <c r="C37">
-        <v>1107.456733118582</v>
+        <v>1115.833261907304</v>
       </c>
       <c r="D37">
-        <v>1583.141733118582</v>
+        <v>1591.518261907304</v>
       </c>
       <c r="E37">
         <v>-476.415</v>
@@ -4303,37 +4303,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M37">
-        <v>27.37954450000001</v>
+        <v>26.6381255</v>
       </c>
       <c r="N37">
-        <v>337.9537888333333</v>
+        <v>338.6952078333333</v>
       </c>
       <c r="O37">
-        <v>84.28567493503333</v>
+        <v>84.47058483363334</v>
       </c>
       <c r="P37">
-        <v>253.6681138983</v>
+        <v>254.2246229997</v>
       </c>
       <c r="Q37">
-        <v>302.6681138983</v>
+        <v>303.2246229997</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.08016666536472375</v>
+        <v>0.08014457065445271</v>
       </c>
       <c r="T37">
         <v>0.7931771513730418</v>
       </c>
       <c r="U37">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.34329478466427</v>
+        <v>13.71467873493325</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4352,13 +4352,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.0655594597058905</v>
+        <v>0.06516683498749512</v>
       </c>
       <c r="C38">
-        <v>1095.288080660903</v>
+        <v>1103.935889708828</v>
       </c>
       <c r="D38">
-        <v>1586.104080660903</v>
+        <v>1594.751889708828</v>
       </c>
       <c r="E38">
         <v>-461.2840000000001</v>
@@ -4385,37 +4385,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M38">
-        <v>28.1618172</v>
+        <v>27.3992148</v>
       </c>
       <c r="N38">
-        <v>337.1715161333333</v>
+        <v>337.9341185333333</v>
       </c>
       <c r="O38">
-        <v>84.09057612365332</v>
+        <v>84.28076916221333</v>
       </c>
       <c r="P38">
-        <v>253.08094000968</v>
+        <v>253.65334937112</v>
       </c>
       <c r="Q38">
-        <v>302.08094000968</v>
+        <v>302.65334937112</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.08060826954045389</v>
+        <v>0.08058589091796112</v>
       </c>
       <c r="T38">
         <v>0.8033693052646909</v>
       </c>
       <c r="U38">
-        <v>0.05170000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V38">
         <v>0.2494</v>
       </c>
       <c r="W38">
-        <v>0.03880602</v>
+        <v>0.03775518</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>12.97264770731248</v>
+        <v>13.33371543674067</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4434,13 +4434,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.06573397412471053</v>
+        <v>0.06502538604959596</v>
       </c>
       <c r="C39">
-        <v>1076.21256624775</v>
+        <v>1092.051684355303</v>
       </c>
       <c r="D39">
-        <v>1582.15956624775</v>
+        <v>1597.998684355303</v>
       </c>
       <c r="E39">
         <v>-446.153</v>
@@ -4467,45 +4467,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M39">
-        <v>29.5599216</v>
+        <v>28.1603041</v>
       </c>
       <c r="N39">
-        <v>335.7734117333333</v>
+        <v>337.1730292333333</v>
       </c>
       <c r="O39">
-        <v>83.74188888629334</v>
+        <v>84.09095349079332</v>
       </c>
       <c r="P39">
-        <v>252.03152284704</v>
+        <v>253.08207574254</v>
       </c>
       <c r="Q39">
-        <v>301.03152284704</v>
+        <v>302.08207574254</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.08106389289636592</v>
+        <v>0.08104122134856501</v>
       </c>
       <c r="T39">
         <v>0.8138850195973445</v>
       </c>
       <c r="U39">
-        <v>0.05280000000000001</v>
+        <v>0.0503</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.03963168</v>
+        <v>0.03775518</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y39">
-        <v>12.35907653196662</v>
+        <v>12.97334474926119</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4516,13 +4516,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.06561125094353058</v>
+        <v>0.0653117791116968</v>
       </c>
       <c r="C40">
-        <v>1063.85340284295</v>
+        <v>1070.360525362837</v>
       </c>
       <c r="D40">
-        <v>1584.93140284295</v>
+        <v>1591.438525362837</v>
       </c>
       <c r="E40">
         <v>-431.022</v>
@@ -4549,37 +4549,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M40">
-        <v>30.3588384</v>
+        <v>29.7838604</v>
       </c>
       <c r="N40">
-        <v>334.9744949333333</v>
+        <v>335.5494729333333</v>
       </c>
       <c r="O40">
-        <v>83.54263903637333</v>
+        <v>83.68603854957334</v>
       </c>
       <c r="P40">
-        <v>251.43185589696</v>
+        <v>251.86343438376</v>
       </c>
       <c r="Q40">
-        <v>300.43185589696</v>
+        <v>300.86343438376</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.08153421377988804</v>
+        <v>0.0815112398575755</v>
       </c>
       <c r="T40">
         <v>0.8247399505213742</v>
       </c>
       <c r="U40">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V40">
         <v>0.2494</v>
       </c>
       <c r="W40">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.03383767586224</v>
+        <v>12.26615114450823</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4598,13 +4598,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.06548852776235065</v>
+        <v>0.06518158917379765</v>
       </c>
       <c r="C41">
-        <v>1051.503968623664</v>
+        <v>1058.204984356567</v>
       </c>
       <c r="D41">
-        <v>1587.712968623664</v>
+        <v>1594.413984356567</v>
       </c>
       <c r="E41">
         <v>-415.891</v>
@@ -4631,37 +4631,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M41">
-        <v>31.15775520000001</v>
+        <v>30.56764620000001</v>
       </c>
       <c r="N41">
-        <v>334.1755781333333</v>
+        <v>334.7656871333333</v>
       </c>
       <c r="O41">
-        <v>83.34338918645334</v>
+        <v>83.49056237105333</v>
       </c>
       <c r="P41">
-        <v>250.83218894688</v>
+        <v>251.27512476228</v>
       </c>
       <c r="Q41">
-        <v>299.83218894688</v>
+        <v>300.27512476228</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.08201995502024695</v>
+        <v>0.08199666880950436</v>
       </c>
       <c r="T41">
         <v>0.8359507808199622</v>
       </c>
       <c r="U41">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V41">
         <v>0.2494</v>
       </c>
       <c r="W41">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.72527773545551</v>
+        <v>11.9516344484952</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4680,13 +4680,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.06536580458117069</v>
+        <v>0.0650513992358985</v>
       </c>
       <c r="C42">
-        <v>1039.164314904318</v>
+        <v>1046.060590422471</v>
       </c>
       <c r="D42">
-        <v>1590.504314904317</v>
+        <v>1597.400590422471</v>
       </c>
       <c r="E42">
         <v>-400.76</v>
@@ -4713,37 +4713,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M42">
-        <v>31.956672</v>
+        <v>31.351432</v>
       </c>
       <c r="N42">
-        <v>333.3766613333333</v>
+        <v>333.9819013333333</v>
       </c>
       <c r="O42">
-        <v>83.14413933653333</v>
+        <v>83.29508619253333</v>
       </c>
       <c r="P42">
-        <v>250.2325219968</v>
+        <v>250.6868151408</v>
       </c>
       <c r="Q42">
-        <v>299.2325219968</v>
+        <v>299.6868151408</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.08252188763528448</v>
+        <v>0.08249827872649751</v>
       </c>
       <c r="T42">
         <v>0.8475353054618364</v>
       </c>
       <c r="U42">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V42">
         <v>0.2494</v>
       </c>
       <c r="W42">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.43214579206913</v>
+        <v>11.65284358728282</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4762,13 +4762,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.06524308139999074</v>
+        <v>0.06492120929799937</v>
       </c>
       <c r="C43">
-        <v>1026.834493360832</v>
+        <v>1033.92740631914</v>
       </c>
       <c r="D43">
-        <v>1593.305493360832</v>
+        <v>1600.39840631914</v>
       </c>
       <c r="E43">
         <v>-385.629</v>
@@ -4795,37 +4795,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M43">
-        <v>32.75558880000001</v>
+        <v>32.1352178</v>
       </c>
       <c r="N43">
-        <v>332.5777445333333</v>
+        <v>333.1981155333333</v>
       </c>
       <c r="O43">
-        <v>82.94488948661333</v>
+        <v>83.09961001401332</v>
       </c>
       <c r="P43">
-        <v>249.63285504672</v>
+        <v>250.09850551932</v>
       </c>
       <c r="Q43">
-        <v>298.63285504672</v>
+        <v>299.09850551932</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.08304083491523853</v>
+        <v>0.08301689236949045</v>
       </c>
       <c r="T43">
         <v>0.8595125258542828</v>
       </c>
       <c r="U43">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V43">
         <v>0.2494</v>
       </c>
       <c r="W43">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.15331296787232</v>
+        <v>11.36862789003202</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4844,13 +4844,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.06512035821881079</v>
+        <v>0.06479101936010022</v>
       </c>
       <c r="C44">
-        <v>1014.514556033816</v>
+        <v>1021.805495277164</v>
       </c>
       <c r="D44">
-        <v>1596.116556033816</v>
+        <v>1603.407495277163</v>
       </c>
       <c r="E44">
         <v>-370.498</v>
@@ -4877,37 +4877,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M44">
-        <v>33.5545056</v>
+        <v>32.9190036</v>
       </c>
       <c r="N44">
-        <v>331.7788277333333</v>
+        <v>332.4143297333333</v>
       </c>
       <c r="O44">
-        <v>82.74563963669333</v>
+        <v>82.90413383549333</v>
       </c>
       <c r="P44">
-        <v>249.0331880966399</v>
+        <v>249.51019589784</v>
       </c>
       <c r="Q44">
-        <v>298.0331880966399</v>
+        <v>298.51019589784</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.0835776769289841</v>
+        <v>0.08355338924155209</v>
       </c>
       <c r="T44">
         <v>0.8719027538464684</v>
       </c>
       <c r="U44">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V44">
         <v>0.2494</v>
       </c>
       <c r="W44">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>10.88775789720869</v>
+        <v>11.09794627360268</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4926,13 +4926,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.06499763503763083</v>
+        <v>0.06466082942220105</v>
       </c>
       <c r="C45">
-        <v>1002.204555331789</v>
+        <v>1009.694921003574</v>
       </c>
       <c r="D45">
-        <v>1598.937555331789</v>
+        <v>1606.427921003574</v>
       </c>
       <c r="E45">
         <v>-355.3670000000001</v>
@@ -4959,37 +4959,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M45">
-        <v>34.3534224</v>
+        <v>33.7027894</v>
       </c>
       <c r="N45">
-        <v>330.9799109333333</v>
+        <v>331.6305439333333</v>
       </c>
       <c r="O45">
-        <v>82.54638978677333</v>
+        <v>82.70865765697334</v>
       </c>
       <c r="P45">
-        <v>248.43352114656</v>
+        <v>248.92188627636</v>
       </c>
       <c r="Q45">
-        <v>297.43352114656</v>
+        <v>297.92188627636</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.08413335550461548</v>
+        <v>0.084108710565265</v>
       </c>
       <c r="T45">
         <v>0.8847277266804853</v>
       </c>
       <c r="U45">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.63455422518058</v>
+        <v>10.83985449979797</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5008,13 +5008,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.06487491185645089</v>
+        <v>0.0645306394843019</v>
       </c>
       <c r="C46">
-        <v>989.9045440344327</v>
+        <v>997.595747686344</v>
       </c>
       <c r="D46">
-        <v>1601.768544034433</v>
+        <v>1609.459747686344</v>
       </c>
       <c r="E46">
         <v>-340.236</v>
@@ -5041,37 +5041,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M46">
-        <v>35.15233920000001</v>
+        <v>34.4865752</v>
       </c>
       <c r="N46">
-        <v>330.1809941333333</v>
+        <v>330.8467581333333</v>
       </c>
       <c r="O46">
-        <v>82.34713993685332</v>
+        <v>82.51318147845333</v>
       </c>
       <c r="P46">
-        <v>247.83385419648</v>
+        <v>248.33357665488</v>
       </c>
       <c r="Q46">
-        <v>296.8338541964799</v>
+        <v>297.3335766548799</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.08470887974366229</v>
+        <v>0.08468386479339626</v>
       </c>
       <c r="T46">
         <v>0.8980107342585743</v>
       </c>
       <c r="U46">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V46">
         <v>0.2494</v>
       </c>
       <c r="W46">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.39285981097193</v>
+        <v>10.59349417025711</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5090,13 +5090,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.06475218867527094</v>
+        <v>0.06440044954640275</v>
       </c>
       <c r="C47">
-        <v>977.6145752958907</v>
+        <v>985.5080399989311</v>
       </c>
       <c r="D47">
-        <v>1604.609575295891</v>
+        <v>1612.503039998931</v>
       </c>
       <c r="E47">
         <v>-325.105</v>
@@ -5123,37 +5123,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M47">
-        <v>35.951256</v>
+        <v>35.270361</v>
       </c>
       <c r="N47">
-        <v>329.3820773333333</v>
+        <v>330.0629723333333</v>
       </c>
       <c r="O47">
-        <v>82.14789008693333</v>
+        <v>82.31770529993334</v>
       </c>
       <c r="P47">
-        <v>247.2341872464</v>
+        <v>247.7452670334</v>
       </c>
       <c r="Q47">
-        <v>296.2341872464</v>
+        <v>296.7452670334</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.08530533213685623</v>
+        <v>0.08527993372073228</v>
       </c>
       <c r="T47">
         <v>0.9117767602940483</v>
       </c>
       <c r="U47">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V47">
         <v>0.2494</v>
       </c>
       <c r="W47">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.16190737072811</v>
+        <v>10.35808318869584</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5172,13 +5172,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.06462946549409097</v>
+        <v>0.0642702596085036</v>
       </c>
       <c r="C48">
-        <v>965.3347026480905</v>
+        <v>973.4318631048801</v>
       </c>
       <c r="D48">
-        <v>1607.46070264809</v>
+        <v>1615.55786310488</v>
       </c>
       <c r="E48">
         <v>-309.974</v>
@@ -5205,37 +5205,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M48">
-        <v>36.7501728</v>
+        <v>36.05414680000001</v>
       </c>
       <c r="N48">
-        <v>328.5831605333333</v>
+        <v>329.2791865333333</v>
       </c>
       <c r="O48">
-        <v>81.94864023701332</v>
+        <v>82.12222912141333</v>
       </c>
       <c r="P48">
-        <v>246.63452029632</v>
+        <v>247.15695741192</v>
       </c>
       <c r="Q48">
-        <v>295.63452029632</v>
+        <v>296.15695741192</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.08592387535942772</v>
+        <v>0.08589807927500669</v>
       </c>
       <c r="T48">
         <v>0.9260526391456509</v>
       </c>
       <c r="U48">
-        <v>0.05280000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V48">
         <v>0.2494</v>
       </c>
       <c r="W48">
-        <v>0.03963168</v>
+        <v>0.03888108</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>9.940996340929676</v>
+        <v>10.13290746720245</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5254,13 +5254,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.06528286271291103</v>
+        <v>0.06414006967060445</v>
       </c>
       <c r="C49">
-        <v>935.1393976258895</v>
+        <v>961.367282662471</v>
       </c>
       <c r="D49">
-        <v>1592.396397625889</v>
+        <v>1618.624282662471</v>
       </c>
       <c r="E49">
         <v>-294.843</v>
@@ -5287,45 +5287,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M49">
-        <v>39.11363500000001</v>
+        <v>36.83793260000001</v>
       </c>
       <c r="N49">
-        <v>326.2196983333333</v>
+        <v>328.4954007333333</v>
       </c>
       <c r="O49">
-        <v>81.35919276433333</v>
+        <v>81.92675294289333</v>
       </c>
       <c r="P49">
-        <v>244.860505569</v>
+        <v>246.56864779044</v>
       </c>
       <c r="Q49">
-        <v>293.860505569</v>
+        <v>295.56864779044</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.08656575983568118</v>
+        <v>0.08653955107661218</v>
       </c>
       <c r="T49">
         <v>0.940867230406748</v>
       </c>
       <c r="U49">
-        <v>0.05500000000000001</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.041283</v>
+        <v>0.03888108</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y49">
-        <v>9.340306349264988</v>
+        <v>9.917313691304523</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5336,13 +5336,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.06517665273173107</v>
+        <v>0.06462236933270532</v>
       </c>
       <c r="C50">
-        <v>922.4378593172192</v>
+        <v>934.9343793347556</v>
       </c>
       <c r="D50">
-        <v>1594.825859317219</v>
+        <v>1607.322379334755</v>
       </c>
       <c r="E50">
         <v>-279.7120000000001</v>
@@ -5369,37 +5369,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M50">
-        <v>39.94584</v>
+        <v>38.856408</v>
       </c>
       <c r="N50">
-        <v>325.3874933333333</v>
+        <v>326.4769253333333</v>
       </c>
       <c r="O50">
-        <v>81.15164083733333</v>
+        <v>81.42334517813333</v>
       </c>
       <c r="P50">
-        <v>244.235852496</v>
+        <v>245.0535801552</v>
       </c>
       <c r="Q50">
-        <v>293.235852496</v>
+        <v>294.0535801552</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.0872323321764059</v>
+        <v>0.08720569487058713</v>
       </c>
       <c r="T50">
         <v>0.9562516136394256</v>
       </c>
       <c r="U50">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V50">
         <v>0.2494</v>
       </c>
       <c r="W50">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.145716633655303</v>
+        <v>9.402138595346573</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5418,13 +5418,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.06507044275055111</v>
+        <v>0.06450493959480616</v>
       </c>
       <c r="C51">
-        <v>909.7437454196803</v>
+        <v>922.5405925075762</v>
       </c>
       <c r="D51">
-        <v>1597.26274541968</v>
+        <v>1610.059592507576</v>
       </c>
       <c r="E51">
         <v>-264.581</v>
@@ -5451,37 +5451,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M51">
-        <v>40.77804500000001</v>
+        <v>39.6659165</v>
       </c>
       <c r="N51">
-        <v>324.5552883333333</v>
+        <v>325.6674168333333</v>
       </c>
       <c r="O51">
-        <v>80.94408891033332</v>
+        <v>81.22145375823334</v>
       </c>
       <c r="P51">
-        <v>243.611199423</v>
+        <v>244.4459630751</v>
       </c>
       <c r="Q51">
-        <v>292.611199423</v>
+        <v>293.4459630751</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.08792504460892375</v>
+        <v>0.08789796195060032</v>
       </c>
       <c r="T51">
         <v>0.972239306018483</v>
       </c>
       <c r="U51">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V51">
         <v>0.2494</v>
       </c>
       <c r="W51">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>8.959069355417437</v>
+        <v>9.210258215849704</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5500,13 +5500,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.06496423276937116</v>
+        <v>0.06438750985690701</v>
       </c>
       <c r="C52">
-        <v>897.0570900187483</v>
+        <v>910.1561443382768</v>
       </c>
       <c r="D52">
-        <v>1599.707090018748</v>
+        <v>1612.806144338277</v>
       </c>
       <c r="E52">
         <v>-249.45</v>
@@ -5533,37 +5533,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M52">
-        <v>41.61025</v>
+        <v>40.475425</v>
       </c>
       <c r="N52">
-        <v>323.7230833333333</v>
+        <v>324.8579083333333</v>
       </c>
       <c r="O52">
-        <v>80.73653698333332</v>
+        <v>81.01956233833333</v>
       </c>
       <c r="P52">
-        <v>242.98654635</v>
+        <v>243.8383459949999</v>
       </c>
       <c r="Q52">
-        <v>291.98654635</v>
+        <v>292.8383459949999</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.08864546553874234</v>
+        <v>0.08861791971381403</v>
       </c>
       <c r="T52">
         <v>0.9888665060927025</v>
       </c>
       <c r="U52">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V52">
         <v>0.2494</v>
       </c>
       <c r="W52">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>8.77988796830909</v>
+        <v>9.026053051532708</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5582,13 +5582,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.06485802278819121</v>
+        <v>0.06427008011900787</v>
       </c>
       <c r="C53">
-        <v>884.3779274088648</v>
+        <v>897.7810827001236</v>
       </c>
       <c r="D53">
-        <v>1602.158927408865</v>
+        <v>1615.562082700123</v>
       </c>
       <c r="E53">
         <v>-234.3190000000001</v>
@@ -5615,37 +5615,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M53">
-        <v>42.442455</v>
+        <v>41.2849335</v>
       </c>
       <c r="N53">
-        <v>322.8908783333333</v>
+        <v>324.0483998333333</v>
       </c>
       <c r="O53">
-        <v>80.52898505633334</v>
+        <v>80.81767091843332</v>
       </c>
       <c r="P53">
-        <v>242.361893277</v>
+        <v>243.2307289149</v>
       </c>
       <c r="Q53">
-        <v>291.361893277</v>
+        <v>292.2307289148999</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.08939529140447186</v>
+        <v>0.08936726350817931</v>
       </c>
       <c r="T53">
         <v>1.006172367394441</v>
       </c>
       <c r="U53">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V53">
         <v>0.2494</v>
       </c>
       <c r="W53">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.607733302263814</v>
+        <v>8.849071619149715</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5664,13 +5664,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.06475181280701127</v>
+        <v>0.06415265038110871</v>
       </c>
       <c r="C54">
-        <v>871.7062920950444</v>
+        <v>885.4154557941621</v>
       </c>
       <c r="D54">
-        <v>1604.618292095044</v>
+        <v>1618.327455794162</v>
       </c>
       <c r="E54">
         <v>-219.188</v>
@@ -5697,37 +5697,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M54">
-        <v>43.27466</v>
+        <v>42.09444200000001</v>
       </c>
       <c r="N54">
-        <v>322.0586733333333</v>
+        <v>323.2388913333333</v>
       </c>
       <c r="O54">
-        <v>80.32143312933334</v>
+        <v>80.61577949853333</v>
       </c>
       <c r="P54">
-        <v>241.737240204</v>
+        <v>242.6231118348</v>
       </c>
       <c r="Q54">
-        <v>290.737240204</v>
+        <v>291.6231118347999</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.0901763600146068</v>
+        <v>0.09014782996064315</v>
       </c>
       <c r="T54">
         <v>1.024199306250419</v>
       </c>
       <c r="U54">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V54">
         <v>0.2494</v>
       </c>
       <c r="W54">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.442199969527971</v>
+        <v>8.678897164935297</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5746,13 +5746,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.06464560282583132</v>
+        <v>0.06403522064320956</v>
       </c>
       <c r="C55">
-        <v>859.0422187944928</v>
+        <v>873.0593121520287</v>
       </c>
       <c r="D55">
-        <v>1607.085218794493</v>
+        <v>1621.102312152029</v>
       </c>
       <c r="E55">
         <v>-204.057</v>
@@ -5779,37 +5779,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M55">
-        <v>44.10686500000001</v>
+        <v>42.9039505</v>
       </c>
       <c r="N55">
-        <v>321.2264683333333</v>
+        <v>322.4293828333333</v>
       </c>
       <c r="O55">
-        <v>80.11388120233333</v>
+        <v>80.41388807863333</v>
       </c>
       <c r="P55">
-        <v>241.1125871309999</v>
+        <v>242.0154947547</v>
       </c>
       <c r="Q55">
-        <v>290.1125871309999</v>
+        <v>291.0154947546999</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.09099066558687513</v>
+        <v>0.09096161200682885</v>
       </c>
       <c r="T55">
         <v>1.042993348887503</v>
       </c>
       <c r="U55">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V55">
         <v>0.2494</v>
       </c>
       <c r="W55">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.282913177650084</v>
+        <v>8.515144388238404</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5828,13 +5828,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.06453939284465136</v>
+        <v>0.06391779090531041</v>
       </c>
       <c r="C56">
-        <v>846.3857424382396</v>
+        <v>860.7127006387897</v>
       </c>
       <c r="D56">
-        <v>1609.559742438239</v>
+        <v>1623.88670063879</v>
       </c>
       <c r="E56">
         <v>-188.926</v>
@@ -5861,37 +5861,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M56">
-        <v>44.93907</v>
+        <v>43.713459</v>
       </c>
       <c r="N56">
-        <v>320.3942633333333</v>
+        <v>321.6198743333333</v>
       </c>
       <c r="O56">
-        <v>79.90632927533333</v>
+        <v>80.21199665873333</v>
       </c>
       <c r="P56">
-        <v>240.487934058</v>
+        <v>241.4078776746</v>
       </c>
       <c r="Q56">
-        <v>289.487934058</v>
+        <v>290.4078776746</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.09184037574924209</v>
+        <v>0.09181077588110959</v>
       </c>
       <c r="T56">
         <v>1.062604523813155</v>
       </c>
       <c r="U56">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V56">
         <v>0.2494</v>
       </c>
       <c r="W56">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.129525896582489</v>
+        <v>8.357456529196952</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5910,13 +5910,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.06443318286347141</v>
+        <v>0.06380036116741125</v>
       </c>
       <c r="C57">
-        <v>833.7368981727888</v>
+        <v>848.3756704558099</v>
       </c>
       <c r="D57">
-        <v>1612.041898172789</v>
+        <v>1626.68067045581</v>
       </c>
       <c r="E57">
         <v>-173.795</v>
@@ -5943,37 +5943,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M57">
-        <v>45.77127500000001</v>
+        <v>44.52296750000001</v>
       </c>
       <c r="N57">
-        <v>319.5620583333333</v>
+        <v>320.8103658333333</v>
       </c>
       <c r="O57">
-        <v>79.69877734833334</v>
+        <v>80.01010523883333</v>
       </c>
       <c r="P57">
-        <v>239.863280985</v>
+        <v>240.8002605945</v>
       </c>
       <c r="Q57">
-        <v>288.863280985</v>
+        <v>289.8002605945</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.09272785080771424</v>
+        <v>0.09269768037202503</v>
       </c>
       <c r="T57">
         <v>1.08308730651328</v>
       </c>
       <c r="U57">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V57">
         <v>0.2494</v>
       </c>
       <c r="W57">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>7.981716334826443</v>
+        <v>8.205502774120644</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5992,13 +5992,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06432697288229144</v>
+        <v>0.0636829314295121</v>
       </c>
       <c r="C58">
-        <v>821.0957213617801</v>
+        <v>836.0482711436491</v>
       </c>
       <c r="D58">
-        <v>1614.53172136178</v>
+        <v>1629.484271143649</v>
       </c>
       <c r="E58">
         <v>-158.664</v>
@@ -6025,37 +6025,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M58">
-        <v>46.60348</v>
+        <v>45.33247600000001</v>
       </c>
       <c r="N58">
-        <v>318.7298533333333</v>
+        <v>320.0008573333333</v>
       </c>
       <c r="O58">
-        <v>79.49122542133334</v>
+        <v>79.80821381893334</v>
       </c>
       <c r="P58">
-        <v>239.238627912</v>
+        <v>240.1926435144</v>
       </c>
       <c r="Q58">
-        <v>288.238627912</v>
+        <v>289.1926435144</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.09365566564157149</v>
+        <v>0.09362489870343661</v>
       </c>
       <c r="T58">
         <v>1.104501124790684</v>
       </c>
       <c r="U58">
-        <v>0.05500000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V58">
         <v>0.2494</v>
       </c>
       <c r="W58">
-        <v>0.041283</v>
+        <v>0.0401571</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>7.839185685990259</v>
+        <v>8.058975938868489</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6074,13 +6074,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.0648625259011115</v>
+        <v>0.06356550169161296</v>
       </c>
       <c r="C59">
-        <v>793.4878213338891</v>
+        <v>823.7305525849927</v>
       </c>
       <c r="D59">
-        <v>1602.054821333889</v>
+        <v>1632.297552584993</v>
       </c>
       <c r="E59">
         <v>-143.5329999999999</v>
@@ -6107,45 +6107,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M59">
-        <v>48.72938550000001</v>
+        <v>46.14198450000001</v>
       </c>
       <c r="N59">
-        <v>316.6039478333333</v>
+        <v>319.1913488333333</v>
       </c>
       <c r="O59">
-        <v>78.96102458963333</v>
+        <v>79.60632239903332</v>
       </c>
       <c r="P59">
-        <v>237.6429232437</v>
+        <v>239.5850264342999</v>
       </c>
       <c r="Q59">
-        <v>286.6429232437</v>
+        <v>288.5850264342999</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.09462663465374768</v>
+        <v>0.09459524346886736</v>
       </c>
       <c r="T59">
         <v>1.126910934615874</v>
       </c>
       <c r="U59">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V59">
         <v>0.2494</v>
       </c>
       <c r="W59">
-        <v>0.0424089</v>
+        <v>0.0401571</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>7.497187366200897</v>
+        <v>7.917590396081321</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6156,13 +6156,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.06476757491993156</v>
+        <v>0.0634480719537138</v>
       </c>
       <c r="C60">
-        <v>780.554832594746</v>
+        <v>811.4225650076086</v>
       </c>
       <c r="D60">
-        <v>1604.252832594746</v>
+        <v>1635.120565007608</v>
       </c>
       <c r="E60">
         <v>-128.4020000000002</v>
@@ -6189,45 +6189,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M60">
-        <v>49.584287</v>
+        <v>46.951493</v>
       </c>
       <c r="N60">
-        <v>315.7490463333333</v>
+        <v>318.3818403333333</v>
       </c>
       <c r="O60">
-        <v>78.74781215553332</v>
+        <v>79.40443097913334</v>
       </c>
       <c r="P60">
-        <v>237.0012341778</v>
+        <v>238.9774093542</v>
       </c>
       <c r="Q60">
-        <v>286.0012341778</v>
+        <v>287.9774093542</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.09564384028555131</v>
+        <v>0.09561179512789</v>
       </c>
       <c r="T60">
         <v>1.150387878242264</v>
       </c>
       <c r="U60">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.0424089</v>
+        <v>0.0401571</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>7.367925515059505</v>
+        <v>7.781080216838543</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6238,13 +6238,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0646726239387516</v>
+        <v>0.06333064221581466</v>
       </c>
       <c r="C61">
-        <v>767.6278834629876</v>
+        <v>799.1243589873353</v>
       </c>
       <c r="D61">
-        <v>1606.456883462987</v>
+        <v>1637.953358987335</v>
       </c>
       <c r="E61">
         <v>-113.2710000000001</v>
@@ -6271,45 +6271,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M61">
-        <v>50.4391885</v>
+        <v>47.7610015</v>
       </c>
       <c r="N61">
-        <v>314.8941448333333</v>
+        <v>317.5723318333333</v>
       </c>
       <c r="O61">
-        <v>78.53459972143334</v>
+        <v>79.20253955923333</v>
       </c>
       <c r="P61">
-        <v>236.3595451119</v>
+        <v>238.3697922741</v>
       </c>
       <c r="Q61">
-        <v>285.3595451119</v>
+        <v>287.3697922741</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.0967106657042722</v>
+        <v>0.09667793467271868</v>
       </c>
       <c r="T61">
         <v>1.175010038630916</v>
       </c>
       <c r="U61">
-        <v>0.05650000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.0424089</v>
+        <v>0.0401571</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>7.24304542158392</v>
+        <v>7.649197501298906</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6320,13 +6320,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.06457767295757165</v>
+        <v>0.0635735004779155</v>
       </c>
       <c r="C62">
-        <v>754.7069988659496</v>
+        <v>778.1456162178611</v>
       </c>
       <c r="D62">
-        <v>1608.666998865949</v>
+        <v>1632.105616217861</v>
       </c>
       <c r="E62">
         <v>-98.1400000000001</v>
@@ -6353,37 +6353,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M62">
-        <v>51.29409</v>
+        <v>49.296798</v>
       </c>
       <c r="N62">
-        <v>314.0392433333333</v>
+        <v>316.0365353333333</v>
       </c>
       <c r="O62">
-        <v>78.32138728733334</v>
+        <v>78.81951191213332</v>
       </c>
       <c r="P62">
-        <v>235.717856046</v>
+        <v>237.2170234212</v>
       </c>
       <c r="Q62">
-        <v>284.717856046</v>
+        <v>286.2170234212</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.09783083239392912</v>
+        <v>0.09779738119478876</v>
       </c>
       <c r="T62">
         <v>1.200863307039002</v>
       </c>
       <c r="U62">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V62">
         <v>0.2494</v>
       </c>
       <c r="W62">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.122327997890855</v>
+        <v>7.410893773127684</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6402,13 +6402,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.0644827219763917</v>
+        <v>0.06346207554001636</v>
       </c>
       <c r="C63">
-        <v>741.7922038683317</v>
+        <v>765.6924059267664</v>
       </c>
       <c r="D63">
-        <v>1610.883203868332</v>
+        <v>1634.783405926766</v>
       </c>
       <c r="E63">
         <v>-83.00900000000013</v>
@@ -6435,37 +6435,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M63">
-        <v>52.1489915</v>
+        <v>50.1184113</v>
       </c>
       <c r="N63">
-        <v>313.1843418333333</v>
+        <v>315.2149220333333</v>
       </c>
       <c r="O63">
-        <v>78.10817485323332</v>
+        <v>78.61460155511334</v>
       </c>
       <c r="P63">
-        <v>235.0761669801</v>
+        <v>236.60032047822</v>
       </c>
       <c r="Q63">
-        <v>284.0761669801</v>
+        <v>285.60032047822</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.09900844352920948</v>
+        <v>0.09897423523081117</v>
       </c>
       <c r="T63">
         <v>1.228042384083399</v>
       </c>
       <c r="U63">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V63">
         <v>0.2494</v>
       </c>
       <c r="W63">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.005568522515595</v>
+        <v>7.289403711273133</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6484,13 +6484,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.06438777099521176</v>
+        <v>0.06335065060211721</v>
       </c>
       <c r="C64">
-        <v>728.8835236731476</v>
+        <v>753.2479969555069</v>
       </c>
       <c r="D64">
-        <v>1613.105523673147</v>
+        <v>1637.469996955507</v>
       </c>
       <c r="E64">
         <v>-67.87800000000004</v>
@@ -6517,37 +6517,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M64">
-        <v>53.00389300000001</v>
+        <v>50.94002460000001</v>
       </c>
       <c r="N64">
-        <v>312.3294403333333</v>
+        <v>314.3933087333333</v>
       </c>
       <c r="O64">
-        <v>77.89496241913334</v>
+        <v>78.40969119809333</v>
       </c>
       <c r="P64">
-        <v>234.4344779142</v>
+        <v>235.98361753524</v>
       </c>
       <c r="Q64">
-        <v>283.4344779142</v>
+        <v>284.98361753524</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1002480341979257</v>
+        <v>0.10021302895294</v>
       </c>
       <c r="T64">
         <v>1.256651938866975</v>
       </c>
       <c r="U64">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V64">
         <v>0.2494</v>
       </c>
       <c r="W64">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>6.892575481829859</v>
+        <v>7.171832683671952</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6566,13 +6566,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.06429282001403179</v>
+        <v>0.06323922566421807</v>
       </c>
       <c r="C65">
-        <v>715.9809836226823</v>
+        <v>740.8124327675839</v>
       </c>
       <c r="D65">
-        <v>1615.333983622682</v>
+        <v>1640.165432767584</v>
       </c>
       <c r="E65">
         <v>-52.74700000000007</v>
@@ -6599,37 +6599,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M65">
-        <v>53.8587945</v>
+        <v>51.7616379</v>
       </c>
       <c r="N65">
-        <v>311.4745388333333</v>
+        <v>313.5716954333333</v>
       </c>
       <c r="O65">
-        <v>77.68174998503333</v>
+        <v>78.20478084107333</v>
       </c>
       <c r="P65">
-        <v>233.7927888483</v>
+        <v>235.36691459226</v>
       </c>
       <c r="Q65">
-        <v>282.7927888483</v>
+        <v>284.36691459226</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1015546297676535</v>
+        <v>0.1015187844978866</v>
       </c>
       <c r="T65">
         <v>1.286807956071285</v>
       </c>
       <c r="U65">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V65">
         <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>6.783169521800814</v>
+        <v>7.057994069645414</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6648,13 +6648,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.06419786903285185</v>
+        <v>0.06312780072631891</v>
       </c>
       <c r="C66">
-        <v>703.084609199449</v>
+        <v>728.3857571131502</v>
       </c>
       <c r="D66">
-        <v>1617.568609199449</v>
+        <v>1642.86975711315</v>
       </c>
       <c r="E66">
         <v>-37.61599999999999</v>
@@ -6681,37 +6681,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M66">
-        <v>54.71369600000001</v>
+        <v>52.58325120000001</v>
       </c>
       <c r="N66">
-        <v>310.6196373333333</v>
+        <v>312.7500821333333</v>
       </c>
       <c r="O66">
-        <v>77.46853755093332</v>
+        <v>77.99987048405333</v>
       </c>
       <c r="P66">
-        <v>233.1510997824</v>
+        <v>234.75021164928</v>
       </c>
       <c r="Q66">
-        <v>282.1510997824</v>
+        <v>283.75021164928</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.102933813980144</v>
+        <v>0.1028970820175525</v>
       </c>
       <c r="T66">
         <v>1.318639307564723</v>
       </c>
       <c r="U66">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V66">
         <v>0.2494</v>
       </c>
       <c r="W66">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.677182498022675</v>
+        <v>6.947712912307204</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6730,13 +6730,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.0641029180516719</v>
+        <v>0.06301637578841976</v>
       </c>
       <c r="C67">
-        <v>690.1944260271688</v>
+        <v>715.9680140313784</v>
       </c>
       <c r="D67">
-        <v>1619.809426027169</v>
+        <v>1645.583014031378</v>
       </c>
       <c r="E67">
         <v>-22.48500000000001</v>
@@ -6763,37 +6763,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M67">
-        <v>55.56859750000001</v>
+        <v>53.40486450000001</v>
       </c>
       <c r="N67">
-        <v>309.7647358333333</v>
+        <v>311.9284688333333</v>
       </c>
       <c r="O67">
-        <v>77.25532511683333</v>
+        <v>77.79496012703332</v>
       </c>
       <c r="P67">
-        <v>232.5094107165</v>
+        <v>234.1335087062999</v>
       </c>
       <c r="Q67">
-        <v>281.5094107165</v>
+        <v>283.1335087062999</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1043918087190626</v>
+        <v>0.104354139395485</v>
       </c>
       <c r="T67">
         <v>1.352289593429215</v>
       </c>
       <c r="U67">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V67">
         <v>0.2494</v>
       </c>
       <c r="W67">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.574456613437711</v>
+        <v>6.840825021348631</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6812,13 +6812,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.06400796707049194</v>
+        <v>0.06290495085052061</v>
       </c>
       <c r="C68">
-        <v>677.310459871743</v>
+        <v>703.5592478528511</v>
       </c>
       <c r="D68">
-        <v>1622.056459871743</v>
+        <v>1648.305247852851</v>
       </c>
       <c r="E68">
         <v>-7.354000000000042</v>
@@ -6845,37 +6845,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M68">
-        <v>56.42349900000001</v>
+        <v>54.2264778</v>
       </c>
       <c r="N68">
-        <v>308.9098343333333</v>
+        <v>311.1068555333333</v>
       </c>
       <c r="O68">
-        <v>77.04211268273333</v>
+        <v>77.59004977001334</v>
       </c>
       <c r="P68">
-        <v>231.8677216506</v>
+        <v>233.51680576332</v>
       </c>
       <c r="Q68">
-        <v>280.8677216506</v>
+        <v>282.51680576332</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1059355678543881</v>
+        <v>0.105896906030943</v>
       </c>
       <c r="T68">
         <v>1.387919307873972</v>
       </c>
       <c r="U68">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V68">
         <v>0.2494</v>
       </c>
       <c r="W68">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.474843634446231</v>
+        <v>6.737176157388804</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6894,13 +6894,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.06391301608931199</v>
+        <v>0.06279352591262147</v>
       </c>
       <c r="C69">
-        <v>664.4327366422449</v>
+        <v>691.1595032019763</v>
       </c>
       <c r="D69">
-        <v>1624.309736642245</v>
+        <v>1651.036503201976</v>
       </c>
       <c r="E69">
         <v>7.777000000000044</v>
@@ -6927,37 +6927,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M69">
-        <v>57.27840050000001</v>
+        <v>55.04809110000001</v>
       </c>
       <c r="N69">
-        <v>308.0549328333333</v>
+        <v>310.2852422333333</v>
       </c>
       <c r="O69">
-        <v>76.82890024863332</v>
+        <v>77.38513941299333</v>
       </c>
       <c r="P69">
-        <v>231.2260325847</v>
+        <v>232.90010282034</v>
       </c>
       <c r="Q69">
-        <v>280.2260325847</v>
+        <v>281.90010282034</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1075728881494303</v>
+        <v>0.1075331736746105</v>
       </c>
       <c r="T69">
         <v>1.425708398951743</v>
       </c>
       <c r="U69">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V69">
         <v>0.2494</v>
       </c>
       <c r="W69">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.378204177215689</v>
+        <v>6.636621289368075</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6976,13 +6976,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.06381806510813204</v>
+        <v>0.06268210097472231</v>
       </c>
       <c r="C70">
-        <v>651.561282391913</v>
+        <v>678.7688249994246</v>
       </c>
       <c r="D70">
-        <v>1626.569282391913</v>
+        <v>1653.776824999424</v>
       </c>
       <c r="E70">
         <v>22.9079999999999</v>
@@ -7009,37 +7009,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M70">
-        <v>58.133302</v>
+        <v>55.8697044</v>
       </c>
       <c r="N70">
-        <v>307.2000313333333</v>
+        <v>309.4636289333333</v>
       </c>
       <c r="O70">
-        <v>76.61568781453333</v>
+        <v>77.18022905597333</v>
       </c>
       <c r="P70">
-        <v>230.5843435188</v>
+        <v>232.28339987736</v>
       </c>
       <c r="Q70">
-        <v>279.5843435188</v>
+        <v>281.28339987736</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1093125409629126</v>
+        <v>0.1092717080460072</v>
       </c>
       <c r="T70">
         <v>1.465859308221876</v>
       </c>
       <c r="U70">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V70">
         <v>0.2494</v>
       </c>
       <c r="W70">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.284407056962519</v>
+        <v>6.539023917465604</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7058,13 +7058,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06372311412695209</v>
+        <v>0.06257067603682316</v>
       </c>
       <c r="C71">
-        <v>638.6961233191578</v>
+        <v>666.387258464591</v>
       </c>
       <c r="D71">
-        <v>1628.835123319158</v>
+        <v>1656.526258464591</v>
       </c>
       <c r="E71">
         <v>38.03899999999999</v>
@@ -7091,37 +7091,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M71">
-        <v>58.98820350000001</v>
+        <v>56.69131770000001</v>
       </c>
       <c r="N71">
-        <v>306.3451298333333</v>
+        <v>308.6420156333333</v>
       </c>
       <c r="O71">
-        <v>76.40247538043333</v>
+        <v>76.97531869895333</v>
       </c>
       <c r="P71">
-        <v>229.9426544529</v>
+        <v>231.66669693438</v>
       </c>
       <c r="Q71">
-        <v>278.9426544529</v>
+        <v>280.66669693438</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1111644294417809</v>
+        <v>0.111122405925236</v>
       </c>
       <c r="T71">
         <v>1.508600598735242</v>
       </c>
       <c r="U71">
-        <v>0.05650000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V71">
         <v>0.2494</v>
       </c>
       <c r="W71">
-        <v>0.0424089</v>
+        <v>0.04075758</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.193328693818134</v>
+        <v>6.444255454893638</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7140,13 +7140,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06436375114577214</v>
+        <v>0.06245925109892401</v>
       </c>
       <c r="C72">
-        <v>608.3986783518678</v>
+        <v>654.0148491180857</v>
       </c>
       <c r="D72">
-        <v>1613.668678351868</v>
+        <v>1659.284849118086</v>
       </c>
       <c r="E72">
         <v>53.17000000000007</v>
@@ -7173,45 +7173,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M72">
-        <v>61.32594300000001</v>
+        <v>57.51293100000001</v>
       </c>
       <c r="N72">
-        <v>304.0073903333333</v>
+        <v>307.8204023333333</v>
       </c>
       <c r="O72">
-        <v>75.81944314913333</v>
+        <v>76.77040834193332</v>
       </c>
       <c r="P72">
-        <v>228.1879471842</v>
+        <v>231.0499939914</v>
       </c>
       <c r="Q72">
-        <v>277.1879471842</v>
+        <v>280.0499939914</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1131397771525738</v>
+        <v>0.11309648366308</v>
       </c>
       <c r="T72">
         <v>1.554191308616167</v>
       </c>
       <c r="U72">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V72">
         <v>0.2494</v>
       </c>
       <c r="W72">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y72">
-        <v>5.957239554120403</v>
+        <v>6.352194662680871</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.06427930856459219</v>
+        <v>0.06234782616102486</v>
       </c>
       <c r="C73">
-        <v>595.2505922211606</v>
+        <v>641.6516427842428</v>
       </c>
       <c r="D73">
-        <v>1615.65159222116</v>
+        <v>1662.052642784243</v>
       </c>
       <c r="E73">
         <v>68.30099999999993</v>
@@ -7255,45 +7255,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M73">
-        <v>62.2020279</v>
+        <v>58.3345443</v>
       </c>
       <c r="N73">
-        <v>303.1313054333333</v>
+        <v>306.9987890333333</v>
       </c>
       <c r="O73">
-        <v>75.60094757507332</v>
+        <v>76.56549798491334</v>
       </c>
       <c r="P73">
-        <v>227.53035785826</v>
+        <v>230.43329104842</v>
       </c>
       <c r="Q73">
-        <v>276.53035785826</v>
+        <v>279.43329104842</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.115251355739973</v>
+        <v>0.1152067046931892</v>
       </c>
       <c r="T73">
         <v>1.602926205385431</v>
       </c>
       <c r="U73">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V73">
         <v>0.2494</v>
       </c>
       <c r="W73">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y73">
-        <v>5.873334771668003</v>
+        <v>6.262727132220578</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7304,13 +7304,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.06419486598341223</v>
+        <v>0.06223640122312571</v>
       </c>
       <c r="C74">
-        <v>582.1073853882667</v>
+        <v>629.2976855936588</v>
       </c>
       <c r="D74">
-        <v>1617.639385388266</v>
+        <v>1664.829685593658</v>
       </c>
       <c r="E74">
         <v>83.43199999999979</v>
@@ -7337,45 +7337,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M74">
-        <v>63.07811279999999</v>
+        <v>59.1561576</v>
       </c>
       <c r="N74">
-        <v>302.2552205333333</v>
+        <v>306.1771757333333</v>
       </c>
       <c r="O74">
-        <v>75.38245200101333</v>
+        <v>76.36058762789334</v>
       </c>
       <c r="P74">
-        <v>226.87276853232</v>
+        <v>229.81658810544</v>
       </c>
       <c r="Q74">
-        <v>275.87276853232</v>
+        <v>278.81658810544</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1175137613693294</v>
+        <v>0.1174676557968775</v>
       </c>
       <c r="T74">
         <v>1.655142166209643</v>
       </c>
       <c r="U74">
-        <v>0.05790000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V74">
         <v>0.2494</v>
       </c>
       <c r="W74">
-        <v>0.04345974</v>
+        <v>0.04075758</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y74">
-        <v>5.79176067761706</v>
+        <v>6.175744810939738</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7386,13 +7386,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.06411042340223227</v>
+        <v>0.06267291428522656</v>
       </c>
       <c r="C75">
-        <v>568.9690758848874</v>
+        <v>603.3401632020386</v>
       </c>
       <c r="D75">
-        <v>1619.632075884887</v>
+        <v>1654.003163202038</v>
       </c>
       <c r="E75">
         <v>98.56299999999987</v>
@@ -7419,37 +7419,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M75">
-        <v>63.9541977</v>
+        <v>61.0823339</v>
       </c>
       <c r="N75">
-        <v>301.3791356333333</v>
+        <v>304.2509994333333</v>
       </c>
       <c r="O75">
-        <v>75.16395642695333</v>
+        <v>75.88019925867334</v>
       </c>
       <c r="P75">
-        <v>226.21517920638</v>
+        <v>228.37080017466</v>
       </c>
       <c r="Q75">
-        <v>275.21517920638</v>
+        <v>277.37080017466</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1199437526008603</v>
+        <v>0.1198960847600983</v>
       </c>
       <c r="T75">
         <v>1.711225975983796</v>
       </c>
       <c r="U75">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V75">
         <v>0.2494</v>
       </c>
       <c r="W75">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.712421490252442</v>
+        <v>5.98099826917932</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.06402598082105232</v>
+        <v>0.06256899534732741</v>
       </c>
       <c r="C76">
-        <v>555.835681831684</v>
+        <v>590.7737998152713</v>
       </c>
       <c r="D76">
-        <v>1621.629681831684</v>
+        <v>1656.567799815271</v>
       </c>
       <c r="E76">
         <v>113.694</v>
@@ -7501,37 +7501,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M76">
-        <v>64.8302826</v>
+        <v>61.91907820000001</v>
       </c>
       <c r="N76">
-        <v>300.5030507333333</v>
+        <v>303.4142551333333</v>
       </c>
       <c r="O76">
-        <v>74.94546085289333</v>
+        <v>75.67151523025333</v>
       </c>
       <c r="P76">
-        <v>225.55758988044</v>
+        <v>227.74273990308</v>
       </c>
       <c r="Q76">
-        <v>274.55758988044</v>
+        <v>276.74273990308</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1225606662348166</v>
+        <v>0.1225113159512592</v>
       </c>
       <c r="T76">
         <v>1.771623924971345</v>
       </c>
       <c r="U76">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V76">
         <v>0.2494</v>
       </c>
       <c r="W76">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.635226605249031</v>
+        <v>5.900173968244464</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7550,13 +7550,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.06394153823987238</v>
+        <v>0.06246507640942826</v>
       </c>
       <c r="C77">
-        <v>542.7072214388256</v>
+        <v>578.2154020425451</v>
       </c>
       <c r="D77">
-        <v>1623.632221438825</v>
+        <v>1659.140402042545</v>
       </c>
       <c r="E77">
         <v>128.8249999999998</v>
@@ -7583,37 +7583,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M77">
-        <v>65.7063675</v>
+        <v>62.7558225</v>
       </c>
       <c r="N77">
-        <v>299.6269658333333</v>
+        <v>302.5775108333333</v>
       </c>
       <c r="O77">
-        <v>74.72696527883333</v>
+        <v>75.46283120183332</v>
       </c>
       <c r="P77">
-        <v>224.9000005545</v>
+        <v>227.1146796315</v>
       </c>
       <c r="Q77">
-        <v>273.9000005545</v>
+        <v>276.1146796314999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1253869329594895</v>
+        <v>0.125335765637713</v>
       </c>
       <c r="T77">
         <v>1.836853709877899</v>
       </c>
       <c r="U77">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V77">
         <v>0.2494</v>
       </c>
       <c r="W77">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.560090250512377</v>
+        <v>5.821504982001205</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7632,13 +7632,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.06385709565869242</v>
+        <v>0.06236115747152911</v>
       </c>
       <c r="C78">
-        <v>529.5837130065436</v>
+        <v>565.6650070526921</v>
       </c>
       <c r="D78">
-        <v>1625.639713006543</v>
+        <v>1661.721007052692</v>
       </c>
       <c r="E78">
         <v>143.9559999999999</v>
@@ -7665,37 +7665,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M78">
-        <v>66.58245240000001</v>
+        <v>63.59256680000001</v>
       </c>
       <c r="N78">
-        <v>298.7508809333333</v>
+        <v>301.7407665333333</v>
       </c>
       <c r="O78">
-        <v>74.50846970477333</v>
+        <v>75.25414717341333</v>
       </c>
       <c r="P78">
-        <v>224.2424112285599</v>
+        <v>226.48661935992</v>
       </c>
       <c r="Q78">
-        <v>273.2424112285599</v>
+        <v>275.48661935992</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1284487219112184</v>
+        <v>0.1283955861313713</v>
       </c>
       <c r="T78">
         <v>1.907519310193332</v>
       </c>
       <c r="U78">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V78">
         <v>0.2494</v>
       </c>
       <c r="W78">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.486931168268792</v>
+        <v>5.744906232238031</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7714,13 +7714,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.06377265307751248</v>
+        <v>0.06225723853362997</v>
       </c>
       <c r="C79">
-        <v>516.4651749256877</v>
+        <v>553.1226522461518</v>
       </c>
       <c r="D79">
-        <v>1627.652174925688</v>
+        <v>1664.309652246152</v>
       </c>
       <c r="E79">
         <v>159.087</v>
@@ -7747,37 +7747,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M79">
-        <v>67.4585373</v>
+        <v>64.42931110000001</v>
       </c>
       <c r="N79">
-        <v>297.8747960333333</v>
+        <v>300.9040222333333</v>
       </c>
       <c r="O79">
-        <v>74.28997413071333</v>
+        <v>75.04546314499333</v>
       </c>
       <c r="P79">
-        <v>223.58482190262</v>
+        <v>225.85855908834</v>
       </c>
       <c r="Q79">
-        <v>272.58482190262</v>
+        <v>274.85855908834</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.131776753380489</v>
+        <v>0.1317214779723042</v>
       </c>
       <c r="T79">
         <v>1.984329745318803</v>
       </c>
       <c r="U79">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V79">
         <v>0.2494</v>
       </c>
       <c r="W79">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.41567232192764</v>
+        <v>5.670297060390784</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7796,13 +7796,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.06368821049633253</v>
+        <v>0.06215331959573081</v>
       </c>
       <c r="C80">
-        <v>503.3516256782889</v>
+        <v>540.5883752567788</v>
       </c>
       <c r="D80">
-        <v>1629.669625678289</v>
+        <v>1666.906375256779</v>
       </c>
       <c r="E80">
         <v>174.2180000000001</v>
@@ -7829,37 +7829,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M80">
-        <v>68.33462220000001</v>
+        <v>65.26605540000001</v>
       </c>
       <c r="N80">
-        <v>296.9987111333333</v>
+        <v>300.0672779333333</v>
       </c>
       <c r="O80">
-        <v>74.07147855665333</v>
+        <v>74.83677911657333</v>
       </c>
       <c r="P80">
-        <v>222.92723257668</v>
+        <v>225.23049881676</v>
       </c>
       <c r="Q80">
-        <v>271.92723257668</v>
+        <v>274.23049881676</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1354073331651478</v>
+        <v>0.1353497236169582</v>
       </c>
       <c r="T80">
         <v>2.068122947273862</v>
       </c>
       <c r="U80">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V80">
         <v>0.2494</v>
       </c>
       <c r="W80">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.346240625492669</v>
+        <v>5.597600944231926</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7878,13 +7878,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.06360376791515257</v>
+        <v>0.06204940065783165</v>
       </c>
       <c r="C81">
-        <v>490.2430838381249</v>
+        <v>528.0622139536663</v>
       </c>
       <c r="D81">
-        <v>1631.692083838125</v>
+        <v>1669.511213953666</v>
       </c>
       <c r="E81">
         <v>189.3489999999999</v>
@@ -7911,37 +7911,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M81">
-        <v>69.21070710000001</v>
+        <v>66.10279970000001</v>
       </c>
       <c r="N81">
-        <v>296.1226262333333</v>
+        <v>299.2305336333333</v>
       </c>
       <c r="O81">
-        <v>73.85298298259333</v>
+        <v>74.62809508815333</v>
       </c>
       <c r="P81">
-        <v>222.26964325074</v>
+        <v>224.60243854518</v>
       </c>
       <c r="Q81">
-        <v>271.26964325074</v>
+        <v>273.60243854518</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.1393836824531075</v>
+        <v>0.139323516465865</v>
       </c>
       <c r="T81">
         <v>2.159896454177022</v>
       </c>
       <c r="U81">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V81">
         <v>0.2494</v>
       </c>
       <c r="W81">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.278566693524408</v>
+        <v>5.526745236077093</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7960,13 +7960,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.06351932533397261</v>
+        <v>0.06194548171993251</v>
       </c>
       <c r="C82">
-        <v>477.139568071289</v>
+        <v>515.5442064429851</v>
       </c>
       <c r="D82">
-        <v>1633.719568071289</v>
+        <v>1672.124206442985</v>
       </c>
       <c r="E82">
         <v>204.48</v>
@@ -7993,37 +7993,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M82">
-        <v>70.086792</v>
+        <v>66.93954400000001</v>
       </c>
       <c r="N82">
-        <v>295.2465413333333</v>
+        <v>298.3937893333333</v>
       </c>
       <c r="O82">
-        <v>73.63448740853333</v>
+        <v>74.41941105973333</v>
       </c>
       <c r="P82">
-        <v>221.6120539248</v>
+        <v>223.9743782736</v>
       </c>
       <c r="Q82">
-        <v>270.6120539248</v>
+        <v>272.9743782736</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.1437576666698631</v>
+        <v>0.1436946885996626</v>
       </c>
       <c r="T82">
         <v>2.260847311770498</v>
       </c>
       <c r="U82">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V82">
         <v>0.2494</v>
       </c>
       <c r="W82">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.212584609855353</v>
+        <v>5.457660920626129</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8042,13 +8042,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06343488275279266</v>
+        <v>0.06184156278203336</v>
       </c>
       <c r="C83">
-        <v>464.041097136766</v>
+        <v>503.0343910698464</v>
       </c>
       <c r="D83">
-        <v>1635.752097136766</v>
+        <v>1674.745391069846</v>
       </c>
       <c r="E83">
         <v>219.6110000000001</v>
@@ -8075,37 +8075,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M83">
-        <v>70.96287690000001</v>
+        <v>67.77628830000002</v>
       </c>
       <c r="N83">
-        <v>294.3704564333333</v>
+        <v>297.5570450333333</v>
       </c>
       <c r="O83">
-        <v>73.41599183447333</v>
+        <v>74.21072703131333</v>
       </c>
       <c r="P83">
-        <v>220.9544645988599</v>
+        <v>223.34631800202</v>
       </c>
       <c r="Q83">
-        <v>269.9544645988599</v>
+        <v>272.34631800202</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.1485920702778561</v>
+        <v>0.148525984115965</v>
       </c>
       <c r="T83">
         <v>2.372424575426444</v>
       </c>
       <c r="U83">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V83">
         <v>0.2494</v>
       </c>
       <c r="W83">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.148231713437385</v>
+        <v>5.390282390741855</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8124,13 +8124,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06335044017161272</v>
+        <v>0.06173764384413422</v>
       </c>
       <c r="C84">
-        <v>450.94768988701</v>
+        <v>490.5328064201719</v>
       </c>
       <c r="D84">
-        <v>1637.78968988701</v>
+        <v>1677.374806420172</v>
       </c>
       <c r="E84">
         <v>234.742</v>
@@ -8157,37 +8157,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M84">
-        <v>71.83896180000001</v>
+        <v>68.61303260000001</v>
       </c>
       <c r="N84">
-        <v>293.4943715333333</v>
+        <v>296.7203007333333</v>
       </c>
       <c r="O84">
-        <v>73.19749626041333</v>
+        <v>74.00204300289333</v>
       </c>
       <c r="P84">
-        <v>220.29687527292</v>
+        <v>222.71825773044</v>
       </c>
       <c r="Q84">
-        <v>269.29687527292</v>
+        <v>271.71825773044</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.1539636298422929</v>
+        <v>0.1538940902451901</v>
       </c>
       <c r="T84">
         <v>2.496399312821941</v>
       </c>
       <c r="U84">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V84">
         <v>0.2494</v>
       </c>
       <c r="W84">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.085448399858882</v>
+        <v>5.324547239635248</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8206,13 +8206,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06326599759043276</v>
+        <v>0.06163372490623506</v>
       </c>
       <c r="C85">
-        <v>437.8593652685272</v>
+        <v>478.0394913225923</v>
       </c>
       <c r="D85">
-        <v>1639.832365268527</v>
+        <v>1680.012491322592</v>
       </c>
       <c r="E85">
         <v>249.873</v>
@@ -8239,37 +8239,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M85">
-        <v>72.71504670000002</v>
+        <v>69.44977690000002</v>
       </c>
       <c r="N85">
-        <v>292.6182866333333</v>
+        <v>295.8835564333333</v>
       </c>
       <c r="O85">
-        <v>72.97900068635333</v>
+        <v>73.79335897447332</v>
       </c>
       <c r="P85">
-        <v>219.63928594698</v>
+        <v>222.09019745886</v>
       </c>
       <c r="Q85">
-        <v>268.63928594698</v>
+        <v>271.09019745886</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.159967137590781</v>
+        <v>0.159893738271971</v>
       </c>
       <c r="T85">
         <v>2.634959313440438</v>
       </c>
       <c r="U85">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V85">
         <v>0.2494</v>
       </c>
       <c r="W85">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.024177937209978</v>
+        <v>5.260396068073376</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8288,13 +8288,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.06318155500925281</v>
+        <v>0.06152980596833591</v>
       </c>
       <c r="C86">
-        <v>424.776142322464</v>
+        <v>465.5544848503544</v>
       </c>
       <c r="D86">
-        <v>1641.880142322464</v>
+        <v>1682.658484850354</v>
       </c>
       <c r="E86">
         <v>265.0039999999999</v>
@@ -8321,37 +8321,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M86">
-        <v>73.5911316</v>
+        <v>70.28652120000001</v>
       </c>
       <c r="N86">
-        <v>291.7422017333333</v>
+        <v>295.0468121333333</v>
       </c>
       <c r="O86">
-        <v>72.76050511229333</v>
+        <v>73.58467494605334</v>
       </c>
       <c r="P86">
-        <v>218.98169662104</v>
+        <v>221.46213718728</v>
       </c>
       <c r="Q86">
-        <v>267.98169662104</v>
+        <v>270.46213718728</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.16672108380783</v>
+        <v>0.1666433423020994</v>
       </c>
       <c r="T86">
         <v>2.790839314136245</v>
       </c>
       <c r="U86">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V86">
         <v>0.2494</v>
       </c>
       <c r="W86">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>4.964366295100337</v>
+        <v>5.197772305358218</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8370,13 +8370,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.06309711242807287</v>
+        <v>0.06142588703043676</v>
       </c>
       <c r="C87">
-        <v>411.6980401851963</v>
+        <v>453.0778263232535</v>
       </c>
       <c r="D87">
-        <v>1643.933040185196</v>
+        <v>1685.312826323253</v>
       </c>
       <c r="E87">
         <v>280.135</v>
@@ -8403,37 +8403,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M87">
-        <v>74.46721650000001</v>
+        <v>71.12326550000002</v>
       </c>
       <c r="N87">
-        <v>290.8661168333333</v>
+        <v>294.2100678333333</v>
       </c>
       <c r="O87">
-        <v>72.54200953823333</v>
+        <v>73.37599091763333</v>
       </c>
       <c r="P87">
-        <v>218.3241072951</v>
+        <v>220.8340769157</v>
       </c>
       <c r="Q87">
-        <v>267.3241072951</v>
+        <v>269.8340769157</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.1743755561871524</v>
+        <v>0.174292893536245</v>
       </c>
       <c r="T87">
         <v>2.967503314924827</v>
       </c>
       <c r="U87">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V87">
         <v>0.2494</v>
       </c>
       <c r="W87">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>4.905961985746215</v>
+        <v>5.136622042942239</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8452,13 +8452,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.06301266984689291</v>
+        <v>0.06132196809253761</v>
       </c>
       <c r="C88">
-        <v>398.6250780889293</v>
+        <v>440.6095553095793</v>
       </c>
       <c r="D88">
-        <v>1645.991078088929</v>
+        <v>1687.975555309579</v>
       </c>
       <c r="E88">
         <v>295.2659999999998</v>
@@ -8485,37 +8485,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M88">
-        <v>75.3433014</v>
+        <v>71.96000980000001</v>
       </c>
       <c r="N88">
-        <v>289.9900319333333</v>
+        <v>293.3733235333333</v>
       </c>
       <c r="O88">
-        <v>72.32351396417333</v>
+        <v>73.16730688921332</v>
       </c>
       <c r="P88">
-        <v>217.6665179691599</v>
+        <v>220.20601664412</v>
       </c>
       <c r="Q88">
-        <v>266.6665179691599</v>
+        <v>269.20601664412</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.1831235246206636</v>
+        <v>0.18303523780384</v>
       </c>
       <c r="T88">
         <v>3.169405030111779</v>
       </c>
       <c r="U88">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V88">
         <v>0.2494</v>
       </c>
       <c r="W88">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>4.848915916144515</v>
+        <v>5.076893879652213</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8534,13 +8534,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.06292822726571295</v>
+        <v>0.06121804915463847</v>
       </c>
       <c r="C89">
-        <v>385.5572753622937</v>
+        <v>428.1497116280825</v>
       </c>
       <c r="D89">
-        <v>1648.054275362294</v>
+        <v>1690.646711628082</v>
       </c>
       <c r="E89">
         <v>310.3969999999999</v>
@@ -8567,37 +8567,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M89">
-        <v>76.21938630000001</v>
+        <v>72.7967541</v>
       </c>
       <c r="N89">
-        <v>289.1139470333333</v>
+        <v>292.5365792333333</v>
       </c>
       <c r="O89">
-        <v>72.10501839011333</v>
+        <v>72.95862286079334</v>
       </c>
       <c r="P89">
-        <v>217.00892864322</v>
+        <v>219.57795637254</v>
       </c>
       <c r="Q89">
-        <v>266.00892864322</v>
+        <v>268.57795637254</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.1932173343516381</v>
+        <v>0.1931225581126035</v>
       </c>
       <c r="T89">
         <v>3.402368547635184</v>
       </c>
       <c r="U89">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V89">
         <v>0.2494</v>
       </c>
       <c r="W89">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>4.793181250441704</v>
+        <v>5.018538777587246</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8616,13 +8616,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.062843784684533</v>
+        <v>0.06111413021673931</v>
       </c>
       <c r="C90">
-        <v>372.4946514309556</v>
+        <v>415.6983353499609</v>
       </c>
       <c r="D90">
-        <v>1650.122651430956</v>
+        <v>1693.326335349961</v>
       </c>
       <c r="E90">
         <v>325.528</v>
@@ -8649,37 +8649,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M90">
-        <v>77.09547120000001</v>
+        <v>73.63349840000001</v>
       </c>
       <c r="N90">
-        <v>288.2378621333333</v>
+        <v>291.6998349333333</v>
       </c>
       <c r="O90">
-        <v>71.88652281605333</v>
+        <v>72.74993883237333</v>
       </c>
       <c r="P90">
-        <v>216.35133931728</v>
+        <v>218.94989610096</v>
       </c>
       <c r="Q90">
-        <v>265.35133931728</v>
+        <v>267.94989610096</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.2049934457044417</v>
+        <v>0.2048910984728276</v>
       </c>
       <c r="T90">
         <v>3.674159318079159</v>
       </c>
       <c r="U90">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V90">
         <v>0.2494</v>
       </c>
       <c r="W90">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.738713281686684</v>
+        <v>4.961509927841936</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8698,13 +8698,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.06275934210335304</v>
+        <v>0.06101021127884015</v>
       </c>
       <c r="C91">
-        <v>359.4372258182216</v>
+        <v>403.2554668008613</v>
       </c>
       <c r="D91">
-        <v>1652.196225818221</v>
+        <v>1696.014466800861</v>
       </c>
       <c r="E91">
         <v>340.6589999999999</v>
@@ -8731,37 +8731,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M91">
-        <v>77.9715561</v>
+        <v>74.4702427</v>
       </c>
       <c r="N91">
-        <v>287.3617772333333</v>
+        <v>290.8630906333333</v>
       </c>
       <c r="O91">
-        <v>71.66802724199333</v>
+        <v>72.54125480395332</v>
       </c>
       <c r="P91">
-        <v>215.69374999134</v>
+        <v>218.3218358293799</v>
       </c>
       <c r="Q91">
-        <v>264.69374999134</v>
+        <v>267.3218358293799</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.2189106682123005</v>
+        <v>0.2187993734440014</v>
       </c>
       <c r="T91">
         <v>3.995366592240218</v>
       </c>
       <c r="U91">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V91">
         <v>0.2494</v>
       </c>
       <c r="W91">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.685469312229531</v>
+        <v>4.905762625281914</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8780,13 +8780,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.0626748995221731</v>
+        <v>0.06090629234094101</v>
       </c>
       <c r="C92">
-        <v>346.385018145656</v>
+        <v>390.8211465629029</v>
       </c>
       <c r="D92">
-        <v>1654.275018145656</v>
+        <v>1698.711146562903</v>
       </c>
       <c r="E92">
         <v>355.79</v>
@@ -8813,37 +8813,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M92">
-        <v>78.84764100000001</v>
+        <v>75.30698700000001</v>
       </c>
       <c r="N92">
-        <v>286.4856923333333</v>
+        <v>290.0263463333333</v>
       </c>
       <c r="O92">
-        <v>71.44953166793333</v>
+        <v>72.33257077553333</v>
       </c>
       <c r="P92">
-        <v>215.0361606654</v>
+        <v>217.6937755578</v>
       </c>
       <c r="Q92">
-        <v>264.0361606654</v>
+        <v>266.6937755578</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.235611335221731</v>
+        <v>0.2354893034094101</v>
       </c>
       <c r="T92">
         <v>4.380815321233489</v>
       </c>
       <c r="U92">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V92">
         <v>0.2494</v>
       </c>
       <c r="W92">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.633408542093647</v>
+        <v>4.85125415166767</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8862,13 +8862,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.06259045694099315</v>
+        <v>0.06080237340304186</v>
       </c>
       <c r="C93">
-        <v>333.3380481336994</v>
+        <v>378.3954154767205</v>
       </c>
       <c r="D93">
-        <v>1656.359048133699</v>
+        <v>1701.41641547672</v>
       </c>
       <c r="E93">
         <v>370.921</v>
@@ -8895,37 +8895,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M93">
-        <v>79.72372590000002</v>
+        <v>76.14373130000001</v>
       </c>
       <c r="N93">
-        <v>285.6096074333333</v>
+        <v>289.1896020333333</v>
       </c>
       <c r="O93">
-        <v>71.23103609387333</v>
+        <v>72.12388674711333</v>
       </c>
       <c r="P93">
-        <v>214.3785713394599</v>
+        <v>217.06571528622</v>
       </c>
       <c r="Q93">
-        <v>263.3785713394599</v>
+        <v>266.06571528622</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.2560232615665906</v>
+        <v>0.2558881067004651</v>
       </c>
       <c r="T93">
         <v>4.851919323336376</v>
       </c>
       <c r="U93">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V93">
         <v>0.2494</v>
       </c>
       <c r="W93">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.582491964708002</v>
+        <v>4.797943666484509</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8944,13 +8944,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.06250601435981319</v>
+        <v>0.06069845446514271</v>
       </c>
       <c r="C94">
-        <v>320.296335602291</v>
+        <v>365.9783146435254</v>
       </c>
       <c r="D94">
-        <v>1658.448335602291</v>
+        <v>1704.130314643525</v>
       </c>
       <c r="E94">
         <v>386.0519999999999</v>
@@ -8977,37 +8977,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M94">
-        <v>80.5998108</v>
+        <v>76.98047560000001</v>
       </c>
       <c r="N94">
-        <v>284.7335225333333</v>
+        <v>288.3528577333333</v>
       </c>
       <c r="O94">
-        <v>71.01254051981333</v>
+        <v>71.91520271869332</v>
       </c>
       <c r="P94">
-        <v>213.72098201352</v>
+        <v>216.43765501464</v>
       </c>
       <c r="Q94">
-        <v>262.72098201352</v>
+        <v>265.43765501464</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.2815381694976651</v>
+        <v>0.281386610814284</v>
       </c>
       <c r="T94">
         <v>5.440799325964988</v>
       </c>
       <c r="U94">
-        <v>0.05790000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V94">
         <v>0.2494</v>
       </c>
       <c r="W94">
-        <v>0.04345974</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.532682269439437</v>
+        <v>4.745792104892286</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9026,13 +9026,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.06423652257863324</v>
+        <v>0.06059453552724356</v>
       </c>
       <c r="C95">
-        <v>263.3751708998627</v>
+        <v>353.5698854271877</v>
       </c>
       <c r="D95">
-        <v>1616.658170899863</v>
+        <v>1706.852885427188</v>
       </c>
       <c r="E95">
         <v>401.183</v>
@@ -9059,45 +9059,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M95">
-        <v>85.13457150000001</v>
+        <v>77.81721990000001</v>
       </c>
       <c r="N95">
-        <v>280.1987618333333</v>
+        <v>287.5161134333333</v>
       </c>
       <c r="O95">
-        <v>69.88157120123333</v>
+        <v>71.70651869027333</v>
       </c>
       <c r="P95">
-        <v>210.3171906321</v>
+        <v>215.80959474306</v>
       </c>
       <c r="Q95">
-        <v>259.3171906321</v>
+        <v>264.80959474306</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.3143430511233323</v>
+        <v>0.3141704018177652</v>
       </c>
       <c r="T95">
         <v>6.197930757916057</v>
       </c>
       <c r="U95">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V95">
         <v>0.2494</v>
       </c>
       <c r="W95">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y95">
-        <v>4.29124534130454</v>
+        <v>4.694762082259036</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9108,13 +9108,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06417159559745329</v>
+        <v>0.06049061658934441</v>
       </c>
       <c r="C96">
-        <v>249.7740343382602</v>
+        <v>341.1701694563355</v>
       </c>
       <c r="D96">
-        <v>1618.18803433826</v>
+        <v>1709.584169456336</v>
       </c>
       <c r="E96">
         <v>416.3140000000001</v>
@@ -9141,45 +9141,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M96">
-        <v>86.04999700000002</v>
+        <v>78.65396420000002</v>
       </c>
       <c r="N96">
-        <v>279.2833363333333</v>
+        <v>286.6793691333333</v>
       </c>
       <c r="O96">
-        <v>69.65326408153332</v>
+        <v>71.49783466185333</v>
       </c>
       <c r="P96">
-        <v>209.6300722518</v>
+        <v>215.1815344714799</v>
       </c>
       <c r="Q96">
-        <v>258.6300722518</v>
+        <v>264.1815344714799</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.3580828932908885</v>
+        <v>0.3578821231557404</v>
       </c>
       <c r="T96">
         <v>7.207439333850816</v>
       </c>
       <c r="U96">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V96">
         <v>0.2494</v>
       </c>
       <c r="W96">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y96">
-        <v>4.245593795120449</v>
+        <v>4.644817804788195</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9190,13 +9190,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06410666861627334</v>
+        <v>0.06038669765144526</v>
       </c>
       <c r="C97">
-        <v>236.175795976299</v>
+        <v>328.7792086264801</v>
       </c>
       <c r="D97">
-        <v>1619.720795976299</v>
+        <v>1712.32420862648</v>
       </c>
       <c r="E97">
         <v>431.4449999999999</v>
@@ -9223,45 +9223,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M97">
-        <v>86.9654225</v>
+        <v>79.49070850000001</v>
       </c>
       <c r="N97">
-        <v>278.3679108333333</v>
+        <v>285.8426248333333</v>
       </c>
       <c r="O97">
-        <v>69.42495696183333</v>
+        <v>71.28915063343332</v>
       </c>
       <c r="P97">
-        <v>208.9429538715</v>
+        <v>214.5534741998999</v>
       </c>
       <c r="Q97">
-        <v>257.9429538715</v>
+        <v>263.5534741998999</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.4193186723254674</v>
+        <v>0.4190785330289056</v>
       </c>
       <c r="T97">
         <v>8.620751340159483</v>
       </c>
       <c r="U97">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V97">
         <v>0.2494</v>
       </c>
       <c r="W97">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y97">
-        <v>4.200903334119182</v>
+        <v>4.595924985790424</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9272,13 +9272,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.06404174163509339</v>
+        <v>0.06028277871354611</v>
       </c>
       <c r="C98">
-        <v>222.5804640573854</v>
+        <v>316.397045102156</v>
       </c>
       <c r="D98">
-        <v>1621.256464057385</v>
+        <v>1715.073045102156</v>
       </c>
       <c r="E98">
         <v>446.5759999999998</v>
@@ -9305,45 +9305,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M98">
-        <v>87.880848</v>
+        <v>80.3274528</v>
       </c>
       <c r="N98">
-        <v>277.4524853333333</v>
+        <v>285.0058805333333</v>
       </c>
       <c r="O98">
-        <v>69.19664984213333</v>
+        <v>71.08046660501333</v>
       </c>
       <c r="P98">
-        <v>208.2558354912</v>
+        <v>213.92541392832</v>
       </c>
       <c r="Q98">
-        <v>257.2558354911999</v>
+        <v>262.92541392832</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.5111723408773343</v>
+        <v>0.5108731478386521</v>
       </c>
       <c r="T98">
         <v>10.74071934962245</v>
       </c>
       <c r="U98">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V98">
         <v>0.2494</v>
       </c>
       <c r="W98">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>4.157143924388773</v>
+        <v>4.548050767188441</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9354,13 +9354,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.06397681465391344</v>
+        <v>0.06017885977564696</v>
       </c>
       <c r="C99">
-        <v>208.9880468562185</v>
+        <v>304.0237213190833</v>
       </c>
       <c r="D99">
-        <v>1622.795046856218</v>
+        <v>1717.830721319083</v>
       </c>
       <c r="E99">
         <v>461.7069999999999</v>
@@ -9387,45 +9387,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M99">
-        <v>88.7962735</v>
+        <v>81.16419710000001</v>
       </c>
       <c r="N99">
-        <v>276.5370598333333</v>
+        <v>284.1691362333333</v>
       </c>
       <c r="O99">
-        <v>68.96834272243333</v>
+        <v>70.87178257659333</v>
       </c>
       <c r="P99">
-        <v>207.5687171109</v>
+        <v>213.29735365674</v>
       </c>
       <c r="Q99">
-        <v>256.5687171109</v>
+        <v>262.29735365674</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>0.6642617884637808</v>
+        <v>0.6638641725215646</v>
       </c>
       <c r="T99">
         <v>14.2739993653941</v>
       </c>
       <c r="U99">
-        <v>0.06050000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V99">
         <v>0.2494</v>
       </c>
       <c r="W99">
-        <v>0.0454113</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y99">
-        <v>4.114286770529096</v>
+        <v>4.50116364587722</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9436,13 +9436,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.06391188767273349</v>
+        <v>0.0619139108377478</v>
       </c>
       <c r="C100">
-        <v>195.3985526789395</v>
+        <v>243.9816620080692</v>
       </c>
       <c r="D100">
-        <v>1624.336552678939</v>
+        <v>1672.919662008069</v>
       </c>
       <c r="E100">
         <v>476.838</v>
@@ -9469,37 +9469,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M100">
-        <v>89.71169900000001</v>
+        <v>85.7080364</v>
       </c>
       <c r="N100">
-        <v>275.6216343333333</v>
+        <v>279.6252969333333</v>
       </c>
       <c r="O100">
-        <v>68.74003560273333</v>
+        <v>69.73854905517332</v>
       </c>
       <c r="P100">
-        <v>206.8815987306</v>
+        <v>209.88674787816</v>
       </c>
       <c r="Q100">
-        <v>255.8815987306</v>
+        <v>258.88674787816</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>0.9704406836366736</v>
+        <v>0.9698462218873893</v>
       </c>
       <c r="T100">
         <v>21.3405593969374</v>
       </c>
       <c r="U100">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V100">
         <v>0.2494</v>
       </c>
       <c r="W100">
-        <v>0.0454113</v>
+        <v>0.04338468</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9507,7 +9507,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.072304252462471</v>
+        <v>4.262532997819715</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9518,13 +9518,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.06384696069155354</v>
+        <v>0.06182875689984866</v>
       </c>
       <c r="C101">
-        <v>181.8119898632781</v>
+        <v>230.9999672722111</v>
       </c>
       <c r="D101">
-        <v>1625.880989863278</v>
+        <v>1675.068967272211</v>
       </c>
       <c r="E101">
         <v>491.9689999999998</v>
@@ -9551,37 +9551,37 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M101">
-        <v>90.62712449999999</v>
+        <v>86.5826082</v>
       </c>
       <c r="N101">
-        <v>274.7062088333333</v>
+        <v>278.7507251333333</v>
       </c>
       <c r="O101">
-        <v>68.51172848303334</v>
+        <v>69.52043084825334</v>
       </c>
       <c r="P101">
-        <v>206.1944803503</v>
+        <v>209.23029428508</v>
       </c>
       <c r="Q101">
-        <v>255.1944803503</v>
+        <v>258.23029428508</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>1.888977369155352</v>
+        <v>1.887792369984864</v>
       </c>
       <c r="T101">
         <v>42.54023949156729</v>
       </c>
       <c r="U101">
-        <v>0.06050000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V101">
         <v>0.2494</v>
       </c>
       <c r="W101">
-        <v>0.0454113</v>
+        <v>0.04338468</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>4.031169866073963</v>
+        <v>4.21947710895285</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/luxembourg/luxembourg_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_hospitals_healthcare_facilities.xlsx
@@ -1260,7 +1260,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1397,22 +1397,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07025899675186452</v>
+        <v>0.07011754781396537</v>
       </c>
       <c r="C2">
-        <v>1539.955310042646</v>
+        <v>1527.643200872283</v>
       </c>
       <c r="D2">
-        <v>1486.055310042646</v>
+        <v>1488.874200872283</v>
       </c>
       <c r="E2">
-        <v>-1006</v>
+        <v>-990.869</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>15.131</v>
       </c>
       <c r="G2">
         <v>53.9</v>
@@ -1433,28 +1433,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.7610893000000001</v>
       </c>
       <c r="N2">
-        <v>365.3333333333333</v>
+        <v>364.5722440333333</v>
       </c>
       <c r="O2">
-        <v>91.11413333333333</v>
+        <v>90.92431766191334</v>
       </c>
       <c r="P2">
-        <v>274.2192</v>
+        <v>273.64792637142</v>
       </c>
       <c r="Q2">
-        <v>323.2192</v>
+        <v>322.64792637142</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07025899675186452</v>
+        <v>0.07044444041814683</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.569155667855585</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1471,7 +1471,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>480.013755722664</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07011754781396537</v>
+        <v>0.06997609887606622</v>
       </c>
       <c r="C3">
-        <v>1527.643200872283</v>
+        <v>1515.341806306019</v>
       </c>
       <c r="D3">
-        <v>1488.874200872283</v>
+        <v>1491.703806306019</v>
       </c>
       <c r="E3">
-        <v>-990.869</v>
+        <v>-975.7380000000001</v>
       </c>
       <c r="F3">
-        <v>15.131</v>
+        <v>30.262</v>
       </c>
       <c r="G3">
         <v>53.9</v>
@@ -1515,28 +1515,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M3">
-        <v>0.7610893000000001</v>
+        <v>1.5221786</v>
       </c>
       <c r="N3">
-        <v>364.5722440333333</v>
+        <v>363.8111547333333</v>
       </c>
       <c r="O3">
-        <v>90.92431766191334</v>
+        <v>90.73450199049333</v>
       </c>
       <c r="P3">
-        <v>273.64792637142</v>
+        <v>273.07665274284</v>
       </c>
       <c r="Q3">
-        <v>322.64792637142</v>
+        <v>322.07665274284</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07044444041814683</v>
+        <v>0.07063366864904716</v>
       </c>
       <c r="T3">
-        <v>0.569155667855585</v>
+        <v>0.5735258348509736</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>480.013755722664</v>
+        <v>240.006877861332</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06997609887606622</v>
+        <v>0.06983464993816706</v>
       </c>
       <c r="C4">
-        <v>1515.341806306019</v>
+        <v>1503.051187549493</v>
       </c>
       <c r="D4">
-        <v>1491.703806306019</v>
+        <v>1494.544187549493</v>
       </c>
       <c r="E4">
-        <v>-975.7380000000001</v>
+        <v>-960.607</v>
       </c>
       <c r="F4">
-        <v>30.262</v>
+        <v>45.39299999999999</v>
       </c>
       <c r="G4">
         <v>53.9</v>
@@ -1597,28 +1597,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M4">
-        <v>1.5221786</v>
+        <v>2.2832679</v>
       </c>
       <c r="N4">
-        <v>363.8111547333333</v>
+        <v>363.0500654333333</v>
       </c>
       <c r="O4">
-        <v>90.73450199049333</v>
+        <v>90.54468631907334</v>
       </c>
       <c r="P4">
-        <v>273.07665274284</v>
+        <v>272.50537911426</v>
       </c>
       <c r="Q4">
-        <v>322.07665274284</v>
+        <v>321.50537911426</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07063366864904716</v>
+        <v>0.07082679849295573</v>
       </c>
       <c r="T4">
-        <v>0.5735258348509736</v>
+        <v>0.5779861083823495</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>240.006877861332</v>
+        <v>160.004585240888</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1643,22 +1643,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.06983464993816706</v>
+        <v>0.06969320100026791</v>
       </c>
       <c r="C5">
-        <v>1503.051187549493</v>
+        <v>1490.771406275401</v>
       </c>
       <c r="D5">
-        <v>1494.544187549493</v>
+        <v>1497.395406275401</v>
       </c>
       <c r="E5">
-        <v>-960.607</v>
+        <v>-945.476</v>
       </c>
       <c r="F5">
-        <v>45.39299999999999</v>
+        <v>60.524</v>
       </c>
       <c r="G5">
         <v>53.9</v>
@@ -1679,28 +1679,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M5">
-        <v>2.2832679</v>
+        <v>3.0443572</v>
       </c>
       <c r="N5">
-        <v>363.0500654333333</v>
+        <v>362.2889761333333</v>
       </c>
       <c r="O5">
-        <v>90.54468631907334</v>
+        <v>90.35487064765334</v>
       </c>
       <c r="P5">
-        <v>272.50537911426</v>
+        <v>271.93410548568</v>
       </c>
       <c r="Q5">
-        <v>321.50537911426</v>
+        <v>320.93410548568</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07082679849295573</v>
+        <v>0.07102395187527907</v>
       </c>
       <c r="T5">
-        <v>0.5779861083823495</v>
+        <v>0.5825393042789625</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>160.004585240888</v>
+        <v>120.003438930666</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06969320100026791</v>
+        <v>0.06955175206236876</v>
       </c>
       <c r="C6">
-        <v>1490.771406275401</v>
+        <v>1478.502524627966</v>
       </c>
       <c r="D6">
-        <v>1497.395406275401</v>
+        <v>1500.257524627965</v>
       </c>
       <c r="E6">
-        <v>-945.476</v>
+        <v>-930.345</v>
       </c>
       <c r="F6">
-        <v>60.524</v>
+        <v>75.655</v>
       </c>
       <c r="G6">
         <v>53.9</v>
@@ -1761,28 +1761,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M6">
-        <v>3.0443572</v>
+        <v>3.8054465</v>
       </c>
       <c r="N6">
-        <v>362.2889761333333</v>
+        <v>361.5278868333333</v>
       </c>
       <c r="O6">
-        <v>90.35487064765334</v>
+        <v>90.16505497623332</v>
       </c>
       <c r="P6">
-        <v>271.93410548568</v>
+        <v>271.3628318571</v>
       </c>
       <c r="Q6">
-        <v>320.93410548568</v>
+        <v>320.3628318571</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07102395187527907</v>
+        <v>0.07122525585512501</v>
       </c>
       <c r="T6">
-        <v>0.5825393042789625</v>
+        <v>0.5871883569312937</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1799,7 +1799,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>120.003438930666</v>
+        <v>96.00275114453278</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1807,22 +1807,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06955175206236876</v>
+        <v>0.06941030312446961</v>
       </c>
       <c r="C7">
-        <v>1478.502524627966</v>
+        <v>1466.244605227447</v>
       </c>
       <c r="D7">
-        <v>1500.257524627965</v>
+        <v>1503.130605227447</v>
       </c>
       <c r="E7">
-        <v>-930.345</v>
+        <v>-915.2139999999999</v>
       </c>
       <c r="F7">
-        <v>75.655</v>
+        <v>90.786</v>
       </c>
       <c r="G7">
         <v>53.9</v>
@@ -1843,28 +1843,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M7">
-        <v>3.8054465</v>
+        <v>4.5665358</v>
       </c>
       <c r="N7">
-        <v>361.5278868333333</v>
+        <v>360.7667975333333</v>
       </c>
       <c r="O7">
-        <v>90.16505497623332</v>
+        <v>89.97523930481333</v>
       </c>
       <c r="P7">
-        <v>271.3628318571</v>
+        <v>270.79155822852</v>
       </c>
       <c r="Q7">
-        <v>320.3628318571</v>
+        <v>319.79155822852</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07122525585512501</v>
+        <v>0.07143084289837193</v>
       </c>
       <c r="T7">
-        <v>0.5871883569312937</v>
+        <v>0.5919363255975041</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>96.00275114453278</v>
+        <v>80.00229262044398</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1889,22 +1889,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06941030312446961</v>
+        <v>0.06926885418657047</v>
       </c>
       <c r="C8">
-        <v>1466.244605227447</v>
+        <v>1453.997711174713</v>
       </c>
       <c r="D8">
-        <v>1503.130605227447</v>
+        <v>1506.014711174713</v>
       </c>
       <c r="E8">
-        <v>-915.2140000000001</v>
+        <v>-900.083</v>
       </c>
       <c r="F8">
-        <v>90.78599999999999</v>
+        <v>105.917</v>
       </c>
       <c r="G8">
         <v>53.9</v>
@@ -1925,28 +1925,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M8">
-        <v>4.5665358</v>
+        <v>5.3276251</v>
       </c>
       <c r="N8">
-        <v>360.7667975333333</v>
+        <v>360.0057082333333</v>
       </c>
       <c r="O8">
-        <v>89.97523930481333</v>
+        <v>89.78542363339334</v>
       </c>
       <c r="P8">
-        <v>270.79155822852</v>
+        <v>270.22028459994</v>
       </c>
       <c r="Q8">
-        <v>319.79155822852</v>
+        <v>319.22028459994</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07143084289837193</v>
+        <v>0.07164085116835534</v>
       </c>
       <c r="T8">
-        <v>0.5919363255975041</v>
+        <v>0.5967864011167515</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1963,7 +1963,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>80.00229262044401</v>
+        <v>68.57339367466629</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1971,22 +1971,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.06926885418657046</v>
+        <v>0.06912740524867132</v>
       </c>
       <c r="C9">
-        <v>1453.997711174713</v>
+        <v>1441.761906055856</v>
       </c>
       <c r="D9">
-        <v>1506.014711174713</v>
+        <v>1508.909906055856</v>
       </c>
       <c r="E9">
-        <v>-900.083</v>
+        <v>-884.952</v>
       </c>
       <c r="F9">
-        <v>105.917</v>
+        <v>121.048</v>
       </c>
       <c r="G9">
         <v>53.9</v>
@@ -2007,28 +2007,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M9">
-        <v>5.327625100000001</v>
+        <v>6.088714400000001</v>
       </c>
       <c r="N9">
-        <v>360.0057082333333</v>
+        <v>359.2446189333333</v>
       </c>
       <c r="O9">
-        <v>89.78542363339334</v>
+        <v>89.59560796197333</v>
       </c>
       <c r="P9">
-        <v>270.22028459994</v>
+        <v>269.64901097136</v>
       </c>
       <c r="Q9">
-        <v>319.22028459994</v>
+        <v>318.64901097136</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07164085116835534</v>
+        <v>0.0718554248355123</v>
       </c>
       <c r="T9">
-        <v>0.5967864011167515</v>
+        <v>0.6017419130603302</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2045,7 +2045,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>68.57339367466628</v>
+        <v>60.00171946533299</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06912740524867132</v>
+        <v>0.06898595631077217</v>
       </c>
       <c r="C10">
-        <v>1441.761906055856</v>
+        <v>1429.537253946868</v>
       </c>
       <c r="D10">
-        <v>1508.909906055856</v>
+        <v>1511.816253946868</v>
       </c>
       <c r="E10">
-        <v>-884.952</v>
+        <v>-869.821</v>
       </c>
       <c r="F10">
-        <v>121.048</v>
+        <v>136.179</v>
       </c>
       <c r="G10">
         <v>53.9</v>
@@ -2089,28 +2089,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M10">
-        <v>6.088714400000001</v>
+        <v>6.849803699999999</v>
       </c>
       <c r="N10">
-        <v>359.2446189333333</v>
+        <v>358.4835296333333</v>
       </c>
       <c r="O10">
-        <v>89.59560796197333</v>
+        <v>89.40579229055334</v>
       </c>
       <c r="P10">
-        <v>269.64901097136</v>
+        <v>269.07773734278</v>
       </c>
       <c r="Q10">
-        <v>318.64901097136</v>
+        <v>318.07773734278</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0718554248355123</v>
+        <v>0.07207471440744194</v>
       </c>
       <c r="T10">
-        <v>0.6017419130603302</v>
+        <v>0.6068063373543173</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>60.00171946533299</v>
+        <v>53.33486174696267</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2135,22 +2135,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06898595631077217</v>
+        <v>0.06884450737287302</v>
       </c>
       <c r="C11">
-        <v>1429.537253946868</v>
+        <v>1417.323819418367</v>
       </c>
       <c r="D11">
-        <v>1511.816253946868</v>
+        <v>1514.733819418367</v>
       </c>
       <c r="E11">
-        <v>-869.821</v>
+        <v>-854.6900000000001</v>
       </c>
       <c r="F11">
-        <v>136.179</v>
+        <v>151.31</v>
       </c>
       <c r="G11">
         <v>53.9</v>
@@ -2171,28 +2171,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M11">
-        <v>6.849803699999999</v>
+        <v>7.610892999999999</v>
       </c>
       <c r="N11">
-        <v>358.4835296333333</v>
+        <v>357.7224403333333</v>
       </c>
       <c r="O11">
-        <v>89.40579229055334</v>
+        <v>89.21597661913334</v>
       </c>
       <c r="P11">
-        <v>269.07773734278</v>
+        <v>268.5064637142</v>
       </c>
       <c r="Q11">
-        <v>318.07773734278</v>
+        <v>317.5064637142</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07207471440744194</v>
+        <v>0.07229887708097002</v>
       </c>
       <c r="T11">
-        <v>0.6068063373543173</v>
+        <v>0.6119833044103929</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2209,7 +2209,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>53.33486174696267</v>
+        <v>48.0013755722664</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2217,22 +2217,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06884450737287302</v>
+        <v>0.06870305843497387</v>
       </c>
       <c r="C12">
-        <v>1417.323819418367</v>
+        <v>1405.121667540379</v>
       </c>
       <c r="D12">
-        <v>1514.733819418367</v>
+        <v>1517.662667540379</v>
       </c>
       <c r="E12">
-        <v>-854.6900000000001</v>
+        <v>-839.559</v>
       </c>
       <c r="F12">
-        <v>151.31</v>
+        <v>166.441</v>
       </c>
       <c r="G12">
         <v>53.9</v>
@@ -2253,28 +2253,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M12">
-        <v>7.610893000000001</v>
+        <v>8.371982300000001</v>
       </c>
       <c r="N12">
-        <v>357.7224403333333</v>
+        <v>356.9613510333333</v>
       </c>
       <c r="O12">
-        <v>89.21597661913334</v>
+        <v>89.02616094771332</v>
       </c>
       <c r="P12">
-        <v>268.5064637142</v>
+        <v>267.93519008562</v>
       </c>
       <c r="Q12">
-        <v>317.5064637142</v>
+        <v>316.93519008562</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07229887708097002</v>
+        <v>0.07252807711794816</v>
       </c>
       <c r="T12">
-        <v>0.6119833044103929</v>
+        <v>0.6172766078048074</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>48.0013755722664</v>
+        <v>43.63761415660581</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2299,22 +2299,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06870305843497387</v>
+        <v>0.06856160949707471</v>
       </c>
       <c r="C13">
-        <v>1405.121667540379</v>
+        <v>1392.930863887175</v>
       </c>
       <c r="D13">
-        <v>1517.662667540379</v>
+        <v>1520.602863887175</v>
       </c>
       <c r="E13">
-        <v>-839.559</v>
+        <v>-824.428</v>
       </c>
       <c r="F13">
-        <v>166.441</v>
+        <v>181.572</v>
       </c>
       <c r="G13">
         <v>53.9</v>
@@ -2335,28 +2335,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M13">
-        <v>8.371982300000001</v>
+        <v>9.133071599999999</v>
       </c>
       <c r="N13">
-        <v>356.9613510333333</v>
+        <v>356.2002617333333</v>
       </c>
       <c r="O13">
-        <v>89.02616094771332</v>
+        <v>88.83634527629333</v>
       </c>
       <c r="P13">
-        <v>267.93519008562</v>
+        <v>267.36391645704</v>
       </c>
       <c r="Q13">
-        <v>316.93519008562</v>
+        <v>316.36391645704</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07252807711794816</v>
+        <v>0.07276248624667581</v>
       </c>
       <c r="T13">
-        <v>0.6172766078048074</v>
+        <v>0.6226902135490949</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>43.63761415660581</v>
+        <v>40.001146310222</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2381,22 +2381,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06856160949707471</v>
+        <v>0.06842016055917557</v>
       </c>
       <c r="C14">
-        <v>1392.930863887175</v>
+        <v>1380.751474542164</v>
       </c>
       <c r="D14">
-        <v>1520.602863887175</v>
+        <v>1523.554474542164</v>
       </c>
       <c r="E14">
-        <v>-824.428</v>
+        <v>-809.297</v>
       </c>
       <c r="F14">
-        <v>181.572</v>
+        <v>196.703</v>
       </c>
       <c r="G14">
         <v>53.9</v>
@@ -2417,28 +2417,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M14">
-        <v>9.133071599999999</v>
+        <v>9.894160900000001</v>
       </c>
       <c r="N14">
-        <v>356.2002617333333</v>
+        <v>355.4391724333333</v>
       </c>
       <c r="O14">
-        <v>88.83634527629333</v>
+        <v>88.64652960487334</v>
       </c>
       <c r="P14">
-        <v>267.36391645704</v>
+        <v>266.79264282846</v>
       </c>
       <c r="Q14">
-        <v>316.36391645704</v>
+        <v>315.79264282846</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07276248624667581</v>
+        <v>0.0730022840910064</v>
       </c>
       <c r="T14">
-        <v>0.6226902135490949</v>
+        <v>0.6282282700001477</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>40.001146310222</v>
+        <v>36.92413505558954</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2463,22 +2463,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06842016055917557</v>
+        <v>0.06827871162127641</v>
       </c>
       <c r="C15">
-        <v>1380.751474542164</v>
+        <v>1368.58356610285</v>
       </c>
       <c r="D15">
-        <v>1523.554474542164</v>
+        <v>1526.51756610285</v>
       </c>
       <c r="E15">
-        <v>-809.297</v>
+        <v>-794.1659999999999</v>
       </c>
       <c r="F15">
-        <v>196.703</v>
+        <v>211.834</v>
       </c>
       <c r="G15">
         <v>53.9</v>
@@ -2499,28 +2499,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M15">
-        <v>9.894160900000001</v>
+        <v>10.6552502</v>
       </c>
       <c r="N15">
-        <v>355.4391724333333</v>
+        <v>354.6780831333333</v>
       </c>
       <c r="O15">
-        <v>88.64652960487334</v>
+        <v>88.45671393345333</v>
       </c>
       <c r="P15">
-        <v>266.79264282846</v>
+        <v>266.22136919988</v>
       </c>
       <c r="Q15">
-        <v>315.79264282846</v>
+        <v>315.22136919988</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0730022840910064</v>
+        <v>0.07324765862939119</v>
       </c>
       <c r="T15">
-        <v>0.6282282700001477</v>
+        <v>0.6338951184616901</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>36.92413505558954</v>
+        <v>34.28669683733314</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2545,22 +2545,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06827871162127641</v>
+        <v>0.06813726268337726</v>
       </c>
       <c r="C16">
-        <v>1368.58356610285</v>
+        <v>1356.427205685832</v>
       </c>
       <c r="D16">
-        <v>1526.51756610285</v>
+        <v>1529.492205685832</v>
       </c>
       <c r="E16">
-        <v>-794.1659999999999</v>
+        <v>-779.035</v>
       </c>
       <c r="F16">
-        <v>211.834</v>
+        <v>226.965</v>
       </c>
       <c r="G16">
         <v>53.9</v>
@@ -2581,28 +2581,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M16">
-        <v>10.6552502</v>
+        <v>11.4163395</v>
       </c>
       <c r="N16">
-        <v>354.6780831333333</v>
+        <v>353.9169938333333</v>
       </c>
       <c r="O16">
-        <v>88.45671393345333</v>
+        <v>88.26689826203334</v>
       </c>
       <c r="P16">
-        <v>266.22136919988</v>
+        <v>265.6500955713</v>
       </c>
       <c r="Q16">
-        <v>315.22136919988</v>
+        <v>314.6500955713</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07324765862939119</v>
+        <v>0.07349880668632619</v>
       </c>
       <c r="T16">
-        <v>0.6338951184616901</v>
+        <v>0.6396953045340922</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>34.28669683733314</v>
+        <v>32.00091704817759</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06813726268337726</v>
+        <v>0.06799581374547811</v>
       </c>
       <c r="C17">
-        <v>1356.427205685832</v>
+        <v>1344.282460931877</v>
       </c>
       <c r="D17">
-        <v>1529.492205685832</v>
+        <v>1532.478460931877</v>
       </c>
       <c r="E17">
-        <v>-779.0350000000001</v>
+        <v>-763.904</v>
       </c>
       <c r="F17">
-        <v>226.965</v>
+        <v>242.096</v>
       </c>
       <c r="G17">
         <v>53.9</v>
@@ -2663,28 +2663,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M17">
-        <v>11.4163395</v>
+        <v>12.1774288</v>
       </c>
       <c r="N17">
-        <v>353.9169938333333</v>
+        <v>353.1559045333333</v>
       </c>
       <c r="O17">
-        <v>88.26689826203334</v>
+        <v>88.07708259061334</v>
       </c>
       <c r="P17">
-        <v>265.6500955713</v>
+        <v>265.07882194272</v>
       </c>
       <c r="Q17">
-        <v>314.6500955713</v>
+        <v>314.07882194272</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07349880668632619</v>
+        <v>0.07375593445890252</v>
       </c>
       <c r="T17">
-        <v>0.6396953045340922</v>
+        <v>0.6456335902748849</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>32.0009170481776</v>
+        <v>30.0008597326665</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2709,22 +2709,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06799581374547811</v>
+        <v>0.06785436480757895</v>
       </c>
       <c r="C18">
-        <v>1344.282460931877</v>
+        <v>1332.149400011048</v>
       </c>
       <c r="D18">
-        <v>1532.478460931877</v>
+        <v>1535.476400011048</v>
       </c>
       <c r="E18">
-        <v>-763.904</v>
+        <v>-748.773</v>
       </c>
       <c r="F18">
-        <v>242.096</v>
+        <v>257.227</v>
       </c>
       <c r="G18">
         <v>53.9</v>
@@ -2745,28 +2745,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M18">
-        <v>12.1774288</v>
+        <v>12.9385181</v>
       </c>
       <c r="N18">
-        <v>353.1559045333333</v>
+        <v>352.3948152333333</v>
       </c>
       <c r="O18">
-        <v>88.07708259061334</v>
+        <v>87.88726691919332</v>
       </c>
       <c r="P18">
-        <v>265.07882194272</v>
+        <v>264.50754831414</v>
       </c>
       <c r="Q18">
-        <v>314.07882194272</v>
+        <v>313.50754831414</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07375593445890252</v>
+        <v>0.07401925808142043</v>
       </c>
       <c r="T18">
-        <v>0.6456335902748849</v>
+        <v>0.6517149672383473</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2783,7 +2783,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>30.0008597326665</v>
+        <v>28.23610327780376</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2791,22 +2791,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06785436480757895</v>
+        <v>0.06771291586967981</v>
       </c>
       <c r="C19">
-        <v>1332.149400011048</v>
+        <v>1320.028091627886</v>
       </c>
       <c r="D19">
-        <v>1535.476400011048</v>
+        <v>1538.486091627886</v>
       </c>
       <c r="E19">
-        <v>-748.773</v>
+        <v>-733.6420000000001</v>
       </c>
       <c r="F19">
-        <v>257.227</v>
+        <v>272.358</v>
       </c>
       <c r="G19">
         <v>53.9</v>
@@ -2827,28 +2827,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M19">
-        <v>12.9385181</v>
+        <v>13.6996074</v>
       </c>
       <c r="N19">
-        <v>352.3948152333333</v>
+        <v>351.6337259333333</v>
       </c>
       <c r="O19">
-        <v>87.88726691919332</v>
+        <v>87.69745124777333</v>
       </c>
       <c r="P19">
-        <v>264.50754831414</v>
+        <v>263.93627468556</v>
       </c>
       <c r="Q19">
-        <v>313.50754831414</v>
+        <v>312.93627468556</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07401925808142043</v>
+        <v>0.07428900423131685</v>
       </c>
       <c r="T19">
-        <v>0.6517149672383473</v>
+        <v>0.6579446704692112</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2865,7 +2865,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>28.23610327780376</v>
+        <v>26.66743087348133</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2873,22 +2873,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06771291586967981</v>
+        <v>0.06757146693178066</v>
       </c>
       <c r="C20">
-        <v>1320.028091627886</v>
+        <v>1307.918605026663</v>
       </c>
       <c r="D20">
-        <v>1538.486091627886</v>
+        <v>1541.507605026663</v>
       </c>
       <c r="E20">
-        <v>-733.6420000000001</v>
+        <v>-718.511</v>
       </c>
       <c r="F20">
-        <v>272.3579999999999</v>
+        <v>287.489</v>
       </c>
       <c r="G20">
         <v>53.9</v>
@@ -2909,28 +2909,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M20">
-        <v>13.6996074</v>
+        <v>14.4606967</v>
       </c>
       <c r="N20">
-        <v>351.6337259333333</v>
+        <v>350.8726366333333</v>
       </c>
       <c r="O20">
-        <v>87.69745124777333</v>
+        <v>87.50763557635332</v>
       </c>
       <c r="P20">
-        <v>263.93627468556</v>
+        <v>263.36500105698</v>
       </c>
       <c r="Q20">
-        <v>312.93627468556</v>
+        <v>312.36500105698</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07428900423131685</v>
+        <v>0.07456541077997612</v>
       </c>
       <c r="T20">
-        <v>0.6579446704692112</v>
+        <v>0.6643281935329359</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>26.66743087348134</v>
+        <v>25.26388188014021</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2955,22 +2955,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06757146693178066</v>
+        <v>0.06743001799388151</v>
       </c>
       <c r="C21">
-        <v>1307.918605026663</v>
+        <v>1295.821009996694</v>
       </c>
       <c r="D21">
-        <v>1541.507605026663</v>
+        <v>1544.541009996694</v>
       </c>
       <c r="E21">
-        <v>-718.511</v>
+        <v>-703.38</v>
       </c>
       <c r="F21">
-        <v>287.489</v>
+        <v>302.62</v>
       </c>
       <c r="G21">
         <v>53.9</v>
@@ -2991,28 +2991,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M21">
-        <v>14.4606967</v>
+        <v>15.221786</v>
       </c>
       <c r="N21">
-        <v>350.8726366333333</v>
+        <v>350.1115473333333</v>
       </c>
       <c r="O21">
-        <v>87.50763557635332</v>
+        <v>87.31781990493333</v>
       </c>
       <c r="P21">
-        <v>263.36500105698</v>
+        <v>262.7937274284</v>
       </c>
       <c r="Q21">
-        <v>312.36500105698</v>
+        <v>311.7937274284</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07456541077997612</v>
+        <v>0.07484872749235189</v>
       </c>
       <c r="T21">
-        <v>0.6643281935329359</v>
+        <v>0.6708713046732538</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>25.26388188014021</v>
+        <v>24.0006877861332</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3037,22 +3037,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06743001799388151</v>
+        <v>0.06728856905598238</v>
       </c>
       <c r="C22">
-        <v>1295.821009996694</v>
+        <v>1283.735376877703</v>
       </c>
       <c r="D22">
-        <v>1544.541009996694</v>
+        <v>1547.586376877703</v>
       </c>
       <c r="E22">
-        <v>-703.38</v>
+        <v>-688.249</v>
       </c>
       <c r="F22">
-        <v>302.62</v>
+        <v>317.751</v>
       </c>
       <c r="G22">
         <v>53.9</v>
@@ -3073,28 +3073,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M22">
-        <v>15.221786</v>
+        <v>15.9828753</v>
       </c>
       <c r="N22">
-        <v>350.1115473333333</v>
+        <v>349.3504580333333</v>
       </c>
       <c r="O22">
-        <v>87.31781990493333</v>
+        <v>87.12800423351334</v>
       </c>
       <c r="P22">
-        <v>262.7937274284</v>
+        <v>262.22245379982</v>
       </c>
       <c r="Q22">
-        <v>311.7937274284</v>
+        <v>311.22245379982</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07484872749235189</v>
+        <v>0.07513921677972452</v>
       </c>
       <c r="T22">
-        <v>0.6708713046732538</v>
+        <v>0.6775800641968709</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3111,7 +3111,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.0006877861332</v>
+        <v>22.85779789155542</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3119,22 +3119,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06728856905598238</v>
+        <v>0.06714712011808321</v>
       </c>
       <c r="C23">
-        <v>1283.735376877703</v>
+        <v>1271.661776565268</v>
       </c>
       <c r="D23">
-        <v>1547.586376877703</v>
+        <v>1550.643776565268</v>
       </c>
       <c r="E23">
-        <v>-688.249</v>
+        <v>-673.1179999999999</v>
       </c>
       <c r="F23">
-        <v>317.751</v>
+        <v>332.882</v>
       </c>
       <c r="G23">
         <v>53.9</v>
@@ -3155,28 +3155,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M23">
-        <v>15.9828753</v>
+        <v>16.7439646</v>
       </c>
       <c r="N23">
-        <v>349.3504580333333</v>
+        <v>348.5893687333333</v>
       </c>
       <c r="O23">
-        <v>87.12800423351334</v>
+        <v>86.93818856209333</v>
       </c>
       <c r="P23">
-        <v>262.22245379982</v>
+        <v>261.65118017124</v>
       </c>
       <c r="Q23">
-        <v>311.22245379982</v>
+        <v>310.65118017124</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07513921677972452</v>
+        <v>0.07543715451036309</v>
       </c>
       <c r="T23">
-        <v>0.6775800641968709</v>
+        <v>0.6844608431954525</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>22.85779789155543</v>
+        <v>21.8188070783029</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3201,22 +3201,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06714712011808321</v>
+        <v>0.06700567118018406</v>
       </c>
       <c r="C24">
-        <v>1271.661776565268</v>
+        <v>1259.600280516318</v>
       </c>
       <c r="D24">
-        <v>1550.643776565268</v>
+        <v>1553.713280516318</v>
       </c>
       <c r="E24">
-        <v>-673.1179999999999</v>
+        <v>-657.9870000000001</v>
       </c>
       <c r="F24">
-        <v>332.882</v>
+        <v>348.013</v>
       </c>
       <c r="G24">
         <v>53.9</v>
@@ -3237,28 +3237,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M24">
-        <v>16.7439646</v>
+        <v>17.5050539</v>
       </c>
       <c r="N24">
-        <v>348.5893687333333</v>
+        <v>347.8282794333333</v>
       </c>
       <c r="O24">
-        <v>86.93818856209333</v>
+        <v>86.74837289067334</v>
       </c>
       <c r="P24">
-        <v>261.65118017124</v>
+        <v>261.07990654266</v>
       </c>
       <c r="Q24">
-        <v>310.65118017124</v>
+        <v>310.07990654266</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07543715451036309</v>
+        <v>0.07574283088335593</v>
       </c>
       <c r="T24">
-        <v>0.6844608431954525</v>
+        <v>0.6915203437264649</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3275,7 +3275,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>21.8188070783029</v>
+        <v>20.87016329228974</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3283,22 +3283,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06700567118018406</v>
+        <v>0.06686422224228492</v>
       </c>
       <c r="C25">
-        <v>1259.600280516318</v>
+        <v>1247.550960754699</v>
       </c>
       <c r="D25">
-        <v>1553.713280516318</v>
+        <v>1556.794960754699</v>
       </c>
       <c r="E25">
-        <v>-657.9870000000001</v>
+        <v>-642.856</v>
       </c>
       <c r="F25">
-        <v>348.013</v>
+        <v>363.144</v>
       </c>
       <c r="G25">
         <v>53.9</v>
@@ -3319,28 +3319,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M25">
-        <v>17.5050539</v>
+        <v>18.2661432</v>
       </c>
       <c r="N25">
-        <v>347.8282794333333</v>
+        <v>347.0671901333333</v>
       </c>
       <c r="O25">
-        <v>86.74837289067334</v>
+        <v>86.55855721925333</v>
       </c>
       <c r="P25">
-        <v>261.07990654266</v>
+        <v>260.50863291408</v>
       </c>
       <c r="Q25">
-        <v>310.07990654266</v>
+        <v>309.50863291408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07574283088335593</v>
+        <v>0.07605655137142751</v>
       </c>
       <c r="T25">
-        <v>0.6915203437264649</v>
+        <v>0.6987656205872406</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3357,7 +3357,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>20.87016329228974</v>
+        <v>20.000573155111</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3365,22 +3365,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06686422224228492</v>
+        <v>0.06672277330438577</v>
       </c>
       <c r="C26">
-        <v>1247.550960754699</v>
+        <v>1235.513889876813</v>
       </c>
       <c r="D26">
-        <v>1556.794960754699</v>
+        <v>1559.888889876813</v>
       </c>
       <c r="E26">
-        <v>-642.856</v>
+        <v>-627.725</v>
       </c>
       <c r="F26">
-        <v>363.1439999999999</v>
+        <v>378.275</v>
       </c>
       <c r="G26">
         <v>53.9</v>
@@ -3401,28 +3401,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M26">
-        <v>18.2661432</v>
+        <v>19.0272325</v>
       </c>
       <c r="N26">
-        <v>347.0671901333333</v>
+        <v>346.3061008333333</v>
       </c>
       <c r="O26">
-        <v>86.55855721925333</v>
+        <v>86.36874154783332</v>
       </c>
       <c r="P26">
-        <v>260.50863291408</v>
+        <v>259.9373592855</v>
       </c>
       <c r="Q26">
-        <v>309.50863291408</v>
+        <v>308.9373592855</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07605655137142751</v>
+        <v>0.07637863773918102</v>
       </c>
       <c r="T26">
-        <v>0.6987656205872406</v>
+        <v>0.7062041048309704</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3439,7 +3439,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.000573155111</v>
+        <v>19.20055022890656</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3447,22 +3447,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06672277330438577</v>
+        <v>0.06658132436648662</v>
       </c>
       <c r="C27">
-        <v>1235.513889876813</v>
+        <v>1223.489141057312</v>
       </c>
       <c r="D27">
-        <v>1559.888889876813</v>
+        <v>1562.995141057311</v>
       </c>
       <c r="E27">
-        <v>-627.725</v>
+        <v>-612.5940000000001</v>
       </c>
       <c r="F27">
-        <v>378.275</v>
+        <v>393.406</v>
       </c>
       <c r="G27">
         <v>53.9</v>
@@ -3483,28 +3483,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M27">
-        <v>19.0272325</v>
+        <v>19.7883218</v>
       </c>
       <c r="N27">
-        <v>346.3061008333333</v>
+        <v>345.5450115333333</v>
       </c>
       <c r="O27">
-        <v>86.36874154783332</v>
+        <v>86.17892587641333</v>
       </c>
       <c r="P27">
-        <v>259.9373592855</v>
+        <v>259.3660856569199</v>
       </c>
       <c r="Q27">
-        <v>308.9373592855</v>
+        <v>308.3660856569199</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07637863773918102</v>
+        <v>0.07670942914390083</v>
       </c>
       <c r="T27">
-        <v>0.7062041048309704</v>
+        <v>0.7138436291893956</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.20055022890656</v>
+        <v>18.46206752779477</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06658132436648662</v>
+        <v>0.06643987542858745</v>
       </c>
       <c r="C28">
-        <v>1223.489141057312</v>
+        <v>1211.476788054872</v>
       </c>
       <c r="D28">
-        <v>1562.995141057311</v>
+        <v>1566.113788054872</v>
       </c>
       <c r="E28">
-        <v>-612.5940000000001</v>
+        <v>-597.463</v>
       </c>
       <c r="F28">
-        <v>393.406</v>
+        <v>408.537</v>
       </c>
       <c r="G28">
         <v>53.9</v>
@@ -3565,28 +3565,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M28">
-        <v>19.7883218</v>
+        <v>20.5494111</v>
       </c>
       <c r="N28">
-        <v>345.5450115333333</v>
+        <v>344.7839222333333</v>
       </c>
       <c r="O28">
-        <v>86.17892587641333</v>
+        <v>85.98911020499334</v>
       </c>
       <c r="P28">
-        <v>259.3660856569199</v>
+        <v>258.79481202834</v>
       </c>
       <c r="Q28">
-        <v>308.3660856569199</v>
+        <v>307.79481202834</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07670942914390083</v>
+        <v>0.07704928332683214</v>
       </c>
       <c r="T28">
-        <v>0.7138436291893956</v>
+        <v>0.7216924555850378</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>18.46206752779477</v>
+        <v>17.77828724898756</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3611,22 +3611,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06643987542858745</v>
+        <v>0.06629842649068832</v>
       </c>
       <c r="C29">
-        <v>1211.476788054872</v>
+        <v>1199.476905218028</v>
       </c>
       <c r="D29">
-        <v>1566.113788054872</v>
+        <v>1569.244905218027</v>
       </c>
       <c r="E29">
-        <v>-597.463</v>
+        <v>-582.332</v>
       </c>
       <c r="F29">
-        <v>408.537</v>
+        <v>423.668</v>
       </c>
       <c r="G29">
         <v>53.9</v>
@@ -3647,28 +3647,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M29">
-        <v>20.5494111</v>
+        <v>21.3105004</v>
       </c>
       <c r="N29">
-        <v>344.7839222333333</v>
+        <v>344.0228329333333</v>
       </c>
       <c r="O29">
-        <v>85.98911020499334</v>
+        <v>85.79929453357333</v>
       </c>
       <c r="P29">
-        <v>258.79481202834</v>
+        <v>258.2235383997599</v>
       </c>
       <c r="Q29">
-        <v>307.79481202834</v>
+        <v>307.2235383997599</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07704928332683214</v>
+        <v>0.07739857790373376</v>
       </c>
       <c r="T29">
-        <v>0.7216924555850378</v>
+        <v>0.7297593049361147</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>17.77828724898756</v>
+        <v>17.14334841866657</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06629842649068832</v>
+        <v>0.06615697755278917</v>
       </c>
       <c r="C30">
-        <v>1199.476905218028</v>
+        <v>1187.489567491084</v>
       </c>
       <c r="D30">
-        <v>1569.244905218027</v>
+        <v>1572.388567491084</v>
       </c>
       <c r="E30">
-        <v>-582.332</v>
+        <v>-567.201</v>
       </c>
       <c r="F30">
-        <v>423.668</v>
+        <v>438.799</v>
       </c>
       <c r="G30">
         <v>53.9</v>
@@ -3729,28 +3729,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M30">
-        <v>21.3105004</v>
+        <v>22.0715897</v>
       </c>
       <c r="N30">
-        <v>344.0228329333333</v>
+        <v>343.2617436333333</v>
       </c>
       <c r="O30">
-        <v>85.79929453357333</v>
+        <v>85.60947886215334</v>
       </c>
       <c r="P30">
-        <v>258.2235383997599</v>
+        <v>257.6522647711799</v>
       </c>
       <c r="Q30">
-        <v>307.2235383997599</v>
+        <v>306.6522647711799</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07739857790373376</v>
+        <v>0.07775771176449178</v>
       </c>
       <c r="T30">
-        <v>0.7297593049361147</v>
+        <v>0.7380533894801797</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3767,7 +3767,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.14334841866657</v>
+        <v>16.5521984731953</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3775,22 +3775,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06615697755278917</v>
+        <v>0.06601552861489002</v>
       </c>
       <c r="C31">
-        <v>1187.489567491084</v>
+        <v>1175.514850420093</v>
       </c>
       <c r="D31">
-        <v>1572.388567491084</v>
+        <v>1575.544850420093</v>
       </c>
       <c r="E31">
-        <v>-567.201</v>
+        <v>-552.0700000000001</v>
       </c>
       <c r="F31">
-        <v>438.7989999999999</v>
+        <v>453.9299999999999</v>
       </c>
       <c r="G31">
         <v>53.9</v>
@@ -3811,28 +3811,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M31">
-        <v>22.0715897</v>
+        <v>22.832679</v>
       </c>
       <c r="N31">
-        <v>343.2617436333333</v>
+        <v>342.5006543333333</v>
       </c>
       <c r="O31">
-        <v>85.60947886215334</v>
+        <v>85.41966319073333</v>
       </c>
       <c r="P31">
-        <v>257.6522647711799</v>
+        <v>257.0809911426</v>
       </c>
       <c r="Q31">
-        <v>306.6522647711799</v>
+        <v>306.0809911426</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07775771176449178</v>
+        <v>0.07812710659270003</v>
       </c>
       <c r="T31">
-        <v>0.7380533894801796</v>
+        <v>0.7465844478683608</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>16.55219847319531</v>
+        <v>16.0004585240888</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3857,22 +3857,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06601552861489002</v>
+        <v>0.06587407967699085</v>
       </c>
       <c r="C32">
-        <v>1175.514850420093</v>
+        <v>1163.552830158907</v>
       </c>
       <c r="D32">
-        <v>1575.544850420093</v>
+        <v>1578.713830158907</v>
       </c>
       <c r="E32">
-        <v>-552.0700000000001</v>
+        <v>-536.9390000000001</v>
       </c>
       <c r="F32">
-        <v>453.9299999999999</v>
+        <v>469.061</v>
       </c>
       <c r="G32">
         <v>53.9</v>
@@ -3893,28 +3893,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M32">
-        <v>22.832679</v>
+        <v>23.5937683</v>
       </c>
       <c r="N32">
-        <v>342.5006543333333</v>
+        <v>341.7395650333333</v>
       </c>
       <c r="O32">
-        <v>85.41966319073333</v>
+        <v>85.22984751931332</v>
       </c>
       <c r="P32">
-        <v>257.0809911426</v>
+        <v>256.5097175140199</v>
       </c>
       <c r="Q32">
-        <v>306.0809911426</v>
+        <v>305.5097175140199</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07812710659270003</v>
+        <v>0.07850720851737805</v>
       </c>
       <c r="T32">
-        <v>0.7465844478683608</v>
+        <v>0.7553627833112716</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3931,7 +3931,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.0004585240888</v>
+        <v>15.48431470073109</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3939,22 +3939,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06587407967699085</v>
+        <v>0.0657326307390917</v>
       </c>
       <c r="C33">
-        <v>1163.552830158907</v>
+        <v>1151.603583475301</v>
       </c>
       <c r="D33">
-        <v>1578.713830158907</v>
+        <v>1581.895583475301</v>
       </c>
       <c r="E33">
-        <v>-536.9390000000001</v>
+        <v>-521.808</v>
       </c>
       <c r="F33">
-        <v>469.061</v>
+        <v>484.192</v>
       </c>
       <c r="G33">
         <v>53.9</v>
@@ -3975,28 +3975,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M33">
-        <v>23.5937683</v>
+        <v>24.3548576</v>
       </c>
       <c r="N33">
-        <v>341.7395650333333</v>
+        <v>340.9784757333333</v>
       </c>
       <c r="O33">
-        <v>85.22984751931332</v>
+        <v>85.04003184789333</v>
       </c>
       <c r="P33">
-        <v>256.5097175140199</v>
+        <v>255.93844388544</v>
       </c>
       <c r="Q33">
-        <v>305.5097175140199</v>
+        <v>304.93844388544</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07850720851737805</v>
+        <v>0.07889848991042898</v>
       </c>
       <c r="T33">
-        <v>0.7553627833112716</v>
+        <v>0.7643993050907387</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4013,7 +4013,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>15.48431470073109</v>
+        <v>15.00042986633325</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4021,22 +4021,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0657326307390917</v>
+        <v>0.06559118180119256</v>
       </c>
       <c r="C34">
-        <v>1151.603583475301</v>
+        <v>1139.667187757176</v>
       </c>
       <c r="D34">
-        <v>1581.895583475301</v>
+        <v>1585.090187757175</v>
       </c>
       <c r="E34">
-        <v>-521.808</v>
+        <v>-506.677</v>
       </c>
       <c r="F34">
-        <v>484.192</v>
+        <v>499.323</v>
       </c>
       <c r="G34">
         <v>53.9</v>
@@ -4057,28 +4057,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M34">
-        <v>24.3548576</v>
+        <v>25.1159469</v>
       </c>
       <c r="N34">
-        <v>340.9784757333333</v>
+        <v>340.2173864333333</v>
       </c>
       <c r="O34">
-        <v>85.04003184789333</v>
+        <v>84.85021617647334</v>
       </c>
       <c r="P34">
-        <v>255.93844388544</v>
+        <v>255.36717025686</v>
       </c>
       <c r="Q34">
-        <v>304.93844388544</v>
+        <v>304.36717025686</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07889848991042898</v>
+        <v>0.07930145134506353</v>
       </c>
       <c r="T34">
-        <v>0.7643993050907387</v>
+        <v>0.773705573788996</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4095,7 +4095,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.00042986633325</v>
+        <v>14.54587138553527</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4103,22 +4103,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06559118180119256</v>
+        <v>0.06544973286329341</v>
       </c>
       <c r="C35">
-        <v>1139.667187757176</v>
+        <v>1127.743721018828</v>
       </c>
       <c r="D35">
-        <v>1585.090187757175</v>
+        <v>1588.297721018828</v>
       </c>
       <c r="E35">
-        <v>-506.677</v>
+        <v>-491.546</v>
       </c>
       <c r="F35">
-        <v>499.323</v>
+        <v>514.454</v>
       </c>
       <c r="G35">
         <v>53.9</v>
@@ -4139,28 +4139,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M35">
-        <v>25.1159469</v>
+        <v>25.8770362</v>
       </c>
       <c r="N35">
-        <v>340.2173864333333</v>
+        <v>339.4562971333333</v>
       </c>
       <c r="O35">
-        <v>84.85021617647334</v>
+        <v>84.66040050505333</v>
       </c>
       <c r="P35">
-        <v>255.36717025686</v>
+        <v>254.79589662828</v>
       </c>
       <c r="Q35">
-        <v>304.36717025686</v>
+        <v>303.7958966282799</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07930145134506353</v>
+        <v>0.07971662373226274</v>
       </c>
       <c r="T35">
-        <v>0.773705573788996</v>
+        <v>0.7832938506296246</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4177,7 +4177,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>14.54587138553527</v>
+        <v>14.11805163890188</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4185,22 +4185,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06544973286329341</v>
+        <v>0.06530828392539426</v>
       </c>
       <c r="C36">
-        <v>1127.743721018828</v>
+        <v>1115.833261907304</v>
       </c>
       <c r="D36">
-        <v>1588.297721018828</v>
+        <v>1591.518261907304</v>
       </c>
       <c r="E36">
-        <v>-491.546</v>
+        <v>-476.415</v>
       </c>
       <c r="F36">
-        <v>514.454</v>
+        <v>529.585</v>
       </c>
       <c r="G36">
         <v>53.9</v>
@@ -4221,28 +4221,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M36">
-        <v>25.8770362</v>
+        <v>26.6381255</v>
       </c>
       <c r="N36">
-        <v>339.4562971333333</v>
+        <v>338.6952078333333</v>
       </c>
       <c r="O36">
-        <v>84.66040050505333</v>
+        <v>84.47058483363334</v>
       </c>
       <c r="P36">
-        <v>254.79589662828</v>
+        <v>254.2246229997</v>
       </c>
       <c r="Q36">
-        <v>303.7958966282799</v>
+        <v>303.2246229997</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07971662373226274</v>
+        <v>0.08014457065445271</v>
       </c>
       <c r="T36">
-        <v>0.7832938506296246</v>
+        <v>0.7931771513730418</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.11805163890188</v>
+        <v>13.71467873493325</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4267,22 +4267,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06530828392539426</v>
+        <v>0.06516683498749511</v>
       </c>
       <c r="C37">
-        <v>1115.833261907304</v>
+        <v>1103.935889708828</v>
       </c>
       <c r="D37">
-        <v>1591.518261907304</v>
+        <v>1594.751889708828</v>
       </c>
       <c r="E37">
-        <v>-476.415</v>
+        <v>-461.284</v>
       </c>
       <c r="F37">
-        <v>529.585</v>
+        <v>544.716</v>
       </c>
       <c r="G37">
         <v>53.9</v>
@@ -4303,28 +4303,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M37">
-        <v>26.6381255</v>
+        <v>27.3992148</v>
       </c>
       <c r="N37">
-        <v>338.6952078333333</v>
+        <v>337.9341185333333</v>
       </c>
       <c r="O37">
-        <v>84.47058483363334</v>
+        <v>84.28076916221333</v>
       </c>
       <c r="P37">
-        <v>254.2246229997</v>
+        <v>253.65334937112</v>
       </c>
       <c r="Q37">
-        <v>303.2246229997</v>
+        <v>302.65334937112</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08014457065445271</v>
+        <v>0.08058589091796112</v>
       </c>
       <c r="T37">
-        <v>0.7931771513730418</v>
+        <v>0.8033693052646909</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>13.71467873493325</v>
+        <v>13.33371543674066</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4349,22 +4349,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06516683498749512</v>
+        <v>0.06502538604959596</v>
       </c>
       <c r="C38">
-        <v>1103.935889708828</v>
+        <v>1092.051684355303</v>
       </c>
       <c r="D38">
-        <v>1594.751889708828</v>
+        <v>1597.998684355303</v>
       </c>
       <c r="E38">
-        <v>-461.2840000000001</v>
+        <v>-446.153</v>
       </c>
       <c r="F38">
-        <v>544.7159999999999</v>
+        <v>559.847</v>
       </c>
       <c r="G38">
         <v>53.9</v>
@@ -4385,28 +4385,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M38">
-        <v>27.3992148</v>
+        <v>28.1603041</v>
       </c>
       <c r="N38">
-        <v>337.9341185333333</v>
+        <v>337.1730292333333</v>
       </c>
       <c r="O38">
-        <v>84.28076916221333</v>
+        <v>84.09095349079332</v>
       </c>
       <c r="P38">
-        <v>253.65334937112</v>
+        <v>253.08207574254</v>
       </c>
       <c r="Q38">
-        <v>302.65334937112</v>
+        <v>302.08207574254</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08058589091796112</v>
+        <v>0.08104122134856501</v>
       </c>
       <c r="T38">
-        <v>0.8033693052646909</v>
+        <v>0.8138850195973445</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.33371543674067</v>
+        <v>12.97334474926119</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4431,22 +4431,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06502538604959596</v>
+        <v>0.0653117791116968</v>
       </c>
       <c r="C39">
-        <v>1092.051684355303</v>
+        <v>1070.360525362837</v>
       </c>
       <c r="D39">
-        <v>1597.998684355303</v>
+        <v>1591.438525362837</v>
       </c>
       <c r="E39">
-        <v>-446.153</v>
+        <v>-431.022</v>
       </c>
       <c r="F39">
-        <v>559.847</v>
+        <v>574.978</v>
       </c>
       <c r="G39">
         <v>53.9</v>
@@ -4467,45 +4467,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M39">
-        <v>28.1603041</v>
+        <v>29.7838604</v>
       </c>
       <c r="N39">
-        <v>337.1730292333333</v>
+        <v>335.5494729333333</v>
       </c>
       <c r="O39">
-        <v>84.09095349079332</v>
+        <v>83.68603854957334</v>
       </c>
       <c r="P39">
-        <v>253.08207574254</v>
+        <v>251.86343438376</v>
       </c>
       <c r="Q39">
-        <v>302.08207574254</v>
+        <v>300.86343438376</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08104122134856501</v>
+        <v>0.0815112398575755</v>
       </c>
       <c r="T39">
-        <v>0.8138850195973445</v>
+        <v>0.8247399505213742</v>
       </c>
       <c r="U39">
-        <v>0.0503</v>
+        <v>0.05180000000000001</v>
       </c>
       <c r="V39">
         <v>0.2494</v>
       </c>
       <c r="W39">
-        <v>0.03775518</v>
+        <v>0.03888108</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y39">
-        <v>12.97334474926119</v>
+        <v>12.26615114450823</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4513,22 +4513,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0653117791116968</v>
+        <v>0.06518158917379765</v>
       </c>
       <c r="C40">
-        <v>1070.360525362837</v>
+        <v>1058.204984356567</v>
       </c>
       <c r="D40">
-        <v>1591.438525362837</v>
+        <v>1594.413984356567</v>
       </c>
       <c r="E40">
-        <v>-431.022</v>
+        <v>-415.891</v>
       </c>
       <c r="F40">
-        <v>574.978</v>
+        <v>590.109</v>
       </c>
       <c r="G40">
         <v>53.9</v>
@@ -4549,28 +4549,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M40">
-        <v>29.7838604</v>
+        <v>30.56764620000001</v>
       </c>
       <c r="N40">
-        <v>335.5494729333333</v>
+        <v>334.7656871333333</v>
       </c>
       <c r="O40">
-        <v>83.68603854957334</v>
+        <v>83.49056237105333</v>
       </c>
       <c r="P40">
-        <v>251.86343438376</v>
+        <v>251.27512476228</v>
       </c>
       <c r="Q40">
-        <v>300.86343438376</v>
+        <v>300.27512476228</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.0815112398575755</v>
+        <v>0.08199666880950436</v>
       </c>
       <c r="T40">
-        <v>0.8247399505213742</v>
+        <v>0.8359507808199622</v>
       </c>
       <c r="U40">
         <v>0.05180000000000001</v>
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>12.26615114450823</v>
+        <v>11.9516344484952</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4595,22 +4595,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06518158917379765</v>
+        <v>0.0650513992358985</v>
       </c>
       <c r="C41">
-        <v>1058.204984356567</v>
+        <v>1046.060590422471</v>
       </c>
       <c r="D41">
-        <v>1594.413984356567</v>
+        <v>1597.400590422471</v>
       </c>
       <c r="E41">
-        <v>-415.891</v>
+        <v>-400.76</v>
       </c>
       <c r="F41">
-        <v>590.109</v>
+        <v>605.24</v>
       </c>
       <c r="G41">
         <v>53.9</v>
@@ -4631,28 +4631,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M41">
-        <v>30.56764620000001</v>
+        <v>31.351432</v>
       </c>
       <c r="N41">
-        <v>334.7656871333333</v>
+        <v>333.9819013333333</v>
       </c>
       <c r="O41">
-        <v>83.49056237105333</v>
+        <v>83.29508619253333</v>
       </c>
       <c r="P41">
-        <v>251.27512476228</v>
+        <v>250.6868151408</v>
       </c>
       <c r="Q41">
-        <v>300.27512476228</v>
+        <v>299.6868151408</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08199666880950436</v>
+        <v>0.08249827872649751</v>
       </c>
       <c r="T41">
-        <v>0.8359507808199622</v>
+        <v>0.8475353054618364</v>
       </c>
       <c r="U41">
         <v>0.05180000000000001</v>
@@ -4669,7 +4669,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>11.9516344484952</v>
+        <v>11.65284358728282</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4677,22 +4677,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0650513992358985</v>
+        <v>0.06492120929799937</v>
       </c>
       <c r="C42">
-        <v>1046.060590422471</v>
+        <v>1033.92740631914</v>
       </c>
       <c r="D42">
-        <v>1597.400590422471</v>
+        <v>1600.39840631914</v>
       </c>
       <c r="E42">
-        <v>-400.76</v>
+        <v>-385.629</v>
       </c>
       <c r="F42">
-        <v>605.24</v>
+        <v>620.371</v>
       </c>
       <c r="G42">
         <v>53.9</v>
@@ -4713,28 +4713,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M42">
-        <v>31.351432</v>
+        <v>32.1352178</v>
       </c>
       <c r="N42">
-        <v>333.9819013333333</v>
+        <v>333.1981155333333</v>
       </c>
       <c r="O42">
-        <v>83.29508619253333</v>
+        <v>83.09961001401332</v>
       </c>
       <c r="P42">
-        <v>250.6868151408</v>
+        <v>250.09850551932</v>
       </c>
       <c r="Q42">
-        <v>299.6868151408</v>
+        <v>299.09850551932</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08249827872649751</v>
+        <v>0.08301689236949045</v>
       </c>
       <c r="T42">
-        <v>0.8475353054618364</v>
+        <v>0.8595125258542828</v>
       </c>
       <c r="U42">
         <v>0.05180000000000001</v>
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>11.65284358728282</v>
+        <v>11.36862789003202</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06492120929799937</v>
+        <v>0.0647910193601002</v>
       </c>
       <c r="C43">
-        <v>1033.92740631914</v>
+        <v>1021.805495277164</v>
       </c>
       <c r="D43">
-        <v>1600.39840631914</v>
+        <v>1603.407495277164</v>
       </c>
       <c r="E43">
-        <v>-385.629</v>
+        <v>-370.4979999999999</v>
       </c>
       <c r="F43">
-        <v>620.371</v>
+        <v>635.5020000000001</v>
       </c>
       <c r="G43">
         <v>53.9</v>
@@ -4795,28 +4795,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M43">
-        <v>32.1352178</v>
+        <v>32.91900360000001</v>
       </c>
       <c r="N43">
-        <v>333.1981155333333</v>
+        <v>332.4143297333333</v>
       </c>
       <c r="O43">
-        <v>83.09961001401332</v>
+        <v>82.90413383549333</v>
       </c>
       <c r="P43">
-        <v>250.09850551932</v>
+        <v>249.51019589784</v>
       </c>
       <c r="Q43">
-        <v>299.09850551932</v>
+        <v>298.51019589784</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08301689236949045</v>
+        <v>0.08355338924155209</v>
       </c>
       <c r="T43">
-        <v>0.8595125258542828</v>
+        <v>0.8719027538464685</v>
       </c>
       <c r="U43">
         <v>0.05180000000000001</v>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.36862789003202</v>
+        <v>11.09794627360268</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4841,22 +4841,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06479101936010022</v>
+        <v>0.06466082942220105</v>
       </c>
       <c r="C44">
-        <v>1021.805495277164</v>
+        <v>1009.694921003574</v>
       </c>
       <c r="D44">
-        <v>1603.407495277163</v>
+        <v>1606.427921003574</v>
       </c>
       <c r="E44">
-        <v>-370.498</v>
+        <v>-355.3670000000001</v>
       </c>
       <c r="F44">
-        <v>635.502</v>
+        <v>650.6329999999999</v>
       </c>
       <c r="G44">
         <v>53.9</v>
@@ -4877,28 +4877,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M44">
-        <v>32.9190036</v>
+        <v>33.7027894</v>
       </c>
       <c r="N44">
-        <v>332.4143297333333</v>
+        <v>331.6305439333333</v>
       </c>
       <c r="O44">
-        <v>82.90413383549333</v>
+        <v>82.70865765697334</v>
       </c>
       <c r="P44">
-        <v>249.51019589784</v>
+        <v>248.92188627636</v>
       </c>
       <c r="Q44">
-        <v>298.51019589784</v>
+        <v>297.92188627636</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08355338924155209</v>
+        <v>0.084108710565265</v>
       </c>
       <c r="T44">
-        <v>0.8719027538464684</v>
+        <v>0.8847277266804853</v>
       </c>
       <c r="U44">
         <v>0.05180000000000001</v>
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.09794627360268</v>
+        <v>10.83985449979797</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4923,22 +4923,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06466082942220105</v>
+        <v>0.0645306394843019</v>
       </c>
       <c r="C45">
-        <v>1009.694921003574</v>
+        <v>997.595747686344</v>
       </c>
       <c r="D45">
-        <v>1606.427921003574</v>
+        <v>1609.459747686344</v>
       </c>
       <c r="E45">
-        <v>-355.3670000000001</v>
+        <v>-340.236</v>
       </c>
       <c r="F45">
-        <v>650.6329999999999</v>
+        <v>665.764</v>
       </c>
       <c r="G45">
         <v>53.9</v>
@@ -4959,28 +4959,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M45">
-        <v>33.7027894</v>
+        <v>34.4865752</v>
       </c>
       <c r="N45">
-        <v>331.6305439333333</v>
+        <v>330.8467581333333</v>
       </c>
       <c r="O45">
-        <v>82.70865765697334</v>
+        <v>82.51318147845333</v>
       </c>
       <c r="P45">
-        <v>248.92188627636</v>
+        <v>248.33357665488</v>
       </c>
       <c r="Q45">
-        <v>297.92188627636</v>
+        <v>297.3335766548799</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.084108710565265</v>
+        <v>0.08468386479339626</v>
       </c>
       <c r="T45">
-        <v>0.8847277266804853</v>
+        <v>0.8980107342585743</v>
       </c>
       <c r="U45">
         <v>0.05180000000000001</v>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>10.83985449979797</v>
+        <v>10.59349417025711</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5005,22 +5005,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0645306394843019</v>
+        <v>0.06440044954640275</v>
       </c>
       <c r="C46">
-        <v>997.595747686344</v>
+        <v>985.5080399989311</v>
       </c>
       <c r="D46">
-        <v>1609.459747686344</v>
+        <v>1612.503039998931</v>
       </c>
       <c r="E46">
-        <v>-340.236</v>
+        <v>-325.105</v>
       </c>
       <c r="F46">
-        <v>665.764</v>
+        <v>680.895</v>
       </c>
       <c r="G46">
         <v>53.9</v>
@@ -5041,28 +5041,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M46">
-        <v>34.4865752</v>
+        <v>35.270361</v>
       </c>
       <c r="N46">
-        <v>330.8467581333333</v>
+        <v>330.0629723333333</v>
       </c>
       <c r="O46">
-        <v>82.51318147845333</v>
+        <v>82.31770529993334</v>
       </c>
       <c r="P46">
-        <v>248.33357665488</v>
+        <v>247.7452670334</v>
       </c>
       <c r="Q46">
-        <v>297.3335766548799</v>
+        <v>296.7452670334</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08468386479339626</v>
+        <v>0.08527993372073228</v>
       </c>
       <c r="T46">
-        <v>0.8980107342585743</v>
+        <v>0.9117767602940483</v>
       </c>
       <c r="U46">
         <v>0.05180000000000001</v>
@@ -5079,7 +5079,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>10.59349417025711</v>
+        <v>10.35808318869584</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5087,22 +5087,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06440044954640275</v>
+        <v>0.0642702596085036</v>
       </c>
       <c r="C47">
-        <v>985.5080399989311</v>
+        <v>973.4318631048801</v>
       </c>
       <c r="D47">
-        <v>1612.503039998931</v>
+        <v>1615.55786310488</v>
       </c>
       <c r="E47">
-        <v>-325.105</v>
+        <v>-309.974</v>
       </c>
       <c r="F47">
-        <v>680.895</v>
+        <v>696.026</v>
       </c>
       <c r="G47">
         <v>53.9</v>
@@ -5123,28 +5123,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M47">
-        <v>35.270361</v>
+        <v>36.05414680000001</v>
       </c>
       <c r="N47">
-        <v>330.0629723333333</v>
+        <v>329.2791865333333</v>
       </c>
       <c r="O47">
-        <v>82.31770529993334</v>
+        <v>82.12222912141333</v>
       </c>
       <c r="P47">
-        <v>247.7452670334</v>
+        <v>247.15695741192</v>
       </c>
       <c r="Q47">
-        <v>296.7452670334</v>
+        <v>296.15695741192</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08527993372073228</v>
+        <v>0.08589807927500669</v>
       </c>
       <c r="T47">
-        <v>0.9117767602940483</v>
+        <v>0.9260526391456509</v>
       </c>
       <c r="U47">
         <v>0.05180000000000001</v>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.35808318869584</v>
+        <v>10.13290746720245</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5169,22 +5169,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0642702596085036</v>
+        <v>0.06414006967060445</v>
       </c>
       <c r="C48">
-        <v>973.4318631048801</v>
+        <v>961.367282662471</v>
       </c>
       <c r="D48">
-        <v>1615.55786310488</v>
+        <v>1618.624282662471</v>
       </c>
       <c r="E48">
-        <v>-309.974</v>
+        <v>-294.843</v>
       </c>
       <c r="F48">
-        <v>696.026</v>
+        <v>711.157</v>
       </c>
       <c r="G48">
         <v>53.9</v>
@@ -5205,28 +5205,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M48">
-        <v>36.05414680000001</v>
+        <v>36.83793260000001</v>
       </c>
       <c r="N48">
-        <v>329.2791865333333</v>
+        <v>328.4954007333333</v>
       </c>
       <c r="O48">
-        <v>82.12222912141333</v>
+        <v>81.92675294289333</v>
       </c>
       <c r="P48">
-        <v>247.15695741192</v>
+        <v>246.56864779044</v>
       </c>
       <c r="Q48">
-        <v>296.15695741192</v>
+        <v>295.56864779044</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08589807927500669</v>
+        <v>0.08653955107661218</v>
       </c>
       <c r="T48">
-        <v>0.9260526391456509</v>
+        <v>0.940867230406748</v>
       </c>
       <c r="U48">
         <v>0.05180000000000001</v>
@@ -5243,7 +5243,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.13290746720245</v>
+        <v>9.917313691304523</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5251,22 +5251,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06414006967060445</v>
+        <v>0.06462236933270532</v>
       </c>
       <c r="C49">
-        <v>961.367282662471</v>
+        <v>934.9343793347555</v>
       </c>
       <c r="D49">
-        <v>1618.624282662471</v>
+        <v>1607.322379334755</v>
       </c>
       <c r="E49">
-        <v>-294.843</v>
+        <v>-279.712</v>
       </c>
       <c r="F49">
-        <v>711.157</v>
+        <v>726.288</v>
       </c>
       <c r="G49">
         <v>53.9</v>
@@ -5287,45 +5287,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M49">
-        <v>36.83793260000001</v>
+        <v>38.856408</v>
       </c>
       <c r="N49">
-        <v>328.4954007333333</v>
+        <v>326.4769253333333</v>
       </c>
       <c r="O49">
-        <v>81.92675294289333</v>
+        <v>81.42334517813333</v>
       </c>
       <c r="P49">
-        <v>246.56864779044</v>
+        <v>245.0535801552</v>
       </c>
       <c r="Q49">
-        <v>295.56864779044</v>
+        <v>294.0535801552</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08653955107661218</v>
+        <v>0.08720569487058713</v>
       </c>
       <c r="T49">
-        <v>0.940867230406748</v>
+        <v>0.9562516136394257</v>
       </c>
       <c r="U49">
-        <v>0.05180000000000001</v>
+        <v>0.05350000000000001</v>
       </c>
       <c r="V49">
         <v>0.2494</v>
       </c>
       <c r="W49">
-        <v>0.03888108</v>
+        <v>0.0401571</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>9.917313691304523</v>
+        <v>9.402138595346573</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5333,22 +5333,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06462236933270532</v>
+        <v>0.06450493959480616</v>
       </c>
       <c r="C50">
-        <v>934.9343793347556</v>
+        <v>922.5405925075762</v>
       </c>
       <c r="D50">
-        <v>1607.322379334755</v>
+        <v>1610.059592507576</v>
       </c>
       <c r="E50">
-        <v>-279.7120000000001</v>
+        <v>-264.581</v>
       </c>
       <c r="F50">
-        <v>726.2879999999999</v>
+        <v>741.419</v>
       </c>
       <c r="G50">
         <v>53.9</v>
@@ -5369,28 +5369,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M50">
-        <v>38.856408</v>
+        <v>39.6659165</v>
       </c>
       <c r="N50">
-        <v>326.4769253333333</v>
+        <v>325.6674168333333</v>
       </c>
       <c r="O50">
-        <v>81.42334517813333</v>
+        <v>81.22145375823334</v>
       </c>
       <c r="P50">
-        <v>245.0535801552</v>
+        <v>244.4459630751</v>
       </c>
       <c r="Q50">
-        <v>294.0535801552</v>
+        <v>293.4459630751</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08720569487058713</v>
+        <v>0.08789796195060032</v>
       </c>
       <c r="T50">
-        <v>0.9562516136394256</v>
+        <v>0.972239306018483</v>
       </c>
       <c r="U50">
         <v>0.05350000000000001</v>
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>9.402138595346573</v>
+        <v>9.210258215849704</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5415,22 +5415,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06450493959480616</v>
+        <v>0.06438750985690701</v>
       </c>
       <c r="C51">
-        <v>922.5405925075762</v>
+        <v>910.1561443382768</v>
       </c>
       <c r="D51">
-        <v>1610.059592507576</v>
+        <v>1612.806144338277</v>
       </c>
       <c r="E51">
-        <v>-264.581</v>
+        <v>-249.45</v>
       </c>
       <c r="F51">
-        <v>741.419</v>
+        <v>756.55</v>
       </c>
       <c r="G51">
         <v>53.9</v>
@@ -5451,28 +5451,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M51">
-        <v>39.6659165</v>
+        <v>40.475425</v>
       </c>
       <c r="N51">
-        <v>325.6674168333333</v>
+        <v>324.8579083333333</v>
       </c>
       <c r="O51">
-        <v>81.22145375823334</v>
+        <v>81.01956233833333</v>
       </c>
       <c r="P51">
-        <v>244.4459630751</v>
+        <v>243.8383459949999</v>
       </c>
       <c r="Q51">
-        <v>293.4459630751</v>
+        <v>292.8383459949999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08789796195060032</v>
+        <v>0.08861791971381403</v>
       </c>
       <c r="T51">
-        <v>0.972239306018483</v>
+        <v>0.9888665060927025</v>
       </c>
       <c r="U51">
         <v>0.05350000000000001</v>
@@ -5489,7 +5489,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>9.210258215849704</v>
+        <v>9.026053051532708</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5497,22 +5497,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06438750985690701</v>
+        <v>0.06427008011900787</v>
       </c>
       <c r="C52">
-        <v>910.1561443382768</v>
+        <v>897.7810827001236</v>
       </c>
       <c r="D52">
-        <v>1612.806144338277</v>
+        <v>1615.562082700123</v>
       </c>
       <c r="E52">
-        <v>-249.45</v>
+        <v>-234.3190000000001</v>
       </c>
       <c r="F52">
-        <v>756.55</v>
+        <v>771.6809999999999</v>
       </c>
       <c r="G52">
         <v>53.9</v>
@@ -5533,28 +5533,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M52">
-        <v>40.475425</v>
+        <v>41.2849335</v>
       </c>
       <c r="N52">
-        <v>324.8579083333333</v>
+        <v>324.0483998333333</v>
       </c>
       <c r="O52">
-        <v>81.01956233833333</v>
+        <v>80.81767091843332</v>
       </c>
       <c r="P52">
-        <v>243.8383459949999</v>
+        <v>243.2307289149</v>
       </c>
       <c r="Q52">
-        <v>292.8383459949999</v>
+        <v>292.2307289148999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08861791971381403</v>
+        <v>0.08936726350817931</v>
       </c>
       <c r="T52">
-        <v>0.9888665060927025</v>
+        <v>1.006172367394441</v>
       </c>
       <c r="U52">
         <v>0.05350000000000001</v>
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.026053051532708</v>
+        <v>8.849071619149715</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5579,22 +5579,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06427008011900787</v>
+        <v>0.06415265038110871</v>
       </c>
       <c r="C53">
-        <v>897.7810827001236</v>
+        <v>885.4154557941621</v>
       </c>
       <c r="D53">
-        <v>1615.562082700123</v>
+        <v>1618.327455794162</v>
       </c>
       <c r="E53">
-        <v>-234.3190000000001</v>
+        <v>-219.188</v>
       </c>
       <c r="F53">
-        <v>771.6809999999999</v>
+        <v>786.812</v>
       </c>
       <c r="G53">
         <v>53.9</v>
@@ -5615,28 +5615,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M53">
-        <v>41.2849335</v>
+        <v>42.09444200000001</v>
       </c>
       <c r="N53">
-        <v>324.0483998333333</v>
+        <v>323.2388913333333</v>
       </c>
       <c r="O53">
-        <v>80.81767091843332</v>
+        <v>80.61577949853333</v>
       </c>
       <c r="P53">
-        <v>243.2307289149</v>
+        <v>242.6231118348</v>
       </c>
       <c r="Q53">
-        <v>292.2307289148999</v>
+        <v>291.6231118347999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08936726350817931</v>
+        <v>0.09014782996064315</v>
       </c>
       <c r="T53">
-        <v>1.006172367394441</v>
+        <v>1.024199306250419</v>
       </c>
       <c r="U53">
         <v>0.05350000000000001</v>
@@ -5653,7 +5653,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>8.849071619149715</v>
+        <v>8.678897164935297</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5661,22 +5661,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06415265038110871</v>
+        <v>0.06403522064320956</v>
       </c>
       <c r="C54">
-        <v>885.4154557941621</v>
+        <v>873.0593121520287</v>
       </c>
       <c r="D54">
-        <v>1618.327455794162</v>
+        <v>1621.102312152029</v>
       </c>
       <c r="E54">
-        <v>-219.188</v>
+        <v>-204.057</v>
       </c>
       <c r="F54">
-        <v>786.812</v>
+        <v>801.943</v>
       </c>
       <c r="G54">
         <v>53.9</v>
@@ -5697,28 +5697,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M54">
-        <v>42.09444200000001</v>
+        <v>42.9039505</v>
       </c>
       <c r="N54">
-        <v>323.2388913333333</v>
+        <v>322.4293828333333</v>
       </c>
       <c r="O54">
-        <v>80.61577949853333</v>
+        <v>80.41388807863333</v>
       </c>
       <c r="P54">
-        <v>242.6231118348</v>
+        <v>242.0154947547</v>
       </c>
       <c r="Q54">
-        <v>291.6231118347999</v>
+        <v>291.0154947546999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09014782996064315</v>
+        <v>0.09096161200682885</v>
       </c>
       <c r="T54">
-        <v>1.024199306250419</v>
+        <v>1.042993348887503</v>
       </c>
       <c r="U54">
         <v>0.05350000000000001</v>
@@ -5735,7 +5735,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>8.678897164935297</v>
+        <v>8.515144388238404</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5743,22 +5743,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06403522064320956</v>
+        <v>0.06391779090531041</v>
       </c>
       <c r="C55">
-        <v>873.0593121520287</v>
+        <v>860.7127006387897</v>
       </c>
       <c r="D55">
-        <v>1621.102312152029</v>
+        <v>1623.88670063879</v>
       </c>
       <c r="E55">
-        <v>-204.057</v>
+        <v>-188.926</v>
       </c>
       <c r="F55">
-        <v>801.943</v>
+        <v>817.074</v>
       </c>
       <c r="G55">
         <v>53.9</v>
@@ -5779,28 +5779,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M55">
-        <v>42.9039505</v>
+        <v>43.713459</v>
       </c>
       <c r="N55">
-        <v>322.4293828333333</v>
+        <v>321.6198743333333</v>
       </c>
       <c r="O55">
-        <v>80.41388807863333</v>
+        <v>80.21199665873333</v>
       </c>
       <c r="P55">
-        <v>242.0154947547</v>
+        <v>241.4078776746</v>
       </c>
       <c r="Q55">
-        <v>291.0154947546999</v>
+        <v>290.4078776746</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09096161200682885</v>
+        <v>0.09181077588110959</v>
       </c>
       <c r="T55">
-        <v>1.042993348887503</v>
+        <v>1.062604523813155</v>
       </c>
       <c r="U55">
         <v>0.05350000000000001</v>
@@ -5817,7 +5817,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.515144388238404</v>
+        <v>8.357456529196952</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06391779090531041</v>
+        <v>0.06380036116741125</v>
       </c>
       <c r="C56">
-        <v>860.7127006387897</v>
+        <v>848.3756704558099</v>
       </c>
       <c r="D56">
-        <v>1623.88670063879</v>
+        <v>1626.68067045581</v>
       </c>
       <c r="E56">
-        <v>-188.926</v>
+        <v>-173.795</v>
       </c>
       <c r="F56">
-        <v>817.074</v>
+        <v>832.205</v>
       </c>
       <c r="G56">
         <v>53.9</v>
@@ -5861,28 +5861,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M56">
-        <v>43.713459</v>
+        <v>44.52296750000001</v>
       </c>
       <c r="N56">
-        <v>321.6198743333333</v>
+        <v>320.8103658333333</v>
       </c>
       <c r="O56">
-        <v>80.21199665873333</v>
+        <v>80.01010523883333</v>
       </c>
       <c r="P56">
-        <v>241.4078776746</v>
+        <v>240.8002605945</v>
       </c>
       <c r="Q56">
-        <v>290.4078776746</v>
+        <v>289.8002605945</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09181077588110959</v>
+        <v>0.09269768037202503</v>
       </c>
       <c r="T56">
-        <v>1.062604523813155</v>
+        <v>1.08308730651328</v>
       </c>
       <c r="U56">
         <v>0.05350000000000001</v>
@@ -5899,7 +5899,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.357456529196952</v>
+        <v>8.205502774120644</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5907,22 +5907,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06380036116741125</v>
+        <v>0.0636829314295121</v>
       </c>
       <c r="C57">
-        <v>848.3756704558099</v>
+        <v>836.0482711436491</v>
       </c>
       <c r="D57">
-        <v>1626.68067045581</v>
+        <v>1629.484271143649</v>
       </c>
       <c r="E57">
-        <v>-173.795</v>
+        <v>-158.664</v>
       </c>
       <c r="F57">
-        <v>832.205</v>
+        <v>847.336</v>
       </c>
       <c r="G57">
         <v>53.9</v>
@@ -5943,28 +5943,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M57">
-        <v>44.52296750000001</v>
+        <v>45.33247600000001</v>
       </c>
       <c r="N57">
-        <v>320.8103658333333</v>
+        <v>320.0008573333333</v>
       </c>
       <c r="O57">
-        <v>80.01010523883333</v>
+        <v>79.80821381893334</v>
       </c>
       <c r="P57">
-        <v>240.8002605945</v>
+        <v>240.1926435144</v>
       </c>
       <c r="Q57">
-        <v>289.8002605945</v>
+        <v>289.1926435144</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09269768037202503</v>
+        <v>0.09362489870343661</v>
       </c>
       <c r="T57">
-        <v>1.08308730651328</v>
+        <v>1.104501124790684</v>
       </c>
       <c r="U57">
         <v>0.05350000000000001</v>
@@ -5981,7 +5981,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.205502774120644</v>
+        <v>8.058975938868489</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5989,22 +5989,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0636829314295121</v>
+        <v>0.06356550169161296</v>
       </c>
       <c r="C58">
-        <v>836.0482711436491</v>
+        <v>823.7305525849927</v>
       </c>
       <c r="D58">
-        <v>1629.484271143649</v>
+        <v>1632.297552584993</v>
       </c>
       <c r="E58">
-        <v>-158.664</v>
+        <v>-143.5329999999999</v>
       </c>
       <c r="F58">
-        <v>847.336</v>
+        <v>862.4670000000001</v>
       </c>
       <c r="G58">
         <v>53.9</v>
@@ -6025,28 +6025,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M58">
-        <v>45.33247600000001</v>
+        <v>46.14198450000001</v>
       </c>
       <c r="N58">
-        <v>320.0008573333333</v>
+        <v>319.1913488333333</v>
       </c>
       <c r="O58">
-        <v>79.80821381893334</v>
+        <v>79.60632239903332</v>
       </c>
       <c r="P58">
-        <v>240.1926435144</v>
+        <v>239.5850264342999</v>
       </c>
       <c r="Q58">
-        <v>289.1926435144</v>
+        <v>288.5850264342999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09362489870343661</v>
+        <v>0.09459524346886736</v>
       </c>
       <c r="T58">
-        <v>1.104501124790684</v>
+        <v>1.126910934615874</v>
       </c>
       <c r="U58">
         <v>0.05350000000000001</v>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.058975938868489</v>
+        <v>7.917590396081321</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6071,22 +6071,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06356550169161296</v>
+        <v>0.06344807195371381</v>
       </c>
       <c r="C59">
-        <v>823.7305525849927</v>
+        <v>811.4225650076081</v>
       </c>
       <c r="D59">
-        <v>1632.297552584993</v>
+        <v>1635.120565007608</v>
       </c>
       <c r="E59">
-        <v>-143.5329999999999</v>
+        <v>-128.4019999999999</v>
       </c>
       <c r="F59">
-        <v>862.4670000000001</v>
+        <v>877.5980000000001</v>
       </c>
       <c r="G59">
         <v>53.9</v>
@@ -6107,28 +6107,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M59">
-        <v>46.14198450000001</v>
+        <v>46.95149300000001</v>
       </c>
       <c r="N59">
-        <v>319.1913488333333</v>
+        <v>318.3818403333333</v>
       </c>
       <c r="O59">
-        <v>79.60632239903332</v>
+        <v>79.40443097913332</v>
       </c>
       <c r="P59">
-        <v>239.5850264342999</v>
+        <v>238.9774093541999</v>
       </c>
       <c r="Q59">
-        <v>288.5850264342999</v>
+        <v>287.9774093541999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09459524346886736</v>
+        <v>0.09561179512789003</v>
       </c>
       <c r="T59">
-        <v>1.126910934615874</v>
+        <v>1.150387878242264</v>
       </c>
       <c r="U59">
         <v>0.05350000000000001</v>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>7.917590396081321</v>
+        <v>7.781080216838541</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6153,22 +6153,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0634480719537138</v>
+        <v>0.06333064221581466</v>
       </c>
       <c r="C60">
-        <v>811.4225650076086</v>
+        <v>799.1243589873353</v>
       </c>
       <c r="D60">
-        <v>1635.120565007608</v>
+        <v>1637.953358987335</v>
       </c>
       <c r="E60">
-        <v>-128.4020000000002</v>
+        <v>-113.2710000000001</v>
       </c>
       <c r="F60">
-        <v>877.5979999999998</v>
+        <v>892.7289999999999</v>
       </c>
       <c r="G60">
         <v>53.9</v>
@@ -6189,28 +6189,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M60">
-        <v>46.951493</v>
+        <v>47.7610015</v>
       </c>
       <c r="N60">
-        <v>318.3818403333333</v>
+        <v>317.5723318333333</v>
       </c>
       <c r="O60">
-        <v>79.40443097913334</v>
+        <v>79.20253955923333</v>
       </c>
       <c r="P60">
-        <v>238.9774093542</v>
+        <v>238.3697922741</v>
       </c>
       <c r="Q60">
-        <v>287.9774093542</v>
+        <v>287.3697922741</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09561179512789</v>
+        <v>0.09667793467271868</v>
       </c>
       <c r="T60">
-        <v>1.150387878242264</v>
+        <v>1.175010038630916</v>
       </c>
       <c r="U60">
         <v>0.05350000000000001</v>
@@ -6227,7 +6227,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>7.781080216838543</v>
+        <v>7.649197501298906</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6235,22 +6235,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06333064221581466</v>
+        <v>0.0635735004779155</v>
       </c>
       <c r="C61">
-        <v>799.1243589873353</v>
+        <v>778.1456162178611</v>
       </c>
       <c r="D61">
-        <v>1637.953358987335</v>
+        <v>1632.105616217861</v>
       </c>
       <c r="E61">
-        <v>-113.2710000000001</v>
+        <v>-98.1400000000001</v>
       </c>
       <c r="F61">
-        <v>892.7289999999999</v>
+        <v>907.8599999999999</v>
       </c>
       <c r="G61">
         <v>53.9</v>
@@ -6271,45 +6271,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M61">
-        <v>47.7610015</v>
+        <v>49.296798</v>
       </c>
       <c r="N61">
-        <v>317.5723318333333</v>
+        <v>316.0365353333333</v>
       </c>
       <c r="O61">
-        <v>79.20253955923333</v>
+        <v>78.81951191213332</v>
       </c>
       <c r="P61">
-        <v>238.3697922741</v>
+        <v>237.2170234212</v>
       </c>
       <c r="Q61">
-        <v>287.3697922741</v>
+        <v>286.2170234212</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09667793467271868</v>
+        <v>0.09779738119478876</v>
       </c>
       <c r="T61">
-        <v>1.175010038630916</v>
+        <v>1.200863307039002</v>
       </c>
       <c r="U61">
-        <v>0.05350000000000001</v>
+        <v>0.05430000000000001</v>
       </c>
       <c r="V61">
         <v>0.2494</v>
       </c>
       <c r="W61">
-        <v>0.0401571</v>
+        <v>0.04075758</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y61">
-        <v>7.649197501298906</v>
+        <v>7.410893773127684</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6317,22 +6317,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0635735004779155</v>
+        <v>0.06346207554001636</v>
       </c>
       <c r="C62">
-        <v>778.1456162178611</v>
+        <v>765.6924059267664</v>
       </c>
       <c r="D62">
-        <v>1632.105616217861</v>
+        <v>1634.783405926766</v>
       </c>
       <c r="E62">
-        <v>-98.1400000000001</v>
+        <v>-83.00900000000013</v>
       </c>
       <c r="F62">
-        <v>907.8599999999999</v>
+        <v>922.9909999999999</v>
       </c>
       <c r="G62">
         <v>53.9</v>
@@ -6353,28 +6353,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M62">
-        <v>49.296798</v>
+        <v>50.1184113</v>
       </c>
       <c r="N62">
-        <v>316.0365353333333</v>
+        <v>315.2149220333333</v>
       </c>
       <c r="O62">
-        <v>78.81951191213332</v>
+        <v>78.61460155511334</v>
       </c>
       <c r="P62">
-        <v>237.2170234212</v>
+        <v>236.60032047822</v>
       </c>
       <c r="Q62">
-        <v>286.2170234212</v>
+        <v>285.60032047822</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.09779738119478876</v>
+        <v>0.09897423523081117</v>
       </c>
       <c r="T62">
-        <v>1.200863307039002</v>
+        <v>1.228042384083399</v>
       </c>
       <c r="U62">
         <v>0.05430000000000001</v>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.410893773127684</v>
+        <v>7.289403711273133</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6399,22 +6399,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06346207554001636</v>
+        <v>0.06335065060211721</v>
       </c>
       <c r="C63">
-        <v>765.6924059267664</v>
+        <v>753.2479969555069</v>
       </c>
       <c r="D63">
-        <v>1634.783405926766</v>
+        <v>1637.469996955507</v>
       </c>
       <c r="E63">
-        <v>-83.00900000000013</v>
+        <v>-67.87800000000004</v>
       </c>
       <c r="F63">
-        <v>922.9909999999999</v>
+        <v>938.122</v>
       </c>
       <c r="G63">
         <v>53.9</v>
@@ -6435,28 +6435,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M63">
-        <v>50.1184113</v>
+        <v>50.94002460000001</v>
       </c>
       <c r="N63">
-        <v>315.2149220333333</v>
+        <v>314.3933087333333</v>
       </c>
       <c r="O63">
-        <v>78.61460155511334</v>
+        <v>78.40969119809333</v>
       </c>
       <c r="P63">
-        <v>236.60032047822</v>
+        <v>235.98361753524</v>
       </c>
       <c r="Q63">
-        <v>285.60032047822</v>
+        <v>284.98361753524</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09897423523081117</v>
+        <v>0.10021302895294</v>
       </c>
       <c r="T63">
-        <v>1.228042384083399</v>
+        <v>1.256651938866975</v>
       </c>
       <c r="U63">
         <v>0.05430000000000001</v>
@@ -6473,7 +6473,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.289403711273133</v>
+        <v>7.171832683671952</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6481,22 +6481,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06335065060211721</v>
+        <v>0.06323922566421807</v>
       </c>
       <c r="C64">
-        <v>753.2479969555069</v>
+        <v>740.8124327675839</v>
       </c>
       <c r="D64">
-        <v>1637.469996955507</v>
+        <v>1640.165432767584</v>
       </c>
       <c r="E64">
-        <v>-67.87800000000004</v>
+        <v>-52.74700000000007</v>
       </c>
       <c r="F64">
-        <v>938.122</v>
+        <v>953.2529999999999</v>
       </c>
       <c r="G64">
         <v>53.9</v>
@@ -6517,28 +6517,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M64">
-        <v>50.94002460000001</v>
+        <v>51.7616379</v>
       </c>
       <c r="N64">
-        <v>314.3933087333333</v>
+        <v>313.5716954333333</v>
       </c>
       <c r="O64">
-        <v>78.40969119809333</v>
+        <v>78.20478084107333</v>
       </c>
       <c r="P64">
-        <v>235.98361753524</v>
+        <v>235.36691459226</v>
       </c>
       <c r="Q64">
-        <v>284.98361753524</v>
+        <v>284.36691459226</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.10021302895294</v>
+        <v>0.1015187844978866</v>
       </c>
       <c r="T64">
-        <v>1.256651938866975</v>
+        <v>1.286807956071285</v>
       </c>
       <c r="U64">
         <v>0.05430000000000001</v>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.171832683671952</v>
+        <v>7.057994069645414</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6563,22 +6563,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06323922566421807</v>
+        <v>0.06312780072631891</v>
       </c>
       <c r="C65">
-        <v>740.8124327675839</v>
+        <v>728.3857571131502</v>
       </c>
       <c r="D65">
-        <v>1640.165432767584</v>
+        <v>1642.86975711315</v>
       </c>
       <c r="E65">
-        <v>-52.74700000000007</v>
+        <v>-37.61599999999999</v>
       </c>
       <c r="F65">
-        <v>953.2529999999999</v>
+        <v>968.384</v>
       </c>
       <c r="G65">
         <v>53.9</v>
@@ -6599,28 +6599,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M65">
-        <v>51.7616379</v>
+        <v>52.58325120000001</v>
       </c>
       <c r="N65">
-        <v>313.5716954333333</v>
+        <v>312.7500821333333</v>
       </c>
       <c r="O65">
-        <v>78.20478084107333</v>
+        <v>77.99987048405333</v>
       </c>
       <c r="P65">
-        <v>235.36691459226</v>
+        <v>234.75021164928</v>
       </c>
       <c r="Q65">
-        <v>284.36691459226</v>
+        <v>283.75021164928</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1015187844978866</v>
+        <v>0.1028970820175525</v>
       </c>
       <c r="T65">
-        <v>1.286807956071285</v>
+        <v>1.318639307564723</v>
       </c>
       <c r="U65">
         <v>0.05430000000000001</v>
@@ -6637,7 +6637,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.057994069645414</v>
+        <v>6.947712912307204</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6645,22 +6645,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06312780072631891</v>
+        <v>0.06301637578841976</v>
       </c>
       <c r="C66">
-        <v>728.3857571131502</v>
+        <v>715.9680140313784</v>
       </c>
       <c r="D66">
-        <v>1642.86975711315</v>
+        <v>1645.583014031378</v>
       </c>
       <c r="E66">
-        <v>-37.61599999999999</v>
+        <v>-22.48500000000001</v>
       </c>
       <c r="F66">
-        <v>968.384</v>
+        <v>983.515</v>
       </c>
       <c r="G66">
         <v>53.9</v>
@@ -6681,28 +6681,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M66">
-        <v>52.58325120000001</v>
+        <v>53.40486450000001</v>
       </c>
       <c r="N66">
-        <v>312.7500821333333</v>
+        <v>311.9284688333333</v>
       </c>
       <c r="O66">
-        <v>77.99987048405333</v>
+        <v>77.79496012703332</v>
       </c>
       <c r="P66">
-        <v>234.75021164928</v>
+        <v>234.1335087062999</v>
       </c>
       <c r="Q66">
-        <v>283.75021164928</v>
+        <v>283.1335087062999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1028970820175525</v>
+        <v>0.104354139395485</v>
       </c>
       <c r="T66">
-        <v>1.318639307564723</v>
+        <v>1.352289593429215</v>
       </c>
       <c r="U66">
         <v>0.05430000000000001</v>
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>6.947712912307204</v>
+        <v>6.840825021348631</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6727,22 +6727,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06301637578841976</v>
+        <v>0.06290495085052061</v>
       </c>
       <c r="C67">
-        <v>715.9680140313784</v>
+        <v>703.5592478528511</v>
       </c>
       <c r="D67">
-        <v>1645.583014031378</v>
+        <v>1648.305247852851</v>
       </c>
       <c r="E67">
-        <v>-22.48500000000001</v>
+        <v>-7.354000000000042</v>
       </c>
       <c r="F67">
-        <v>983.515</v>
+        <v>998.646</v>
       </c>
       <c r="G67">
         <v>53.9</v>
@@ -6763,28 +6763,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M67">
-        <v>53.40486450000001</v>
+        <v>54.2264778</v>
       </c>
       <c r="N67">
-        <v>311.9284688333333</v>
+        <v>311.1068555333333</v>
       </c>
       <c r="O67">
-        <v>77.79496012703332</v>
+        <v>77.59004977001334</v>
       </c>
       <c r="P67">
-        <v>234.1335087062999</v>
+        <v>233.51680576332</v>
       </c>
       <c r="Q67">
-        <v>283.1335087062999</v>
+        <v>282.51680576332</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.104354139395485</v>
+        <v>0.105896906030943</v>
       </c>
       <c r="T67">
-        <v>1.352289593429215</v>
+        <v>1.387919307873972</v>
       </c>
       <c r="U67">
         <v>0.05430000000000001</v>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>6.840825021348631</v>
+        <v>6.737176157388804</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6809,22 +6809,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06290495085052061</v>
+        <v>0.06279352591262147</v>
       </c>
       <c r="C68">
-        <v>703.5592478528511</v>
+        <v>691.1595032019763</v>
       </c>
       <c r="D68">
-        <v>1648.305247852851</v>
+        <v>1651.036503201976</v>
       </c>
       <c r="E68">
-        <v>-7.354000000000042</v>
+        <v>7.777000000000044</v>
       </c>
       <c r="F68">
-        <v>998.646</v>
+        <v>1013.777</v>
       </c>
       <c r="G68">
         <v>53.9</v>
@@ -6845,28 +6845,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M68">
-        <v>54.2264778</v>
+        <v>55.04809110000001</v>
       </c>
       <c r="N68">
-        <v>311.1068555333333</v>
+        <v>310.2852422333333</v>
       </c>
       <c r="O68">
-        <v>77.59004977001334</v>
+        <v>77.38513941299333</v>
       </c>
       <c r="P68">
-        <v>233.51680576332</v>
+        <v>232.90010282034</v>
       </c>
       <c r="Q68">
-        <v>282.51680576332</v>
+        <v>281.90010282034</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.105896906030943</v>
+        <v>0.1075331736746105</v>
       </c>
       <c r="T68">
-        <v>1.387919307873972</v>
+        <v>1.425708398951743</v>
       </c>
       <c r="U68">
         <v>0.05430000000000001</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>6.737176157388804</v>
+        <v>6.636621289368075</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06279352591262147</v>
+        <v>0.06268210097472231</v>
       </c>
       <c r="C69">
-        <v>691.1595032019763</v>
+        <v>678.7688249994246</v>
       </c>
       <c r="D69">
-        <v>1651.036503201976</v>
+        <v>1653.776824999424</v>
       </c>
       <c r="E69">
-        <v>7.777000000000044</v>
+        <v>22.9079999999999</v>
       </c>
       <c r="F69">
-        <v>1013.777</v>
+        <v>1028.908</v>
       </c>
       <c r="G69">
         <v>53.9</v>
@@ -6927,28 +6927,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M69">
-        <v>55.04809110000001</v>
+        <v>55.8697044</v>
       </c>
       <c r="N69">
-        <v>310.2852422333333</v>
+        <v>309.4636289333333</v>
       </c>
       <c r="O69">
-        <v>77.38513941299333</v>
+        <v>77.18022905597333</v>
       </c>
       <c r="P69">
-        <v>232.90010282034</v>
+        <v>232.28339987736</v>
       </c>
       <c r="Q69">
-        <v>281.90010282034</v>
+        <v>281.28339987736</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1075331736746105</v>
+        <v>0.1092717080460072</v>
       </c>
       <c r="T69">
-        <v>1.425708398951743</v>
+        <v>1.465859308221876</v>
       </c>
       <c r="U69">
         <v>0.05430000000000001</v>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.636621289368075</v>
+        <v>6.539023917465604</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6973,22 +6973,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06268210097472231</v>
+        <v>0.06257067603682316</v>
       </c>
       <c r="C70">
-        <v>678.7688249994246</v>
+        <v>666.387258464591</v>
       </c>
       <c r="D70">
-        <v>1653.776824999424</v>
+        <v>1656.526258464591</v>
       </c>
       <c r="E70">
-        <v>22.9079999999999</v>
+        <v>38.03899999999999</v>
       </c>
       <c r="F70">
-        <v>1028.908</v>
+        <v>1044.039</v>
       </c>
       <c r="G70">
         <v>53.9</v>
@@ -7009,28 +7009,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M70">
-        <v>55.8697044</v>
+        <v>56.69131770000001</v>
       </c>
       <c r="N70">
-        <v>309.4636289333333</v>
+        <v>308.6420156333333</v>
       </c>
       <c r="O70">
-        <v>77.18022905597333</v>
+        <v>76.97531869895333</v>
       </c>
       <c r="P70">
-        <v>232.28339987736</v>
+        <v>231.66669693438</v>
       </c>
       <c r="Q70">
-        <v>281.28339987736</v>
+        <v>280.66669693438</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1092717080460072</v>
+        <v>0.111122405925236</v>
       </c>
       <c r="T70">
-        <v>1.465859308221876</v>
+        <v>1.508600598735242</v>
       </c>
       <c r="U70">
         <v>0.05430000000000001</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.539023917465604</v>
+        <v>6.444255454893638</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7055,22 +7055,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06257067603682316</v>
+        <v>0.06245925109892401</v>
       </c>
       <c r="C71">
-        <v>666.387258464591</v>
+        <v>654.0148491180857</v>
       </c>
       <c r="D71">
-        <v>1656.526258464591</v>
+        <v>1659.284849118086</v>
       </c>
       <c r="E71">
-        <v>38.03899999999999</v>
+        <v>53.17000000000007</v>
       </c>
       <c r="F71">
-        <v>1044.039</v>
+        <v>1059.17</v>
       </c>
       <c r="G71">
         <v>53.9</v>
@@ -7091,28 +7091,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M71">
-        <v>56.69131770000001</v>
+        <v>57.51293100000001</v>
       </c>
       <c r="N71">
-        <v>308.6420156333333</v>
+        <v>307.8204023333333</v>
       </c>
       <c r="O71">
-        <v>76.97531869895333</v>
+        <v>76.77040834193332</v>
       </c>
       <c r="P71">
-        <v>231.66669693438</v>
+        <v>231.0499939914</v>
       </c>
       <c r="Q71">
-        <v>280.66669693438</v>
+        <v>280.0499939914</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.111122405925236</v>
+        <v>0.11309648366308</v>
       </c>
       <c r="T71">
-        <v>1.508600598735242</v>
+        <v>1.554191308616167</v>
       </c>
       <c r="U71">
         <v>0.05430000000000001</v>
@@ -7129,7 +7129,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.444255454893638</v>
+        <v>6.352194662680871</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7137,22 +7137,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.06245925109892401</v>
+        <v>0.06234782616102487</v>
       </c>
       <c r="C72">
-        <v>654.0148491180857</v>
+        <v>641.6516427842423</v>
       </c>
       <c r="D72">
-        <v>1659.284849118086</v>
+        <v>1662.052642784242</v>
       </c>
       <c r="E72">
-        <v>53.17000000000007</v>
+        <v>68.30100000000016</v>
       </c>
       <c r="F72">
-        <v>1059.17</v>
+        <v>1074.301</v>
       </c>
       <c r="G72">
         <v>53.9</v>
@@ -7173,28 +7173,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M72">
-        <v>57.51293100000001</v>
+        <v>58.33454430000002</v>
       </c>
       <c r="N72">
-        <v>307.8204023333333</v>
+        <v>306.9987890333333</v>
       </c>
       <c r="O72">
-        <v>76.77040834193332</v>
+        <v>76.56549798491334</v>
       </c>
       <c r="P72">
-        <v>231.0499939914</v>
+        <v>230.43329104842</v>
       </c>
       <c r="Q72">
-        <v>280.0499939914</v>
+        <v>279.43329104842</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.11309648366308</v>
+        <v>0.1152067046931892</v>
       </c>
       <c r="T72">
-        <v>1.554191308616167</v>
+        <v>1.602926205385432</v>
       </c>
       <c r="U72">
         <v>0.05430000000000001</v>
@@ -7211,7 +7211,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.352194662680871</v>
+        <v>6.262727132220577</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7219,22 +7219,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.06234782616102486</v>
+        <v>0.06223640122312571</v>
       </c>
       <c r="C73">
-        <v>641.6516427842428</v>
+        <v>629.2976855936588</v>
       </c>
       <c r="D73">
-        <v>1662.052642784243</v>
+        <v>1664.829685593658</v>
       </c>
       <c r="E73">
-        <v>68.30099999999993</v>
+        <v>83.43199999999979</v>
       </c>
       <c r="F73">
-        <v>1074.301</v>
+        <v>1089.432</v>
       </c>
       <c r="G73">
         <v>53.9</v>
@@ -7255,28 +7255,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M73">
-        <v>58.3345443</v>
+        <v>59.1561576</v>
       </c>
       <c r="N73">
-        <v>306.9987890333333</v>
+        <v>306.1771757333333</v>
       </c>
       <c r="O73">
-        <v>76.56549798491334</v>
+        <v>76.36058762789334</v>
       </c>
       <c r="P73">
-        <v>230.43329104842</v>
+        <v>229.81658810544</v>
       </c>
       <c r="Q73">
-        <v>279.43329104842</v>
+        <v>278.81658810544</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1152067046931892</v>
+        <v>0.1174676557968775</v>
       </c>
       <c r="T73">
-        <v>1.602926205385431</v>
+        <v>1.655142166209643</v>
       </c>
       <c r="U73">
         <v>0.05430000000000001</v>
@@ -7293,7 +7293,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.262727132220578</v>
+        <v>6.175744810939738</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7301,22 +7301,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06223640122312571</v>
+        <v>0.06267291428522656</v>
       </c>
       <c r="C74">
-        <v>629.2976855936588</v>
+        <v>603.3401632020386</v>
       </c>
       <c r="D74">
-        <v>1664.829685593658</v>
+        <v>1654.003163202038</v>
       </c>
       <c r="E74">
-        <v>83.43199999999979</v>
+        <v>98.56299999999987</v>
       </c>
       <c r="F74">
-        <v>1089.432</v>
+        <v>1104.563</v>
       </c>
       <c r="G74">
         <v>53.9</v>
@@ -7337,45 +7337,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M74">
-        <v>59.1561576</v>
+        <v>61.0823339</v>
       </c>
       <c r="N74">
-        <v>306.1771757333333</v>
+        <v>304.2509994333333</v>
       </c>
       <c r="O74">
-        <v>76.36058762789334</v>
+        <v>75.88019925867334</v>
       </c>
       <c r="P74">
-        <v>229.81658810544</v>
+        <v>228.37080017466</v>
       </c>
       <c r="Q74">
-        <v>278.81658810544</v>
+        <v>277.37080017466</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1174676557968775</v>
+        <v>0.1198960847600983</v>
       </c>
       <c r="T74">
-        <v>1.655142166209643</v>
+        <v>1.711225975983796</v>
       </c>
       <c r="U74">
-        <v>0.05430000000000001</v>
+        <v>0.05530000000000001</v>
       </c>
       <c r="V74">
         <v>0.2494</v>
       </c>
       <c r="W74">
-        <v>0.04075758</v>
+        <v>0.04150818000000001</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>6.175744810939738</v>
+        <v>5.98099826917932</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7383,22 +7383,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06267291428522656</v>
+        <v>0.06256899534732741</v>
       </c>
       <c r="C75">
-        <v>603.3401632020386</v>
+        <v>590.7737998152713</v>
       </c>
       <c r="D75">
-        <v>1654.003163202038</v>
+        <v>1656.567799815271</v>
       </c>
       <c r="E75">
-        <v>98.56299999999987</v>
+        <v>113.694</v>
       </c>
       <c r="F75">
-        <v>1104.563</v>
+        <v>1119.694</v>
       </c>
       <c r="G75">
         <v>53.9</v>
@@ -7419,28 +7419,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M75">
-        <v>61.0823339</v>
+        <v>61.91907820000001</v>
       </c>
       <c r="N75">
-        <v>304.2509994333333</v>
+        <v>303.4142551333333</v>
       </c>
       <c r="O75">
-        <v>75.88019925867334</v>
+        <v>75.67151523025333</v>
       </c>
       <c r="P75">
-        <v>228.37080017466</v>
+        <v>227.74273990308</v>
       </c>
       <c r="Q75">
-        <v>277.37080017466</v>
+        <v>276.74273990308</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1198960847600983</v>
+        <v>0.1225113159512592</v>
       </c>
       <c r="T75">
-        <v>1.711225975983796</v>
+        <v>1.771623924971345</v>
       </c>
       <c r="U75">
         <v>0.05530000000000001</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>5.98099826917932</v>
+        <v>5.900173968244464</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7465,22 +7465,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06256899534732741</v>
+        <v>0.06246507640942826</v>
       </c>
       <c r="C76">
-        <v>590.7737998152713</v>
+        <v>578.2154020425451</v>
       </c>
       <c r="D76">
-        <v>1656.567799815271</v>
+        <v>1659.140402042545</v>
       </c>
       <c r="E76">
-        <v>113.694</v>
+        <v>128.8249999999998</v>
       </c>
       <c r="F76">
-        <v>1119.694</v>
+        <v>1134.825</v>
       </c>
       <c r="G76">
         <v>53.9</v>
@@ -7501,28 +7501,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M76">
-        <v>61.91907820000001</v>
+        <v>62.7558225</v>
       </c>
       <c r="N76">
-        <v>303.4142551333333</v>
+        <v>302.5775108333333</v>
       </c>
       <c r="O76">
-        <v>75.67151523025333</v>
+        <v>75.46283120183332</v>
       </c>
       <c r="P76">
-        <v>227.74273990308</v>
+        <v>227.1146796315</v>
       </c>
       <c r="Q76">
-        <v>276.74273990308</v>
+        <v>276.1146796314999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1225113159512592</v>
+        <v>0.125335765637713</v>
       </c>
       <c r="T76">
-        <v>1.771623924971345</v>
+        <v>1.836853709877899</v>
       </c>
       <c r="U76">
         <v>0.05530000000000001</v>
@@ -7539,7 +7539,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>5.900173968244464</v>
+        <v>5.821504982001205</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06246507640942826</v>
+        <v>0.06236115747152911</v>
       </c>
       <c r="C77">
-        <v>578.2154020425451</v>
+        <v>565.6650070526921</v>
       </c>
       <c r="D77">
-        <v>1659.140402042545</v>
+        <v>1661.721007052692</v>
       </c>
       <c r="E77">
-        <v>128.8249999999998</v>
+        <v>143.9559999999999</v>
       </c>
       <c r="F77">
-        <v>1134.825</v>
+        <v>1149.956</v>
       </c>
       <c r="G77">
         <v>53.9</v>
@@ -7583,28 +7583,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M77">
-        <v>62.7558225</v>
+        <v>63.59256680000001</v>
       </c>
       <c r="N77">
-        <v>302.5775108333333</v>
+        <v>301.7407665333333</v>
       </c>
       <c r="O77">
-        <v>75.46283120183332</v>
+        <v>75.25414717341333</v>
       </c>
       <c r="P77">
-        <v>227.1146796315</v>
+        <v>226.48661935992</v>
       </c>
       <c r="Q77">
-        <v>276.1146796314999</v>
+        <v>275.48661935992</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.125335765637713</v>
+        <v>0.1283955861313713</v>
       </c>
       <c r="T77">
-        <v>1.836853709877899</v>
+        <v>1.907519310193332</v>
       </c>
       <c r="U77">
         <v>0.05530000000000001</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>5.821504982001205</v>
+        <v>5.744906232238031</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7629,22 +7629,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.06236115747152911</v>
+        <v>0.06225723853362997</v>
       </c>
       <c r="C78">
-        <v>565.6650070526921</v>
+        <v>553.1226522461518</v>
       </c>
       <c r="D78">
-        <v>1661.721007052692</v>
+        <v>1664.309652246152</v>
       </c>
       <c r="E78">
-        <v>143.9559999999999</v>
+        <v>159.087</v>
       </c>
       <c r="F78">
-        <v>1149.956</v>
+        <v>1165.087</v>
       </c>
       <c r="G78">
         <v>53.9</v>
@@ -7665,28 +7665,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M78">
-        <v>63.59256680000001</v>
+        <v>64.42931110000001</v>
       </c>
       <c r="N78">
-        <v>301.7407665333333</v>
+        <v>300.9040222333333</v>
       </c>
       <c r="O78">
-        <v>75.25414717341333</v>
+        <v>75.04546314499333</v>
       </c>
       <c r="P78">
-        <v>226.48661935992</v>
+        <v>225.85855908834</v>
       </c>
       <c r="Q78">
-        <v>275.48661935992</v>
+        <v>274.85855908834</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1283955861313713</v>
+        <v>0.1317214779723042</v>
       </c>
       <c r="T78">
-        <v>1.907519310193332</v>
+        <v>1.984329745318803</v>
       </c>
       <c r="U78">
         <v>0.05530000000000001</v>
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>5.744906232238031</v>
+        <v>5.670297060390784</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7711,22 +7711,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.06225723853362997</v>
+        <v>0.06215331959573081</v>
       </c>
       <c r="C79">
-        <v>553.1226522461518</v>
+        <v>540.5883752567788</v>
       </c>
       <c r="D79">
-        <v>1664.309652246152</v>
+        <v>1666.906375256779</v>
       </c>
       <c r="E79">
-        <v>159.087</v>
+        <v>174.2180000000001</v>
       </c>
       <c r="F79">
-        <v>1165.087</v>
+        <v>1180.218</v>
       </c>
       <c r="G79">
         <v>53.9</v>
@@ -7747,28 +7747,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M79">
-        <v>64.42931110000001</v>
+        <v>65.26605540000001</v>
       </c>
       <c r="N79">
-        <v>300.9040222333333</v>
+        <v>300.0672779333333</v>
       </c>
       <c r="O79">
-        <v>75.04546314499333</v>
+        <v>74.83677911657333</v>
       </c>
       <c r="P79">
-        <v>225.85855908834</v>
+        <v>225.23049881676</v>
       </c>
       <c r="Q79">
-        <v>274.85855908834</v>
+        <v>274.23049881676</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1317214779723042</v>
+        <v>0.1353497236169582</v>
       </c>
       <c r="T79">
-        <v>1.984329745318803</v>
+        <v>2.068122947273862</v>
       </c>
       <c r="U79">
         <v>0.05530000000000001</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.670297060390784</v>
+        <v>5.597600944231926</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7793,22 +7793,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.06215331959573081</v>
+        <v>0.06204940065783165</v>
       </c>
       <c r="C80">
-        <v>540.5883752567788</v>
+        <v>528.0622139536663</v>
       </c>
       <c r="D80">
-        <v>1666.906375256779</v>
+        <v>1669.511213953666</v>
       </c>
       <c r="E80">
-        <v>174.2180000000001</v>
+        <v>189.3489999999999</v>
       </c>
       <c r="F80">
-        <v>1180.218</v>
+        <v>1195.349</v>
       </c>
       <c r="G80">
         <v>53.9</v>
@@ -7829,28 +7829,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M80">
-        <v>65.26605540000001</v>
+        <v>66.10279970000001</v>
       </c>
       <c r="N80">
-        <v>300.0672779333333</v>
+        <v>299.2305336333333</v>
       </c>
       <c r="O80">
-        <v>74.83677911657333</v>
+        <v>74.62809508815333</v>
       </c>
       <c r="P80">
-        <v>225.23049881676</v>
+        <v>224.60243854518</v>
       </c>
       <c r="Q80">
-        <v>274.23049881676</v>
+        <v>273.60243854518</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1353497236169582</v>
+        <v>0.139323516465865</v>
       </c>
       <c r="T80">
-        <v>2.068122947273862</v>
+        <v>2.159896454177022</v>
       </c>
       <c r="U80">
         <v>0.05530000000000001</v>
@@ -7867,7 +7867,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.597600944231926</v>
+        <v>5.526745236077093</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7875,22 +7875,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.06204940065783165</v>
+        <v>0.06194548171993251</v>
       </c>
       <c r="C81">
-        <v>528.0622139536663</v>
+        <v>515.5442064429851</v>
       </c>
       <c r="D81">
-        <v>1669.511213953666</v>
+        <v>1672.124206442985</v>
       </c>
       <c r="E81">
-        <v>189.3489999999999</v>
+        <v>204.48</v>
       </c>
       <c r="F81">
-        <v>1195.349</v>
+        <v>1210.48</v>
       </c>
       <c r="G81">
         <v>53.9</v>
@@ -7911,28 +7911,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M81">
-        <v>66.10279970000001</v>
+        <v>66.93954400000001</v>
       </c>
       <c r="N81">
-        <v>299.2305336333333</v>
+        <v>298.3937893333333</v>
       </c>
       <c r="O81">
-        <v>74.62809508815333</v>
+        <v>74.41941105973333</v>
       </c>
       <c r="P81">
-        <v>224.60243854518</v>
+        <v>223.9743782736</v>
       </c>
       <c r="Q81">
-        <v>273.60243854518</v>
+        <v>272.9743782736</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.139323516465865</v>
+        <v>0.1436946885996626</v>
       </c>
       <c r="T81">
-        <v>2.159896454177022</v>
+        <v>2.260847311770498</v>
       </c>
       <c r="U81">
         <v>0.05530000000000001</v>
@@ -7949,7 +7949,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.526745236077093</v>
+        <v>5.457660920626129</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7957,22 +7957,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.06194548171993251</v>
+        <v>0.06184156278203336</v>
       </c>
       <c r="C82">
-        <v>515.5442064429851</v>
+        <v>503.0343910698464</v>
       </c>
       <c r="D82">
-        <v>1672.124206442985</v>
+        <v>1674.745391069846</v>
       </c>
       <c r="E82">
-        <v>204.48</v>
+        <v>219.6110000000001</v>
       </c>
       <c r="F82">
-        <v>1210.48</v>
+        <v>1225.611</v>
       </c>
       <c r="G82">
         <v>53.9</v>
@@ -7993,28 +7993,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M82">
-        <v>66.93954400000001</v>
+        <v>67.77628830000002</v>
       </c>
       <c r="N82">
-        <v>298.3937893333333</v>
+        <v>297.5570450333333</v>
       </c>
       <c r="O82">
-        <v>74.41941105973333</v>
+        <v>74.21072703131333</v>
       </c>
       <c r="P82">
-        <v>223.9743782736</v>
+        <v>223.34631800202</v>
       </c>
       <c r="Q82">
-        <v>272.9743782736</v>
+        <v>272.34631800202</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1436946885996626</v>
+        <v>0.148525984115965</v>
       </c>
       <c r="T82">
-        <v>2.260847311770498</v>
+        <v>2.372424575426444</v>
       </c>
       <c r="U82">
         <v>0.05530000000000001</v>
@@ -8031,7 +8031,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.457660920626129</v>
+        <v>5.390282390741855</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8039,22 +8039,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.06184156278203336</v>
+        <v>0.06173764384413422</v>
       </c>
       <c r="C83">
-        <v>503.0343910698464</v>
+        <v>490.5328064201719</v>
       </c>
       <c r="D83">
-        <v>1674.745391069846</v>
+        <v>1677.374806420172</v>
       </c>
       <c r="E83">
-        <v>219.6110000000001</v>
+        <v>234.742</v>
       </c>
       <c r="F83">
-        <v>1225.611</v>
+        <v>1240.742</v>
       </c>
       <c r="G83">
         <v>53.9</v>
@@ -8075,28 +8075,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M83">
-        <v>67.77628830000002</v>
+        <v>68.61303260000001</v>
       </c>
       <c r="N83">
-        <v>297.5570450333333</v>
+        <v>296.7203007333333</v>
       </c>
       <c r="O83">
-        <v>74.21072703131333</v>
+        <v>74.00204300289333</v>
       </c>
       <c r="P83">
-        <v>223.34631800202</v>
+        <v>222.71825773044</v>
       </c>
       <c r="Q83">
-        <v>272.34631800202</v>
+        <v>271.71825773044</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.148525984115965</v>
+        <v>0.1538940902451901</v>
       </c>
       <c r="T83">
-        <v>2.372424575426444</v>
+        <v>2.496399312821941</v>
       </c>
       <c r="U83">
         <v>0.05530000000000001</v>
@@ -8113,7 +8113,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.390282390741855</v>
+        <v>5.324547239635248</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8121,22 +8121,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.06173764384413422</v>
+        <v>0.06163372490623506</v>
       </c>
       <c r="C84">
-        <v>490.5328064201719</v>
+        <v>478.0394913225923</v>
       </c>
       <c r="D84">
-        <v>1677.374806420172</v>
+        <v>1680.012491322592</v>
       </c>
       <c r="E84">
-        <v>234.742</v>
+        <v>249.873</v>
       </c>
       <c r="F84">
-        <v>1240.742</v>
+        <v>1255.873</v>
       </c>
       <c r="G84">
         <v>53.9</v>
@@ -8157,28 +8157,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M84">
-        <v>68.61303260000001</v>
+        <v>69.44977690000002</v>
       </c>
       <c r="N84">
-        <v>296.7203007333333</v>
+        <v>295.8835564333333</v>
       </c>
       <c r="O84">
-        <v>74.00204300289333</v>
+        <v>73.79335897447332</v>
       </c>
       <c r="P84">
-        <v>222.71825773044</v>
+        <v>222.09019745886</v>
       </c>
       <c r="Q84">
-        <v>271.71825773044</v>
+        <v>271.09019745886</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1538940902451901</v>
+        <v>0.159893738271971</v>
       </c>
       <c r="T84">
-        <v>2.496399312821941</v>
+        <v>2.634959313440438</v>
       </c>
       <c r="U84">
         <v>0.05530000000000001</v>
@@ -8195,7 +8195,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.324547239635248</v>
+        <v>5.260396068073376</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8203,22 +8203,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.06163372490623506</v>
+        <v>0.06152980596833591</v>
       </c>
       <c r="C85">
-        <v>478.0394913225923</v>
+        <v>465.5544848503541</v>
       </c>
       <c r="D85">
-        <v>1680.012491322592</v>
+        <v>1682.658484850354</v>
       </c>
       <c r="E85">
-        <v>249.873</v>
+        <v>265.0040000000001</v>
       </c>
       <c r="F85">
-        <v>1255.873</v>
+        <v>1271.004</v>
       </c>
       <c r="G85">
         <v>53.9</v>
@@ -8239,28 +8239,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M85">
-        <v>69.44977690000002</v>
+        <v>70.28652120000002</v>
       </c>
       <c r="N85">
-        <v>295.8835564333333</v>
+        <v>295.0468121333333</v>
       </c>
       <c r="O85">
-        <v>73.79335897447332</v>
+        <v>73.58467494605333</v>
       </c>
       <c r="P85">
-        <v>222.09019745886</v>
+        <v>221.46213718728</v>
       </c>
       <c r="Q85">
-        <v>271.09019745886</v>
+        <v>270.46213718728</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.159893738271971</v>
+        <v>0.1666433423020995</v>
       </c>
       <c r="T85">
-        <v>2.634959313440438</v>
+        <v>2.790839314136246</v>
       </c>
       <c r="U85">
         <v>0.05530000000000001</v>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.260396068073376</v>
+        <v>5.197772305358217</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8285,22 +8285,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.06152980596833591</v>
+        <v>0.06142588703043676</v>
       </c>
       <c r="C86">
-        <v>465.5544848503544</v>
+        <v>453.0778263232535</v>
       </c>
       <c r="D86">
-        <v>1682.658484850354</v>
+        <v>1685.312826323253</v>
       </c>
       <c r="E86">
-        <v>265.0039999999999</v>
+        <v>280.135</v>
       </c>
       <c r="F86">
-        <v>1271.004</v>
+        <v>1286.135</v>
       </c>
       <c r="G86">
         <v>53.9</v>
@@ -8321,28 +8321,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M86">
-        <v>70.28652120000001</v>
+        <v>71.12326550000002</v>
       </c>
       <c r="N86">
-        <v>295.0468121333333</v>
+        <v>294.2100678333333</v>
       </c>
       <c r="O86">
-        <v>73.58467494605334</v>
+        <v>73.37599091763333</v>
       </c>
       <c r="P86">
-        <v>221.46213718728</v>
+        <v>220.8340769157</v>
       </c>
       <c r="Q86">
-        <v>270.46213718728</v>
+        <v>269.8340769157</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1666433423020994</v>
+        <v>0.174292893536245</v>
       </c>
       <c r="T86">
-        <v>2.790839314136245</v>
+        <v>2.967503314924827</v>
       </c>
       <c r="U86">
         <v>0.05530000000000001</v>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.197772305358218</v>
+        <v>5.136622042942239</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8367,22 +8367,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.06142588703043676</v>
+        <v>0.06132196809253761</v>
       </c>
       <c r="C87">
-        <v>453.0778263232535</v>
+        <v>440.6095553095793</v>
       </c>
       <c r="D87">
-        <v>1685.312826323253</v>
+        <v>1687.975555309579</v>
       </c>
       <c r="E87">
-        <v>280.135</v>
+        <v>295.2659999999998</v>
       </c>
       <c r="F87">
-        <v>1286.135</v>
+        <v>1301.266</v>
       </c>
       <c r="G87">
         <v>53.9</v>
@@ -8403,28 +8403,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M87">
-        <v>71.12326550000002</v>
+        <v>71.96000980000001</v>
       </c>
       <c r="N87">
-        <v>294.2100678333333</v>
+        <v>293.3733235333333</v>
       </c>
       <c r="O87">
-        <v>73.37599091763333</v>
+        <v>73.16730688921332</v>
       </c>
       <c r="P87">
-        <v>220.8340769157</v>
+        <v>220.20601664412</v>
       </c>
       <c r="Q87">
-        <v>269.8340769157</v>
+        <v>269.20601664412</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.174292893536245</v>
+        <v>0.18303523780384</v>
       </c>
       <c r="T87">
-        <v>2.967503314924827</v>
+        <v>3.169405030111779</v>
       </c>
       <c r="U87">
         <v>0.05530000000000001</v>
@@ -8441,7 +8441,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.136622042942239</v>
+        <v>5.076893879652213</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8449,22 +8449,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.06132196809253761</v>
+        <v>0.06121804915463847</v>
       </c>
       <c r="C88">
-        <v>440.6095553095793</v>
+        <v>428.1497116280825</v>
       </c>
       <c r="D88">
-        <v>1687.975555309579</v>
+        <v>1690.646711628082</v>
       </c>
       <c r="E88">
-        <v>295.2659999999998</v>
+        <v>310.3969999999999</v>
       </c>
       <c r="F88">
-        <v>1301.266</v>
+        <v>1316.397</v>
       </c>
       <c r="G88">
         <v>53.9</v>
@@ -8485,28 +8485,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M88">
-        <v>71.96000980000001</v>
+        <v>72.7967541</v>
       </c>
       <c r="N88">
-        <v>293.3733235333333</v>
+        <v>292.5365792333333</v>
       </c>
       <c r="O88">
-        <v>73.16730688921332</v>
+        <v>72.95862286079334</v>
       </c>
       <c r="P88">
-        <v>220.20601664412</v>
+        <v>219.57795637254</v>
       </c>
       <c r="Q88">
-        <v>269.20601664412</v>
+        <v>268.57795637254</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.18303523780384</v>
+        <v>0.1931225581126035</v>
       </c>
       <c r="T88">
-        <v>3.169405030111779</v>
+        <v>3.402368547635184</v>
       </c>
       <c r="U88">
         <v>0.05530000000000001</v>
@@ -8523,7 +8523,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.076893879652213</v>
+        <v>5.018538777587246</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8531,22 +8531,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.06121804915463847</v>
+        <v>0.06111413021673931</v>
       </c>
       <c r="C89">
-        <v>428.1497116280825</v>
+        <v>415.6983353499609</v>
       </c>
       <c r="D89">
-        <v>1690.646711628082</v>
+        <v>1693.326335349961</v>
       </c>
       <c r="E89">
-        <v>310.3969999999999</v>
+        <v>325.528</v>
       </c>
       <c r="F89">
-        <v>1316.397</v>
+        <v>1331.528</v>
       </c>
       <c r="G89">
         <v>53.9</v>
@@ -8567,28 +8567,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M89">
-        <v>72.7967541</v>
+        <v>73.63349840000001</v>
       </c>
       <c r="N89">
-        <v>292.5365792333333</v>
+        <v>291.6998349333333</v>
       </c>
       <c r="O89">
-        <v>72.95862286079334</v>
+        <v>72.74993883237333</v>
       </c>
       <c r="P89">
-        <v>219.57795637254</v>
+        <v>218.94989610096</v>
       </c>
       <c r="Q89">
-        <v>268.57795637254</v>
+        <v>267.94989610096</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1931225581126035</v>
+        <v>0.2048910984728276</v>
       </c>
       <c r="T89">
-        <v>3.402368547635184</v>
+        <v>3.674159318079159</v>
       </c>
       <c r="U89">
         <v>0.05530000000000001</v>
@@ -8605,7 +8605,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.018538777587246</v>
+        <v>4.961509927841936</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8613,22 +8613,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.06111413021673931</v>
+        <v>0.06101021127884015</v>
       </c>
       <c r="C90">
-        <v>415.6983353499609</v>
+        <v>403.2554668008613</v>
       </c>
       <c r="D90">
-        <v>1693.326335349961</v>
+        <v>1696.014466800861</v>
       </c>
       <c r="E90">
-        <v>325.528</v>
+        <v>340.6589999999999</v>
       </c>
       <c r="F90">
-        <v>1331.528</v>
+        <v>1346.659</v>
       </c>
       <c r="G90">
         <v>53.9</v>
@@ -8649,28 +8649,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M90">
-        <v>73.63349840000001</v>
+        <v>74.4702427</v>
       </c>
       <c r="N90">
-        <v>291.6998349333333</v>
+        <v>290.8630906333333</v>
       </c>
       <c r="O90">
-        <v>72.74993883237333</v>
+        <v>72.54125480395332</v>
       </c>
       <c r="P90">
-        <v>218.94989610096</v>
+        <v>218.3218358293799</v>
       </c>
       <c r="Q90">
-        <v>267.94989610096</v>
+        <v>267.3218358293799</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2048910984728276</v>
+        <v>0.2187993734440014</v>
       </c>
       <c r="T90">
-        <v>3.674159318079159</v>
+        <v>3.995366592240218</v>
       </c>
       <c r="U90">
         <v>0.05530000000000001</v>
@@ -8687,7 +8687,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>4.961509927841936</v>
+        <v>4.905762625281914</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8695,22 +8695,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.06101021127884015</v>
+        <v>0.06090629234094101</v>
       </c>
       <c r="C91">
-        <v>403.2554668008613</v>
+        <v>390.8211465629029</v>
       </c>
       <c r="D91">
-        <v>1696.014466800861</v>
+        <v>1698.711146562903</v>
       </c>
       <c r="E91">
-        <v>340.6589999999999</v>
+        <v>355.79</v>
       </c>
       <c r="F91">
-        <v>1346.659</v>
+        <v>1361.79</v>
       </c>
       <c r="G91">
         <v>53.9</v>
@@ -8731,28 +8731,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M91">
-        <v>74.4702427</v>
+        <v>75.30698700000001</v>
       </c>
       <c r="N91">
-        <v>290.8630906333333</v>
+        <v>290.0263463333333</v>
       </c>
       <c r="O91">
-        <v>72.54125480395332</v>
+        <v>72.33257077553333</v>
       </c>
       <c r="P91">
-        <v>218.3218358293799</v>
+        <v>217.6937755578</v>
       </c>
       <c r="Q91">
-        <v>267.3218358293799</v>
+        <v>266.6937755578</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2187993734440014</v>
+        <v>0.2354893034094101</v>
       </c>
       <c r="T91">
-        <v>3.995366592240218</v>
+        <v>4.380815321233489</v>
       </c>
       <c r="U91">
         <v>0.05530000000000001</v>
@@ -8769,7 +8769,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>4.905762625281914</v>
+        <v>4.85125415166767</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8777,22 +8777,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.06090629234094101</v>
+        <v>0.06080237340304186</v>
       </c>
       <c r="C92">
-        <v>390.8211465629029</v>
+        <v>378.3954154767205</v>
       </c>
       <c r="D92">
-        <v>1698.711146562903</v>
+        <v>1701.41641547672</v>
       </c>
       <c r="E92">
-        <v>355.79</v>
+        <v>370.921</v>
       </c>
       <c r="F92">
-        <v>1361.79</v>
+        <v>1376.921</v>
       </c>
       <c r="G92">
         <v>53.9</v>
@@ -8813,28 +8813,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M92">
-        <v>75.30698700000001</v>
+        <v>76.14373130000001</v>
       </c>
       <c r="N92">
-        <v>290.0263463333333</v>
+        <v>289.1896020333333</v>
       </c>
       <c r="O92">
-        <v>72.33257077553333</v>
+        <v>72.12388674711333</v>
       </c>
       <c r="P92">
-        <v>217.6937755578</v>
+        <v>217.06571528622</v>
       </c>
       <c r="Q92">
-        <v>266.6937755578</v>
+        <v>266.06571528622</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2354893034094101</v>
+        <v>0.2558881067004651</v>
       </c>
       <c r="T92">
-        <v>4.380815321233489</v>
+        <v>4.851919323336376</v>
       </c>
       <c r="U92">
         <v>0.05530000000000001</v>
@@ -8851,7 +8851,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>4.85125415166767</v>
+        <v>4.797943666484509</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8859,22 +8859,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.06080237340304186</v>
+        <v>0.06069845446514271</v>
       </c>
       <c r="C93">
-        <v>378.3954154767205</v>
+        <v>365.9783146435254</v>
       </c>
       <c r="D93">
-        <v>1701.41641547672</v>
+        <v>1704.130314643525</v>
       </c>
       <c r="E93">
-        <v>370.921</v>
+        <v>386.0519999999999</v>
       </c>
       <c r="F93">
-        <v>1376.921</v>
+        <v>1392.052</v>
       </c>
       <c r="G93">
         <v>53.9</v>
@@ -8895,28 +8895,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M93">
-        <v>76.14373130000001</v>
+        <v>76.98047560000001</v>
       </c>
       <c r="N93">
-        <v>289.1896020333333</v>
+        <v>288.3528577333333</v>
       </c>
       <c r="O93">
-        <v>72.12388674711333</v>
+        <v>71.91520271869332</v>
       </c>
       <c r="P93">
-        <v>217.06571528622</v>
+        <v>216.43765501464</v>
       </c>
       <c r="Q93">
-        <v>266.06571528622</v>
+        <v>265.43765501464</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2558881067004651</v>
+        <v>0.281386610814284</v>
       </c>
       <c r="T93">
-        <v>4.851919323336376</v>
+        <v>5.440799325964988</v>
       </c>
       <c r="U93">
         <v>0.05530000000000001</v>
@@ -8933,7 +8933,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.797943666484509</v>
+        <v>4.745792104892286</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8941,22 +8941,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.06069845446514271</v>
+        <v>0.06059453552724356</v>
       </c>
       <c r="C94">
-        <v>365.9783146435254</v>
+        <v>353.5698854271877</v>
       </c>
       <c r="D94">
-        <v>1704.130314643525</v>
+        <v>1706.852885427188</v>
       </c>
       <c r="E94">
-        <v>386.0519999999999</v>
+        <v>401.183</v>
       </c>
       <c r="F94">
-        <v>1392.052</v>
+        <v>1407.183</v>
       </c>
       <c r="G94">
         <v>53.9</v>
@@ -8977,28 +8977,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M94">
-        <v>76.98047560000001</v>
+        <v>77.81721990000001</v>
       </c>
       <c r="N94">
-        <v>288.3528577333333</v>
+        <v>287.5161134333333</v>
       </c>
       <c r="O94">
-        <v>71.91520271869332</v>
+        <v>71.70651869027333</v>
       </c>
       <c r="P94">
-        <v>216.43765501464</v>
+        <v>215.80959474306</v>
       </c>
       <c r="Q94">
-        <v>265.43765501464</v>
+        <v>264.80959474306</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.281386610814284</v>
+        <v>0.3141704018177652</v>
       </c>
       <c r="T94">
-        <v>5.440799325964988</v>
+        <v>6.197930757916057</v>
       </c>
       <c r="U94">
         <v>0.05530000000000001</v>
@@ -9015,7 +9015,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.745792104892286</v>
+        <v>4.694762082259036</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9023,22 +9023,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.06059453552724356</v>
+        <v>0.06049061658934441</v>
       </c>
       <c r="C95">
-        <v>353.5698854271877</v>
+        <v>341.1701694563355</v>
       </c>
       <c r="D95">
-        <v>1706.852885427188</v>
+        <v>1709.584169456336</v>
       </c>
       <c r="E95">
-        <v>401.183</v>
+        <v>416.3140000000001</v>
       </c>
       <c r="F95">
-        <v>1407.183</v>
+        <v>1422.314</v>
       </c>
       <c r="G95">
         <v>53.9</v>
@@ -9059,28 +9059,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M95">
-        <v>77.81721990000001</v>
+        <v>78.65396420000002</v>
       </c>
       <c r="N95">
-        <v>287.5161134333333</v>
+        <v>286.6793691333333</v>
       </c>
       <c r="O95">
-        <v>71.70651869027333</v>
+        <v>71.49783466185333</v>
       </c>
       <c r="P95">
-        <v>215.80959474306</v>
+        <v>215.1815344714799</v>
       </c>
       <c r="Q95">
-        <v>264.80959474306</v>
+        <v>264.1815344714799</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3141704018177652</v>
+        <v>0.3578821231557404</v>
       </c>
       <c r="T95">
-        <v>6.197930757916057</v>
+        <v>7.207439333850816</v>
       </c>
       <c r="U95">
         <v>0.05530000000000001</v>
@@ -9097,7 +9097,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.694762082259036</v>
+        <v>4.644817804788195</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9105,22 +9105,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.06049061658934441</v>
+        <v>0.06038669765144526</v>
       </c>
       <c r="C96">
-        <v>341.1701694563355</v>
+        <v>328.7792086264801</v>
       </c>
       <c r="D96">
-        <v>1709.584169456336</v>
+        <v>1712.32420862648</v>
       </c>
       <c r="E96">
-        <v>416.3140000000001</v>
+        <v>431.4449999999999</v>
       </c>
       <c r="F96">
-        <v>1422.314</v>
+        <v>1437.445</v>
       </c>
       <c r="G96">
         <v>53.9</v>
@@ -9141,28 +9141,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M96">
-        <v>78.65396420000002</v>
+        <v>79.49070850000001</v>
       </c>
       <c r="N96">
-        <v>286.6793691333333</v>
+        <v>285.8426248333333</v>
       </c>
       <c r="O96">
-        <v>71.49783466185333</v>
+        <v>71.28915063343332</v>
       </c>
       <c r="P96">
-        <v>215.1815344714799</v>
+        <v>214.5534741998999</v>
       </c>
       <c r="Q96">
-        <v>264.1815344714799</v>
+        <v>263.5534741998999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3578821231557404</v>
+        <v>0.4190785330289056</v>
       </c>
       <c r="T96">
-        <v>7.207439333850816</v>
+        <v>8.620751340159483</v>
       </c>
       <c r="U96">
         <v>0.05530000000000001</v>
@@ -9179,7 +9179,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.644817804788195</v>
+        <v>4.595924985790424</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9187,22 +9187,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.06038669765144526</v>
+        <v>0.06028277871354611</v>
       </c>
       <c r="C97">
-        <v>328.7792086264801</v>
+        <v>316.3970451021557</v>
       </c>
       <c r="D97">
-        <v>1712.32420862648</v>
+        <v>1715.073045102156</v>
       </c>
       <c r="E97">
-        <v>431.4449999999999</v>
+        <v>446.576</v>
       </c>
       <c r="F97">
-        <v>1437.445</v>
+        <v>1452.576</v>
       </c>
       <c r="G97">
         <v>53.9</v>
@@ -9223,28 +9223,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M97">
-        <v>79.49070850000001</v>
+        <v>80.32745280000002</v>
       </c>
       <c r="N97">
-        <v>285.8426248333333</v>
+        <v>285.0058805333333</v>
       </c>
       <c r="O97">
-        <v>71.28915063343332</v>
+        <v>71.08046660501333</v>
       </c>
       <c r="P97">
-        <v>214.5534741998999</v>
+        <v>213.92541392832</v>
       </c>
       <c r="Q97">
-        <v>263.5534741998999</v>
+        <v>262.92541392832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4190785330289056</v>
+        <v>0.5108731478386535</v>
       </c>
       <c r="T97">
-        <v>8.620751340159483</v>
+        <v>10.74071934962248</v>
       </c>
       <c r="U97">
         <v>0.05530000000000001</v>
@@ -9261,7 +9261,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.595924985790424</v>
+        <v>4.548050767188441</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9269,22 +9269,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.06028277871354611</v>
+        <v>0.06017885977564696</v>
       </c>
       <c r="C98">
-        <v>316.397045102156</v>
+        <v>304.0237213190833</v>
       </c>
       <c r="D98">
-        <v>1715.073045102156</v>
+        <v>1717.830721319083</v>
       </c>
       <c r="E98">
-        <v>446.5759999999998</v>
+        <v>461.7069999999999</v>
       </c>
       <c r="F98">
-        <v>1452.576</v>
+        <v>1467.707</v>
       </c>
       <c r="G98">
         <v>53.9</v>
@@ -9305,28 +9305,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M98">
-        <v>80.3274528</v>
+        <v>81.16419710000001</v>
       </c>
       <c r="N98">
-        <v>285.0058805333333</v>
+        <v>284.1691362333333</v>
       </c>
       <c r="O98">
-        <v>71.08046660501333</v>
+        <v>70.87178257659333</v>
       </c>
       <c r="P98">
-        <v>213.92541392832</v>
+        <v>213.29735365674</v>
       </c>
       <c r="Q98">
-        <v>262.92541392832</v>
+        <v>262.29735365674</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5108731478386521</v>
+        <v>0.6638641725215646</v>
       </c>
       <c r="T98">
-        <v>10.74071934962245</v>
+        <v>14.2739993653941</v>
       </c>
       <c r="U98">
         <v>0.05530000000000001</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.548050767188441</v>
+        <v>4.50116364587722</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9351,22 +9351,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.06017885977564696</v>
+        <v>0.0619139108377478</v>
       </c>
       <c r="C99">
-        <v>304.0237213190833</v>
+        <v>243.9816620080692</v>
       </c>
       <c r="D99">
-        <v>1717.830721319083</v>
+        <v>1672.919662008069</v>
       </c>
       <c r="E99">
-        <v>461.7069999999999</v>
+        <v>476.838</v>
       </c>
       <c r="F99">
-        <v>1467.707</v>
+        <v>1482.838</v>
       </c>
       <c r="G99">
         <v>53.9</v>
@@ -9387,45 +9387,45 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M99">
-        <v>81.16419710000001</v>
+        <v>85.7080364</v>
       </c>
       <c r="N99">
-        <v>284.1691362333333</v>
+        <v>279.6252969333333</v>
       </c>
       <c r="O99">
-        <v>70.87178257659333</v>
+        <v>69.73854905517332</v>
       </c>
       <c r="P99">
-        <v>213.29735365674</v>
+        <v>209.88674787816</v>
       </c>
       <c r="Q99">
-        <v>262.29735365674</v>
+        <v>258.88674787816</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6638641725215646</v>
+        <v>0.9698462218873893</v>
       </c>
       <c r="T99">
-        <v>14.2739993653941</v>
+        <v>21.3405593969374</v>
       </c>
       <c r="U99">
-        <v>0.05530000000000001</v>
+        <v>0.0578</v>
       </c>
       <c r="V99">
         <v>0.2494</v>
       </c>
       <c r="W99">
-        <v>0.04150818000000001</v>
+        <v>0.04338468</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y99">
-        <v>4.50116364587722</v>
+        <v>4.262532997819715</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9433,22 +9433,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.0619139108377478</v>
+        <v>0.06182875689984866</v>
       </c>
       <c r="C100">
-        <v>243.9816620080692</v>
+        <v>230.9999672722111</v>
       </c>
       <c r="D100">
-        <v>1672.919662008069</v>
+        <v>1675.068967272211</v>
       </c>
       <c r="E100">
-        <v>476.838</v>
+        <v>491.9689999999998</v>
       </c>
       <c r="F100">
-        <v>1482.838</v>
+        <v>1497.969</v>
       </c>
       <c r="G100">
         <v>53.9</v>
@@ -9469,28 +9469,28 @@
         <v>365.3333333333333</v>
       </c>
       <c r="M100">
-        <v>85.7080364</v>
+        <v>86.5826082</v>
       </c>
       <c r="N100">
-        <v>279.6252969333333</v>
+        <v>278.7507251333333</v>
       </c>
       <c r="O100">
-        <v>69.73854905517332</v>
+        <v>69.52043084825334</v>
       </c>
       <c r="P100">
-        <v>209.88674787816</v>
+        <v>209.23029428508</v>
       </c>
       <c r="Q100">
-        <v>258.88674787816</v>
+        <v>258.23029428508</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9698462218873893</v>
+        <v>1.887792369984864</v>
       </c>
       <c r="T100">
-        <v>21.3405593969374</v>
+        <v>42.54023949156729</v>
       </c>
       <c r="U100">
         <v>0.0578</v>
@@ -9507,91 +9507,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.262532997819715</v>
+        <v>4.21947710895285</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.06182875689984866</v>
-      </c>
-      <c r="C101">
-        <v>230.9999672722111</v>
-      </c>
-      <c r="D101">
-        <v>1675.068967272211</v>
-      </c>
-      <c r="E101">
-        <v>491.9689999999998</v>
-      </c>
-      <c r="F101">
-        <v>1497.969</v>
-      </c>
-      <c r="G101">
-        <v>53.9</v>
-      </c>
-      <c r="H101">
-        <v>507.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>414.3333333333333</v>
-      </c>
-      <c r="K101">
-        <v>49</v>
-      </c>
-      <c r="L101">
-        <v>365.3333333333333</v>
-      </c>
-      <c r="M101">
-        <v>86.5826082</v>
-      </c>
-      <c r="N101">
-        <v>278.7507251333333</v>
-      </c>
-      <c r="O101">
-        <v>69.52043084825334</v>
-      </c>
-      <c r="P101">
-        <v>209.23029428508</v>
-      </c>
-      <c r="Q101">
-        <v>258.23029428508</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.887792369984864</v>
-      </c>
-      <c r="T101">
-        <v>42.54023949156729</v>
-      </c>
-      <c r="U101">
-        <v>0.0578</v>
-      </c>
-      <c r="V101">
-        <v>0.2494</v>
-      </c>
-      <c r="W101">
-        <v>0.04338468</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Baa2/BBB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.21947710895285</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
